--- a/data/modelling/competitive_pricing_workbook.xlsx
+++ b/data/modelling/competitive_pricing_workbook.xlsx
@@ -99,7 +99,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B45"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -116,7 +116,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Source table</t>
+          <t>Comparable source table</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="6">
@@ -128,391 +128,403 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Hedonic training table</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="6">
+        <is>
+          <t>data\modelling\hedonic_training_table.parquet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Price unit</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr" s="6">
+      <c r="B4" t="inlineStr" s="6">
         <is>
           <t>EUR/night for a 2-guest Booking.com search</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4"/>
-      <c r="B4" s="6"/>
-    </row>
     <row r="5">
-      <c r="A5" t="inlineStr" s="2">
+      <c r="A5"/>
+      <c r="B5" s="6"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr" s="2">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="B5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Property</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr" s="6">
-        <is>
-          <t>Stavros Villas &amp; Apartments</t>
-        </is>
-      </c>
+      <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>Property</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="6">
         <is>
-          <t>https://www.booking.com/hotel/gr/stavros-villas-amp-apartments.en-gb.html</t>
+          <t>Stavros Villas &amp; Apartments</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>URL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="6">
         <is>
-          <t>Apartment</t>
+          <t>https://www.booking.com/hotel/gr/stavros-villas-amp-apartments.en-gb.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="6">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Reference price</t>
         </is>
       </c>
-      <c r="B9" s="4">
+      <c r="B10" s="4">
         <v>133.48</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10"/>
-      <c r="B10" s="6"/>
-    </row>
     <row r="11">
-      <c r="A11" t="inlineStr" s="2">
+      <c r="A11"/>
+      <c r="B11" s="6"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="2">
         <is>
           <t>Peer Price Position</t>
         </is>
       </c>
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Peer rows</t>
-        </is>
-      </c>
-      <c r="B12" s="6">
-        <v>109</v>
-      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Peer properties with prices</t>
+          <t>Peer rows</t>
         </is>
       </c>
       <c r="B13" s="6">
-        <v>19</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Peer p25</t>
-        </is>
-      </c>
-      <c r="B14" s="4">
-        <v>95.25</v>
+          <t>Peer properties with prices</t>
+        </is>
+      </c>
+      <c r="B14" s="6">
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Peer median</t>
+          <t>Peer p25</t>
         </is>
       </c>
       <c r="B15" s="4">
-        <v>119.0</v>
+        <v>95.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Peer p75</t>
+          <t>Peer median</t>
         </is>
       </c>
       <c r="B16" s="4">
-        <v>162.25</v>
+        <v>119.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Subject median</t>
+          <t>Peer p75</t>
         </is>
       </c>
       <c r="B17" s="4">
-        <v>133.48000000000002</v>
+        <v>162.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Subject percentile vs peers</t>
-        </is>
-      </c>
-      <c r="B18" s="5">
-        <v>0.578</v>
+          <t>Subject median</t>
+        </is>
+      </c>
+      <c r="B18" s="4">
+        <v>133.48000000000002</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gap to peer median</t>
-        </is>
-      </c>
-      <c r="B19" s="4">
-        <v>14.48</v>
+          <t>Subject percentile vs peers</t>
+        </is>
+      </c>
+      <c r="B19" s="5">
+        <v>0.578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gap to peer median pct</t>
-        </is>
-      </c>
-      <c r="B20" s="5">
-        <v>0.1217</v>
+          <t>Gap to peer median</t>
+        </is>
+      </c>
+      <c r="B20" s="4">
+        <v>14.48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Gap to peer median pct</t>
+        </is>
+      </c>
+      <c r="B21" s="5">
+        <v>0.1217</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Flags</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr" s="6">
+      <c r="B22" t="inlineStr" s="6">
         <is>
           <t>none</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22"/>
-      <c r="B22" s="6"/>
-    </row>
     <row r="23">
-      <c r="A23" t="inlineStr" s="2">
+      <c r="A23"/>
+      <c r="B23" s="6"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr" s="2">
         <is>
           <t>Feature-Adjusted Benchmark</t>
         </is>
       </c>
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Adjusted peer rows</t>
-        </is>
-      </c>
-      <c r="B24" s="6">
-        <v>109</v>
-      </c>
+      <c r="B24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Adjusted peer p25</t>
-        </is>
-      </c>
-      <c r="B25" s="4">
-        <v>114.14401759364988</v>
+          <t>Adjusted peer rows</t>
+        </is>
+      </c>
+      <c r="B25" s="6">
+        <v>109</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Adjusted peer median</t>
+          <t>Adjusted peer p25</t>
         </is>
       </c>
       <c r="B26" s="4">
-        <v>120.3503418701948</v>
+        <v>99.18554836537695</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Adjusted peer median</t>
+        </is>
+      </c>
+      <c r="B27" s="4">
+        <v>113.62549015423039</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Adjusted peer p75</t>
         </is>
       </c>
-      <c r="B27" s="4">
-        <v>129.55977905777118</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28"/>
-      <c r="B28" s="6"/>
+      <c r="B28" s="4">
+        <v>130.79983170794557</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr" s="2">
+      <c r="A29"/>
+      <c r="B29" s="6"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr" s="2">
         <is>
           <t>Hedonic Training</t>
         </is>
       </c>
-      <c r="B29" s="2"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Training rows</t>
-        </is>
-      </c>
-      <c r="B30" s="6">
-        <v>1256</v>
-      </c>
+      <c r="B30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Training properties</t>
+          <t>Training rows</t>
         </is>
       </c>
       <c r="B31" s="6">
-        <v>67</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Grouped CV folds</t>
+          <t>Training properties</t>
         </is>
       </c>
       <c r="B32" s="6">
-        <v>5</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GBM mean log R2</t>
+          <t>Grouped CV folds</t>
         </is>
       </c>
       <c r="B33" s="6">
-        <v>-1.6276315989865757</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GBM mean log MAE</t>
+          <t>GBM mean log R2</t>
         </is>
       </c>
       <c r="B34" s="6">
-        <v>0.383152815729961</v>
+        <v>0.3108050369803198</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GBM mean EUR/night MAE</t>
-        </is>
-      </c>
-      <c r="B35" s="4">
-        <v>83.3125819910135</v>
+          <t>GBM mean log MAE</t>
+        </is>
+      </c>
+      <c r="B35" s="6">
+        <v>0.2851139151161721</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OLS R2</t>
-        </is>
-      </c>
-      <c r="B36" s="6">
-        <v>0.8668255626390471</v>
+          <t>GBM mean EUR/night MAE</t>
+        </is>
+      </c>
+      <c r="B36" s="4">
+        <v>53.32149472419017</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>OLS R2</t>
+        </is>
+      </c>
+      <c r="B37" s="6">
+        <v>0.6246570229449309</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>OLS condition number</t>
         </is>
       </c>
-      <c r="B37" s="6">
-        <v>1.1247963270357698e+16</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38"/>
-      <c r="B38" s="6"/>
+      <c r="B38" s="6">
+        <v>9.448097188104942e+16</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr" s="2">
+      <c r="A39"/>
+      <c r="B39" s="6"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr" s="2">
         <is>
           <t>Price Gap Decomposition</t>
         </is>
       </c>
-      <c r="B39" s="2"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Client observed price</t>
-        </is>
-      </c>
-      <c r="B40" s="4">
-        <v>117.86</v>
-      </c>
+      <c r="B40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Competitor observed price</t>
+          <t>Client observed price</t>
         </is>
       </c>
       <c r="B41" s="4">
-        <v>57.0</v>
+        <v>117.86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Observed gap</t>
+          <t>Competitor observed price</t>
         </is>
       </c>
       <c r="B42" s="4">
-        <v>60.86</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Feature-explained gap</t>
+          <t>Observed gap</t>
         </is>
       </c>
       <c r="B43" s="4">
-        <v>59.97577158285408</v>
+        <v>60.86</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Feature-explained gap</t>
+        </is>
+      </c>
+      <c r="B44" s="4">
+        <v>35.79981320938094</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>Residual gap</t>
         </is>
       </c>
-      <c r="B44" s="4">
-        <v>0.8842284171459198</v>
+      <c r="B45" s="4">
+        <v>25.060186790619056</v>
       </c>
     </row>
   </sheetData>
@@ -7310,16 +7322,16 @@
         <v>108.0</v>
       </c>
       <c r="K4" s="4">
-        <v>113.89000568434557</v>
+        <v>159.76552449754183</v>
       </c>
       <c r="L4" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M4" s="6">
-        <v>1.0777489841273864</v>
+        <v>0.8366202276729348</v>
       </c>
       <c r="N4" s="4">
-        <v>116.39689028575773</v>
+        <v>90.35498458867696</v>
       </c>
     </row>
     <row r="5">
@@ -7368,16 +7380,16 @@
         <v>108.0</v>
       </c>
       <c r="K5" s="4">
-        <v>114.88542199838649</v>
+        <v>159.76552449754183</v>
       </c>
       <c r="L5" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M5" s="6">
-        <v>1.0684109070887131</v>
+        <v>0.8366202276729348</v>
       </c>
       <c r="N5" s="4">
-        <v>115.38837796558101</v>
+        <v>90.35498458867696</v>
       </c>
     </row>
     <row r="6">
@@ -7426,16 +7438,16 @@
         <v>109.25</v>
       </c>
       <c r="K6" s="4">
-        <v>118.01807343709262</v>
+        <v>169.36024625036478</v>
       </c>
       <c r="L6" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M6" s="6">
-        <v>1.0412296785409456</v>
+        <v>0.8080410429188393</v>
       </c>
       <c r="N6" s="4">
-        <v>113.7543423805983</v>
+        <v>88.27848393888318</v>
       </c>
     </row>
     <row r="7">
@@ -7484,16 +7496,16 @@
         <v>98.0</v>
       </c>
       <c r="K7" s="4">
-        <v>104.65585606761886</v>
+        <v>161.09504804553345</v>
       </c>
       <c r="L7" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M7" s="6">
-        <v>1.1728425196699879</v>
+        <v>0.8297155691690751</v>
       </c>
       <c r="N7" s="4">
-        <v>114.93856692765881</v>
+        <v>81.31212577856935</v>
       </c>
     </row>
     <row r="8">
@@ -7542,16 +7554,16 @@
         <v>67.0</v>
       </c>
       <c r="K8" s="4">
-        <v>72.174717089582</v>
+        <v>80.91214979625612</v>
       </c>
       <c r="L8" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M8" s="6">
-        <v>1.7006625433143983</v>
+        <v>1.651953010963058</v>
       </c>
       <c r="N8" s="4">
-        <v>113.94439040206468</v>
+        <v>110.6808517345249</v>
       </c>
     </row>
     <row r="9">
@@ -7600,16 +7612,16 @@
         <v>67.0</v>
       </c>
       <c r="K9" s="4">
-        <v>72.04849027209481</v>
+        <v>80.91214979625612</v>
       </c>
       <c r="L9" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M9" s="6">
-        <v>1.7036420536365653</v>
+        <v>1.651953010963058</v>
       </c>
       <c r="N9" s="4">
-        <v>114.14401759364988</v>
+        <v>110.6808517345249</v>
       </c>
     </row>
     <row r="10">
@@ -7658,16 +7670,16 @@
         <v>397.0</v>
       </c>
       <c r="K10" s="4">
-        <v>323.69235948765885</v>
+        <v>264.0379161331309</v>
       </c>
       <c r="L10" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M10" s="6">
-        <v>0.37963182344318125</v>
+        <v>0.5182968871036494</v>
       </c>
       <c r="N10" s="4">
-        <v>150.71383390694297</v>
+        <v>205.7638641801488</v>
       </c>
     </row>
     <row r="11">
@@ -7716,16 +7728,16 @@
         <v>312.0</v>
       </c>
       <c r="K11" s="4">
-        <v>323.69235948765885</v>
+        <v>264.0379161331309</v>
       </c>
       <c r="L11" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M11" s="6">
-        <v>0.37963182344318125</v>
+        <v>0.5182968871036494</v>
       </c>
       <c r="N11" s="4">
-        <v>118.44512891427254</v>
+        <v>161.70862877633863</v>
       </c>
     </row>
     <row r="12">
@@ -7774,16 +7786,16 @@
         <v>359.0</v>
       </c>
       <c r="K12" s="4">
-        <v>309.1970711478095</v>
+        <v>247.28879874441662</v>
       </c>
       <c r="L12" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M12" s="6">
-        <v>0.3974291225034983</v>
+        <v>0.5534016530630507</v>
       </c>
       <c r="N12" s="4">
-        <v>142.6770549787559</v>
+        <v>198.67119344963518</v>
       </c>
     </row>
     <row r="13">
@@ -7832,16 +7844,16 @@
         <v>265.5</v>
       </c>
       <c r="K13" s="4">
-        <v>309.1970711478095</v>
+        <v>247.28879874441662</v>
       </c>
       <c r="L13" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M13" s="6">
-        <v>0.3974291225034983</v>
+        <v>0.5534016530630507</v>
       </c>
       <c r="N13" s="4">
-        <v>105.51743202467881</v>
+        <v>146.92813888823994</v>
       </c>
     </row>
     <row r="14">
@@ -7890,16 +7902,16 @@
         <v>94.0</v>
       </c>
       <c r="K14" s="4">
-        <v>96.03966857849892</v>
+        <v>112.22666603798459</v>
       </c>
       <c r="L14" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M14" s="6">
-        <v>1.2780639473806499</v>
+        <v>1.191009892730657</v>
       </c>
       <c r="N14" s="4">
-        <v>120.13801105378109</v>
+        <v>111.95492991668175</v>
       </c>
     </row>
     <row r="15">
@@ -7948,16 +7960,16 @@
         <v>84.75</v>
       </c>
       <c r="K15" s="4">
-        <v>94.15556545540535</v>
+        <v>112.22666603798459</v>
       </c>
       <c r="L15" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M15" s="6">
-        <v>1.3036386891723466</v>
+        <v>1.191009892730657</v>
       </c>
       <c r="N15" s="4">
-        <v>110.48337890735637</v>
+        <v>100.93808840892318</v>
       </c>
     </row>
     <row r="16">
@@ -8006,16 +8018,16 @@
         <v>105.5</v>
       </c>
       <c r="K16" s="4">
-        <v>97.4321138962438</v>
+        <v>110.00185161043224</v>
       </c>
       <c r="L16" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M16" s="6">
-        <v>1.259798571744811</v>
+        <v>1.215098359914726</v>
       </c>
       <c r="N16" s="4">
-        <v>132.90874931907757</v>
+        <v>128.19287697100359</v>
       </c>
     </row>
     <row r="17">
@@ -8064,16 +8076,16 @@
         <v>95.25</v>
       </c>
       <c r="K17" s="4">
-        <v>94.99389487743872</v>
+        <v>110.00185161043224</v>
       </c>
       <c r="L17" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M17" s="6">
-        <v>1.292133963839795</v>
+        <v>1.215098359914726</v>
       </c>
       <c r="N17" s="4">
-        <v>123.07576005574047</v>
+        <v>115.73811878187766</v>
       </c>
     </row>
     <row r="18">
@@ -8122,16 +8134,16 @@
         <v>94.0</v>
       </c>
       <c r="K18" s="4">
-        <v>95.26304885932275</v>
+        <v>113.57728926038003</v>
       </c>
       <c r="L18" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M18" s="6">
-        <v>1.2884831988720618</v>
+        <v>1.1768468005341444</v>
       </c>
       <c r="N18" s="4">
-        <v>121.1174206939738</v>
+        <v>110.62359925020957</v>
       </c>
     </row>
     <row r="19">
@@ -8180,16 +8192,16 @@
         <v>84.75</v>
       </c>
       <c r="K19" s="4">
-        <v>92.87911025602502</v>
+        <v>113.57728926038003</v>
       </c>
       <c r="L19" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M19" s="6">
-        <v>1.3215548425282564</v>
+        <v>1.1768468005341444</v>
       </c>
       <c r="N19" s="4">
-        <v>112.00177290426973</v>
+        <v>99.73776634526874</v>
       </c>
     </row>
     <row r="20">
@@ -8238,16 +8250,16 @@
         <v>94.0</v>
       </c>
       <c r="K20" s="4">
-        <v>96.03966857849892</v>
+        <v>112.22666603798459</v>
       </c>
       <c r="L20" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M20" s="6">
-        <v>1.2780639473806499</v>
+        <v>1.191009892730657</v>
       </c>
       <c r="N20" s="4">
-        <v>120.13801105378109</v>
+        <v>111.95492991668175</v>
       </c>
     </row>
     <row r="21">
@@ -8296,16 +8308,16 @@
         <v>84.86</v>
       </c>
       <c r="K21" s="4">
-        <v>94.15556545540535</v>
+        <v>112.22666603798459</v>
       </c>
       <c r="L21" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M21" s="6">
-        <v>1.3036386891723466</v>
+        <v>1.191009892730657</v>
       </c>
       <c r="N21" s="4">
-        <v>110.62677916316534</v>
+        <v>101.06909949712355</v>
       </c>
     </row>
     <row r="22">
@@ -8354,16 +8366,16 @@
         <v>105.57</v>
       </c>
       <c r="K22" s="4">
-        <v>97.4321138962438</v>
+        <v>110.00185161043224</v>
       </c>
       <c r="L22" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M22" s="6">
-        <v>1.259798571744811</v>
+        <v>1.215098359914726</v>
       </c>
       <c r="N22" s="4">
-        <v>132.9969352190997</v>
+        <v>128.27793385619762</v>
       </c>
     </row>
     <row r="23">
@@ -8412,16 +8424,16 @@
         <v>95.14</v>
       </c>
       <c r="K23" s="4">
-        <v>94.99389487743872</v>
+        <v>110.00185161043224</v>
       </c>
       <c r="L23" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M23" s="6">
-        <v>1.292133963839795</v>
+        <v>1.215098359914726</v>
       </c>
       <c r="N23" s="4">
-        <v>122.9336253197181</v>
+        <v>115.60445796228703</v>
       </c>
     </row>
     <row r="24">
@@ -8470,16 +8482,16 @@
         <v>94.0</v>
       </c>
       <c r="K24" s="4">
-        <v>95.26304885932275</v>
+        <v>113.57728926038003</v>
       </c>
       <c r="L24" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M24" s="6">
-        <v>1.2884831988720618</v>
+        <v>1.1768468005341444</v>
       </c>
       <c r="N24" s="4">
-        <v>121.1174206939738</v>
+        <v>110.62359925020957</v>
       </c>
     </row>
     <row r="25">
@@ -8528,16 +8540,16 @@
         <v>84.86</v>
       </c>
       <c r="K25" s="4">
-        <v>92.87911025602502</v>
+        <v>113.57728926038003</v>
       </c>
       <c r="L25" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M25" s="6">
-        <v>1.3215548425282564</v>
+        <v>1.1768468005341444</v>
       </c>
       <c r="N25" s="4">
-        <v>112.14714393694784</v>
+        <v>99.8672194933275</v>
       </c>
     </row>
     <row r="26">
@@ -8586,16 +8598,16 @@
         <v>94.0</v>
       </c>
       <c r="K26" s="4">
-        <v>96.03966857849892</v>
+        <v>115.58397887994236</v>
       </c>
       <c r="L26" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M26" s="6">
-        <v>1.279512127496414</v>
+        <v>1.1839878790752045</v>
       </c>
       <c r="N26" s="4">
-        <v>120.27413998466292</v>
+        <v>111.29486063306922</v>
       </c>
     </row>
     <row r="27">
@@ -8644,16 +8656,16 @@
         <v>84.75</v>
       </c>
       <c r="K27" s="4">
-        <v>94.26225355810983</v>
+        <v>115.58397887994236</v>
       </c>
       <c r="L27" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M27" s="6">
-        <v>1.3036386891723466</v>
+        <v>1.1839878790752045</v>
       </c>
       <c r="N27" s="4">
-        <v>110.48337890735637</v>
+        <v>100.34297275162358</v>
       </c>
     </row>
     <row r="28">
@@ -8702,16 +8714,16 @@
         <v>105.5</v>
       </c>
       <c r="K28" s="4">
-        <v>97.60366316364556</v>
+        <v>114.53332534144914</v>
       </c>
       <c r="L28" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M28" s="6">
-        <v>1.2590093105511253</v>
+        <v>1.1948490066201782</v>
       </c>
       <c r="N28" s="4">
-        <v>132.82548226314373</v>
+        <v>126.0565701984288</v>
       </c>
     </row>
     <row r="29">
@@ -8760,16 +8772,16 @@
         <v>95.25</v>
       </c>
       <c r="K29" s="4">
-        <v>95.26897869546248</v>
+        <v>114.53332534144914</v>
       </c>
       <c r="L29" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M29" s="6">
-        <v>1.289862895032572</v>
+        <v>1.1948490066201782</v>
       </c>
       <c r="N29" s="4">
-        <v>122.85944075185247</v>
+        <v>113.80936788057198</v>
       </c>
     </row>
     <row r="30">
@@ -8818,16 +8830,16 @@
         <v>94.0</v>
       </c>
       <c r="K30" s="4">
-        <v>96.03966857849892</v>
+        <v>115.58397887994236</v>
       </c>
       <c r="L30" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M30" s="6">
-        <v>1.279512127496414</v>
+        <v>1.1839878790752045</v>
       </c>
       <c r="N30" s="4">
-        <v>120.27413998466292</v>
+        <v>111.29486063306922</v>
       </c>
     </row>
     <row r="31">
@@ -8876,16 +8888,16 @@
         <v>84.86</v>
       </c>
       <c r="K31" s="4">
-        <v>94.26225355810983</v>
+        <v>115.58397887994236</v>
       </c>
       <c r="L31" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M31" s="6">
-        <v>1.3036386891723466</v>
+        <v>1.1839878790752045</v>
       </c>
       <c r="N31" s="4">
-        <v>110.62677916316534</v>
+        <v>100.47321141832185</v>
       </c>
     </row>
     <row r="32">
@@ -8934,16 +8946,16 @@
         <v>105.57</v>
       </c>
       <c r="K32" s="4">
-        <v>97.60366316364556</v>
+        <v>114.53332534144914</v>
       </c>
       <c r="L32" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M32" s="6">
-        <v>1.2590093105511253</v>
+        <v>1.1948490066201782</v>
       </c>
       <c r="N32" s="4">
-        <v>132.9136129148823</v>
+        <v>126.14020962889221</v>
       </c>
     </row>
     <row r="33">
@@ -8992,16 +9004,16 @@
         <v>95.14</v>
       </c>
       <c r="K33" s="4">
-        <v>95.26897869546248</v>
+        <v>114.53332534144914</v>
       </c>
       <c r="L33" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M33" s="6">
-        <v>1.289862895032572</v>
+        <v>1.1948490066201782</v>
       </c>
       <c r="N33" s="4">
-        <v>122.71755583339889</v>
+        <v>113.67793448984376</v>
       </c>
     </row>
     <row r="34">
@@ -9050,16 +9062,16 @@
         <v>78.25</v>
       </c>
       <c r="K34" s="4">
-        <v>93.96918490138768</v>
+        <v>137.07818020641773</v>
       </c>
       <c r="L34" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M34" s="6">
-        <v>1.306224354902892</v>
+        <v>0.9750864016296696</v>
       </c>
       <c r="N34" s="4">
-        <v>102.2120557711513</v>
+        <v>76.30051092752164</v>
       </c>
     </row>
     <row r="35">
@@ -9108,16 +9120,16 @@
         <v>162.0</v>
       </c>
       <c r="K35" s="4">
-        <v>140.0016160383906</v>
+        <v>169.49337450969628</v>
       </c>
       <c r="L35" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M35" s="6">
-        <v>0.8777321587004324</v>
+        <v>0.8074063685675652</v>
       </c>
       <c r="N35" s="4">
-        <v>142.19260970947005</v>
+        <v>130.79983170794557</v>
       </c>
     </row>
     <row r="36">
@@ -9166,16 +9178,16 @@
         <v>162.0</v>
       </c>
       <c r="K36" s="4">
-        <v>139.756766329958</v>
+        <v>169.49337450969628</v>
       </c>
       <c r="L36" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M36" s="6">
-        <v>0.8792699194027109</v>
+        <v>0.8074063685675652</v>
       </c>
       <c r="N36" s="4">
-        <v>142.44172694323916</v>
+        <v>130.79983170794557</v>
       </c>
     </row>
     <row r="37">
@@ -9224,16 +9236,16 @@
         <v>57.0</v>
       </c>
       <c r="K37" s="4">
-        <v>62.76906634571162</v>
+        <v>97.86325627003833</v>
       </c>
       <c r="L37" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M37" s="6">
-        <v>1.955498863923306</v>
+        <v>1.365814653771554</v>
       </c>
       <c r="N37" s="4">
-        <v>111.46343524362844</v>
+        <v>77.85143526497858</v>
       </c>
     </row>
     <row r="38">
@@ -9282,16 +9294,16 @@
         <v>57.0</v>
       </c>
       <c r="K38" s="4">
-        <v>62.76906634571162</v>
+        <v>97.86325627003833</v>
       </c>
       <c r="L38" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M38" s="6">
-        <v>1.955498863923306</v>
+        <v>1.365814653771554</v>
       </c>
       <c r="N38" s="4">
-        <v>111.46343524362844</v>
+        <v>77.85143526497858</v>
       </c>
     </row>
     <row r="39">
@@ -9340,16 +9352,16 @@
         <v>104.5</v>
       </c>
       <c r="K39" s="4">
-        <v>116.87592762370659</v>
+        <v>138.65658333877644</v>
       </c>
       <c r="L39" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M39" s="6">
-        <v>1.0514048800755824</v>
+        <v>0.9869710237614442</v>
       </c>
       <c r="N39" s="4">
-        <v>109.87180996789836</v>
+        <v>103.13847198307091</v>
       </c>
     </row>
     <row r="40">
@@ -9398,16 +9410,16 @@
         <v>292.0</v>
       </c>
       <c r="K40" s="4">
-        <v>238.68141028008677</v>
+        <v>193.5507743994551</v>
       </c>
       <c r="L40" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M40" s="6">
-        <v>0.5142622451598876</v>
+        <v>0.6905840077062259</v>
       </c>
       <c r="N40" s="4">
-        <v>150.1645755866872</v>
+        <v>201.65053025021794</v>
       </c>
     </row>
     <row r="41">
@@ -9456,16 +9468,16 @@
         <v>237.0</v>
       </c>
       <c r="K41" s="4">
-        <v>238.68141028008677</v>
+        <v>193.5507743994551</v>
       </c>
       <c r="L41" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M41" s="6">
-        <v>0.5142622451598876</v>
+        <v>0.6905840077062259</v>
       </c>
       <c r="N41" s="4">
-        <v>121.88015210289336</v>
+        <v>163.66840982637552</v>
       </c>
     </row>
     <row r="42">
@@ -9514,16 +9526,16 @@
         <v>148.25</v>
       </c>
       <c r="K42" s="4">
-        <v>142.4737245110662</v>
+        <v>144.5534797662274</v>
       </c>
       <c r="L42" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M42" s="6">
-        <v>0.8625023392111929</v>
+        <v>0.946708652261092</v>
       </c>
       <c r="N42" s="4">
-        <v>127.86597178805935</v>
+        <v>140.3495576977069</v>
       </c>
     </row>
     <row r="43">
@@ -9572,16 +9584,16 @@
         <v>155.5</v>
       </c>
       <c r="K43" s="4">
-        <v>142.4737245110662</v>
+        <v>144.5534797662274</v>
       </c>
       <c r="L43" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M43" s="6">
-        <v>0.8625023392111929</v>
+        <v>0.946708652261092</v>
       </c>
       <c r="N43" s="4">
-        <v>134.1191137473405</v>
+        <v>147.2131954265998</v>
       </c>
     </row>
     <row r="44">
@@ -9630,16 +9642,16 @@
         <v>126.25</v>
       </c>
       <c r="K44" s="4">
-        <v>134.97903810085595</v>
+        <v>135.96498312721945</v>
       </c>
       <c r="L44" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M44" s="6">
-        <v>0.9103926238910307</v>
+        <v>1.0065093736751958</v>
       </c>
       <c r="N44" s="4">
-        <v>114.93706876624263</v>
+        <v>127.07180842649346</v>
       </c>
     </row>
     <row r="45">
@@ -9688,16 +9700,16 @@
         <v>148.14</v>
       </c>
       <c r="K45" s="4">
-        <v>141.90927719537683</v>
+        <v>144.5534797662274</v>
       </c>
       <c r="L45" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M45" s="6">
-        <v>0.865932961505698</v>
+        <v>0.946708652261092</v>
       </c>
       <c r="N45" s="4">
-        <v>128.27930891745407</v>
+        <v>140.24541974595815</v>
       </c>
     </row>
     <row r="46">
@@ -9746,16 +9758,16 @@
         <v>155.57</v>
       </c>
       <c r="K46" s="4">
-        <v>141.90927719537683</v>
+        <v>144.5534797662274</v>
       </c>
       <c r="L46" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M46" s="6">
-        <v>0.865932961505698</v>
+        <v>0.946708652261092</v>
       </c>
       <c r="N46" s="4">
-        <v>134.71319082144143</v>
+        <v>147.2794650322581</v>
       </c>
     </row>
     <row r="47">
@@ -9804,16 +9816,16 @@
         <v>126.29</v>
       </c>
       <c r="K47" s="4">
-        <v>134.97903810085595</v>
+        <v>135.96498312721945</v>
       </c>
       <c r="L47" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M47" s="6">
-        <v>0.9103926238910307</v>
+        <v>1.0065093736751958</v>
       </c>
       <c r="N47" s="4">
-        <v>114.97348447119828</v>
+        <v>127.11206880144049</v>
       </c>
     </row>
     <row r="48">
@@ -9862,16 +9874,16 @@
         <v>96.5</v>
       </c>
       <c r="K48" s="4">
-        <v>105.66355841979203</v>
+        <v>141.03401096560432</v>
       </c>
       <c r="L48" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M48" s="6">
-        <v>1.1629735218524313</v>
+        <v>0.9703335321187984</v>
       </c>
       <c r="N48" s="4">
-        <v>112.22694485875962</v>
+        <v>93.63718584946405</v>
       </c>
     </row>
     <row r="49">
@@ -9920,16 +9932,16 @@
         <v>99.5</v>
       </c>
       <c r="K49" s="4">
-        <v>105.85735190575747</v>
+        <v>141.03401096560432</v>
       </c>
       <c r="L49" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M49" s="6">
-        <v>1.160844461481774</v>
+        <v>0.9703335321187984</v>
       </c>
       <c r="N49" s="4">
-        <v>115.5040239174365</v>
+        <v>96.54818644582043</v>
       </c>
     </row>
     <row r="50">
@@ -9978,16 +9990,16 @@
         <v>100.43</v>
       </c>
       <c r="K50" s="4">
-        <v>105.66355841979203</v>
+        <v>141.03401096560432</v>
       </c>
       <c r="L50" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M50" s="6">
-        <v>1.1629735218524313</v>
+        <v>0.9703335321187984</v>
       </c>
       <c r="N50" s="4">
-        <v>116.79743079963968</v>
+        <v>97.45059663069092</v>
       </c>
     </row>
     <row r="51">
@@ -10036,16 +10048,16 @@
         <v>103.43</v>
       </c>
       <c r="K51" s="4">
-        <v>105.85735190575747</v>
+        <v>141.03401096560432</v>
       </c>
       <c r="L51" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M51" s="6">
-        <v>1.160844461481774</v>
+        <v>0.9703335321187984</v>
       </c>
       <c r="N51" s="4">
-        <v>120.06614265105988</v>
+        <v>100.36159722704733</v>
       </c>
     </row>
     <row r="52">
@@ -10094,16 +10106,16 @@
         <v>127.5</v>
       </c>
       <c r="K52" s="4">
-        <v>140.63790213457088</v>
+        <v>199.10000053971513</v>
       </c>
       <c r="L52" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M52" s="6">
-        <v>0.8727721052829414</v>
+        <v>0.6713363592018528</v>
       </c>
       <c r="N52" s="4">
-        <v>111.27844342357503</v>
+        <v>85.59538579823622</v>
       </c>
     </row>
     <row r="53">
@@ -10152,16 +10164,16 @@
         <v>114.0</v>
       </c>
       <c r="K53" s="4">
-        <v>140.17026592564633</v>
+        <v>197.9361580715072</v>
       </c>
       <c r="L53" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M53" s="6">
-        <v>0.875683848625043</v>
+        <v>0.6752837418978882</v>
       </c>
       <c r="N53" s="4">
-        <v>99.8279587432549</v>
+        <v>76.98234657635925</v>
       </c>
     </row>
     <row r="54">
@@ -10210,16 +10222,16 @@
         <v>141.0</v>
       </c>
       <c r="K54" s="4">
-        <v>140.63790213457088</v>
+        <v>199.10000053971513</v>
       </c>
       <c r="L54" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M54" s="6">
-        <v>0.8727721052829414</v>
+        <v>0.6713363592018528</v>
       </c>
       <c r="N54" s="4">
-        <v>123.06086684489473</v>
+        <v>94.65842664746124</v>
       </c>
     </row>
     <row r="55">
@@ -10268,16 +10280,16 @@
         <v>161.0</v>
       </c>
       <c r="K55" s="4">
-        <v>152.7041136628763</v>
+        <v>221.41082210362913</v>
       </c>
       <c r="L55" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M55" s="6">
-        <v>0.8047191245824298</v>
+        <v>0.6180819379510045</v>
       </c>
       <c r="N55" s="4">
-        <v>129.55977905777118</v>
+        <v>99.51119201011173</v>
       </c>
     </row>
     <row r="56">
@@ -10326,16 +10338,16 @@
         <v>147.5</v>
       </c>
       <c r="K56" s="4">
-        <v>152.19635599786105</v>
+        <v>220.11656134528408</v>
       </c>
       <c r="L56" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M56" s="6">
-        <v>0.8074038294888787</v>
+        <v>0.6217161906071551</v>
       </c>
       <c r="N56" s="4">
-        <v>119.0920648496096</v>
+        <v>91.70313811455537</v>
       </c>
     </row>
     <row r="57">
@@ -10384,16 +10396,16 @@
         <v>174.5</v>
       </c>
       <c r="K57" s="4">
-        <v>152.7041136628763</v>
+        <v>221.41082210362913</v>
       </c>
       <c r="L57" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M57" s="6">
-        <v>0.8047191245824298</v>
+        <v>0.6180819379510045</v>
       </c>
       <c r="N57" s="4">
-        <v>140.423487239634</v>
+        <v>107.85529817245029</v>
       </c>
     </row>
     <row r="58">
@@ -10442,16 +10454,16 @@
         <v>174.25</v>
       </c>
       <c r="K58" s="4">
-        <v>166.57212208415493</v>
+        <v>165.15338178273944</v>
       </c>
       <c r="L58" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M58" s="6">
-        <v>0.7368870396365187</v>
+        <v>0.8093268695839003</v>
       </c>
       <c r="N58" s="4">
-        <v>128.4025666566634</v>
+        <v>141.02520702499464</v>
       </c>
     </row>
     <row r="59">
@@ -10500,16 +10512,16 @@
         <v>193.25</v>
       </c>
       <c r="K59" s="4">
-        <v>166.57212208415493</v>
+        <v>165.15338178273944</v>
       </c>
       <c r="L59" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M59" s="6">
-        <v>0.7368870396365187</v>
+        <v>0.8093268695839003</v>
       </c>
       <c r="N59" s="4">
-        <v>142.40342040975725</v>
+        <v>156.40241754708873</v>
       </c>
     </row>
     <row r="60">
@@ -10558,16 +10570,16 @@
         <v>93.75</v>
       </c>
       <c r="K60" s="4">
-        <v>109.09371084818066</v>
+        <v>146.02245920024416</v>
       </c>
       <c r="L60" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M60" s="6">
-        <v>1.1264070101890293</v>
+        <v>0.9371848053967535</v>
       </c>
       <c r="N60" s="4">
-        <v>105.6006572052215</v>
+        <v>87.86107550594565</v>
       </c>
     </row>
     <row r="61">
@@ -10616,16 +10628,16 @@
         <v>105.0</v>
       </c>
       <c r="K61" s="4">
-        <v>108.66150727900911</v>
+        <v>146.02245920024416</v>
       </c>
       <c r="L61" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M61" s="6">
-        <v>1.1308873191994089</v>
+        <v>0.9371848053967535</v>
       </c>
       <c r="N61" s="4">
-        <v>118.74316851593794</v>
+        <v>98.40440456665912</v>
       </c>
     </row>
     <row r="62">
@@ -10674,16 +10686,16 @@
         <v>98.5</v>
       </c>
       <c r="K62" s="4">
-        <v>108.14636321883161</v>
+        <v>128.95914476387685</v>
       </c>
       <c r="L62" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M62" s="6">
-        <v>1.134988124197893</v>
+        <v>1.036476084919416</v>
       </c>
       <c r="N62" s="4">
-        <v>111.79633023349245</v>
+        <v>102.09289436456247</v>
       </c>
     </row>
     <row r="63">
@@ -10732,16 +10744,16 @@
         <v>103.75</v>
       </c>
       <c r="K63" s="4">
-        <v>114.83344650851977</v>
+        <v>143.14777553222757</v>
       </c>
       <c r="L63" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M63" s="6">
-        <v>1.0701056565241087</v>
+        <v>0.9560052854494163</v>
       </c>
       <c r="N63" s="4">
-        <v>111.02346186437627</v>
+        <v>99.18554836537695</v>
       </c>
     </row>
     <row r="64">
@@ -10790,16 +10802,16 @@
         <v>268.5</v>
       </c>
       <c r="K64" s="4">
-        <v>247.72251424661061</v>
+        <v>177.3028997780227</v>
       </c>
       <c r="L64" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M64" s="6">
-        <v>0.49605471283321995</v>
+        <v>0.7718431575595653</v>
       </c>
       <c r="N64" s="4">
-        <v>133.19069039571954</v>
+        <v>207.2398878047433</v>
       </c>
     </row>
     <row r="65">
@@ -10848,16 +10860,16 @@
         <v>269.5</v>
       </c>
       <c r="K65" s="4">
-        <v>247.72251424661061</v>
+        <v>177.3028997780227</v>
       </c>
       <c r="L65" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M65" s="6">
-        <v>0.49605471283321995</v>
+        <v>0.7718431575595653</v>
       </c>
       <c r="N65" s="4">
-        <v>133.68674510855277</v>
+        <v>208.01173096230286</v>
       </c>
     </row>
     <row r="66">
@@ -10906,16 +10918,16 @@
         <v>213.25</v>
       </c>
       <c r="K66" s="4">
-        <v>232.09214493713023</v>
+        <v>166.4658778765534</v>
       </c>
       <c r="L66" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M66" s="6">
-        <v>0.5294617820875102</v>
+        <v>0.822090579491735</v>
       </c>
       <c r="N66" s="4">
-        <v>112.90772503016154</v>
+        <v>175.3108160766125</v>
       </c>
     </row>
     <row r="67">
@@ -10964,16 +10976,16 @@
         <v>214.0</v>
       </c>
       <c r="K67" s="4">
-        <v>232.09214493713023</v>
+        <v>166.4658778765534</v>
       </c>
       <c r="L67" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M67" s="6">
-        <v>0.5294617820875102</v>
+        <v>0.822090579491735</v>
       </c>
       <c r="N67" s="4">
-        <v>113.30482136672717</v>
+        <v>175.92738401123128</v>
       </c>
     </row>
     <row r="68">
@@ -11022,16 +11034,16 @@
         <v>271.14</v>
       </c>
       <c r="K68" s="4">
-        <v>247.28927078055773</v>
+        <v>177.3028997780227</v>
       </c>
       <c r="L68" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M68" s="6">
-        <v>0.4969237859736007</v>
+        <v>0.7718431575595653</v>
       </c>
       <c r="N68" s="4">
-        <v>134.7359153288821</v>
+        <v>209.27755374070054</v>
       </c>
     </row>
     <row r="69">
@@ -11080,16 +11092,16 @@
         <v>272.29</v>
       </c>
       <c r="K69" s="4">
-        <v>247.28927078055773</v>
+        <v>177.3028997780227</v>
       </c>
       <c r="L69" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M69" s="6">
-        <v>0.4969237859736007</v>
+        <v>0.7718431575595653</v>
       </c>
       <c r="N69" s="4">
-        <v>135.30737768275173</v>
+        <v>210.16517337189407</v>
       </c>
     </row>
     <row r="70">
@@ -11138,16 +11150,16 @@
         <v>253.57</v>
       </c>
       <c r="K70" s="4">
-        <v>236.34612724541662</v>
+        <v>166.4658778765534</v>
       </c>
       <c r="L70" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M70" s="6">
-        <v>0.5199320255386529</v>
+        <v>0.822090579491735</v>
       </c>
       <c r="N70" s="4">
-        <v>131.8391637158362</v>
+        <v>208.45750824171924</v>
       </c>
     </row>
     <row r="71">
@@ -11196,16 +11208,16 @@
         <v>254.57</v>
       </c>
       <c r="K71" s="4">
-        <v>236.34612724541662</v>
+        <v>166.4658778765534</v>
       </c>
       <c r="L71" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M71" s="6">
-        <v>0.5199320255386529</v>
+        <v>0.822090579491735</v>
       </c>
       <c r="N71" s="4">
-        <v>132.35909574137486</v>
+        <v>209.27959882121098</v>
       </c>
     </row>
     <row r="72">
@@ -11254,16 +11266,16 @@
         <v>215.43</v>
       </c>
       <c r="K72" s="4">
-        <v>232.09214493713023</v>
+        <v>166.4658778765534</v>
       </c>
       <c r="L72" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M72" s="6">
-        <v>0.5294617820875102</v>
+        <v>0.822090579491735</v>
       </c>
       <c r="N72" s="4">
-        <v>114.06195171511231</v>
+        <v>177.1029735399045</v>
       </c>
     </row>
     <row r="73">
@@ -11312,16 +11324,16 @@
         <v>216.29</v>
       </c>
       <c r="K73" s="4">
-        <v>232.09214493713023</v>
+        <v>166.4658778765534</v>
       </c>
       <c r="L73" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M73" s="6">
-        <v>0.5294617820875102</v>
+        <v>0.822090579491735</v>
       </c>
       <c r="N73" s="4">
-        <v>114.51728884770756</v>
+        <v>177.80997143826735</v>
       </c>
     </row>
     <row r="74">
@@ -11370,16 +11382,16 @@
         <v>145.25</v>
       </c>
       <c r="K74" s="4">
-        <v>153.74316538311908</v>
+        <v>170.06009663053555</v>
       </c>
       <c r="L74" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M74" s="6">
-        <v>0.7983758993298509</v>
+        <v>0.7859755000010924</v>
       </c>
       <c r="N74" s="4">
-        <v>115.96409937766084</v>
+        <v>114.16294137515867</v>
       </c>
     </row>
     <row r="75">
@@ -11428,16 +11440,16 @@
         <v>184.75</v>
       </c>
       <c r="K75" s="4">
-        <v>166.4951347878498</v>
+        <v>185.3932137216464</v>
       </c>
       <c r="L75" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M75" s="6">
-        <v>0.7372277759645574</v>
+        <v>0.720970669833169</v>
       </c>
       <c r="N75" s="4">
-        <v>136.20283160945198</v>
+        <v>133.199331251678</v>
       </c>
     </row>
     <row r="76">
@@ -11486,16 +11498,16 @@
         <v>161.0</v>
       </c>
       <c r="K76" s="4">
-        <v>153.74316538311908</v>
+        <v>170.06009663053555</v>
       </c>
       <c r="L76" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M76" s="6">
-        <v>0.7983758993298509</v>
+        <v>0.7859755000010924</v>
       </c>
       <c r="N76" s="4">
-        <v>128.538519792106</v>
+        <v>126.54205550017588</v>
       </c>
     </row>
     <row r="77">
@@ -11544,16 +11556,16 @@
         <v>145.14</v>
       </c>
       <c r="K77" s="4">
-        <v>153.74316538311908</v>
+        <v>170.06009663053555</v>
       </c>
       <c r="L77" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M77" s="6">
-        <v>0.7983758993298509</v>
+        <v>0.7859755000010924</v>
       </c>
       <c r="N77" s="4">
-        <v>115.87627802873455</v>
+        <v>114.07648407015854</v>
       </c>
     </row>
     <row r="78">
@@ -11602,16 +11614,16 @@
         <v>184.71</v>
       </c>
       <c r="K78" s="4">
-        <v>165.83552030645086</v>
+        <v>185.3932137216464</v>
       </c>
       <c r="L78" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M78" s="6">
-        <v>0.7401601158891834</v>
+        <v>0.720970669833169</v>
       </c>
       <c r="N78" s="4">
-        <v>136.71497500589106</v>
+        <v>133.17049242488466</v>
       </c>
     </row>
     <row r="79">
@@ -11660,16 +11672,16 @@
         <v>161.0</v>
       </c>
       <c r="K79" s="4">
-        <v>153.74316538311908</v>
+        <v>170.06009663053555</v>
       </c>
       <c r="L79" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M79" s="6">
-        <v>0.7983758993298509</v>
+        <v>0.7859755000010924</v>
       </c>
       <c r="N79" s="4">
-        <v>128.538519792106</v>
+        <v>126.54205550017588</v>
       </c>
     </row>
     <row r="80">
@@ -11718,16 +11730,16 @@
         <v>169.0</v>
       </c>
       <c r="K80" s="4">
-        <v>175.76549845944535</v>
+        <v>186.31710450169973</v>
       </c>
       <c r="L80" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M80" s="6">
-        <v>0.6991356195839473</v>
+        <v>0.7345006266340283</v>
       </c>
       <c r="N80" s="4">
-        <v>118.1539197096871</v>
+        <v>124.13060590115077</v>
       </c>
     </row>
     <row r="81">
@@ -11776,16 +11788,16 @@
         <v>215.25</v>
       </c>
       <c r="K81" s="4">
-        <v>189.4046710658608</v>
+        <v>203.11600110357506</v>
       </c>
       <c r="L81" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M81" s="6">
-        <v>0.6487903385666546</v>
+        <v>0.673753073443742</v>
       </c>
       <c r="N81" s="4">
-        <v>139.6521203764724</v>
+        <v>145.02534905876547</v>
       </c>
     </row>
     <row r="82">
@@ -11834,16 +11846,16 @@
         <v>187.5</v>
       </c>
       <c r="K82" s="4">
-        <v>189.4046710658608</v>
+        <v>203.11600110357506</v>
       </c>
       <c r="L82" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M82" s="6">
-        <v>0.6487903385666546</v>
+        <v>0.673753073443742</v>
       </c>
       <c r="N82" s="4">
-        <v>121.64818848124773</v>
+        <v>126.32870127070163</v>
       </c>
     </row>
     <row r="83">
@@ -11892,16 +11904,16 @@
         <v>127.5</v>
       </c>
       <c r="K83" s="4">
-        <v>152.97719997110767</v>
+        <v>207.3118842825195</v>
       </c>
       <c r="L83" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M83" s="6">
-        <v>0.8032825851835069</v>
+        <v>0.6601166666482099</v>
       </c>
       <c r="N83" s="4">
-        <v>102.41852961089714</v>
+        <v>84.16487499764676</v>
       </c>
     </row>
     <row r="84">
@@ -11950,16 +11962,16 @@
         <v>162.25</v>
       </c>
       <c r="K84" s="4">
-        <v>165.66563765737328</v>
+        <v>225.19267012523204</v>
       </c>
       <c r="L84" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M84" s="6">
-        <v>0.7417586555944209</v>
+        <v>0.6077019733059359</v>
       </c>
       <c r="N84" s="4">
-        <v>120.3503418701948</v>
+        <v>98.5996451688881</v>
       </c>
     </row>
     <row r="85">
@@ -12008,16 +12020,16 @@
         <v>141.25</v>
       </c>
       <c r="K85" s="4">
-        <v>165.66563765737328</v>
+        <v>225.19267012523204</v>
       </c>
       <c r="L85" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M85" s="6">
-        <v>0.7417586555944209</v>
+        <v>0.6077019733059359</v>
       </c>
       <c r="N85" s="4">
-        <v>104.77341010271195</v>
+        <v>85.83790372946345</v>
       </c>
     </row>
     <row r="86">
@@ -12066,16 +12078,16 @@
         <v>169.14</v>
       </c>
       <c r="K86" s="4">
-        <v>175.76549845944535</v>
+        <v>186.31710450169973</v>
       </c>
       <c r="L86" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M86" s="6">
-        <v>0.6991356195839473</v>
+        <v>0.7345006266340283</v>
       </c>
       <c r="N86" s="4">
-        <v>118.25179869642884</v>
+        <v>124.23343598887953</v>
       </c>
     </row>
     <row r="87">
@@ -12124,16 +12136,16 @@
         <v>215.29</v>
       </c>
       <c r="K87" s="4">
-        <v>188.65429440146858</v>
+        <v>203.11600110357506</v>
       </c>
       <c r="L87" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M87" s="6">
-        <v>0.6513709166112102</v>
+        <v>0.673753073443742</v>
       </c>
       <c r="N87" s="4">
-        <v>140.23364463722743</v>
+        <v>145.0522991817032</v>
       </c>
     </row>
     <row r="88">
@@ -12182,16 +12194,16 @@
         <v>187.57</v>
       </c>
       <c r="K88" s="4">
-        <v>188.65429440146858</v>
+        <v>203.11600110357506</v>
       </c>
       <c r="L88" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M88" s="6">
-        <v>0.6513709166112102</v>
+        <v>0.673753073443742</v>
       </c>
       <c r="N88" s="4">
-        <v>122.17764282876469</v>
+        <v>126.37586398584268</v>
       </c>
     </row>
     <row r="89">
@@ -12240,16 +12252,16 @@
         <v>83.0</v>
       </c>
       <c r="K89" s="4">
-        <v>91.60017368131598</v>
+        <v>140.1205598713433</v>
       </c>
       <c r="L89" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M89" s="6">
-        <v>1.3400066069263623</v>
+        <v>0.9539147545666875</v>
       </c>
       <c r="N89" s="4">
-        <v>111.22054837488807</v>
+        <v>79.17492462903506</v>
       </c>
     </row>
     <row r="90">
@@ -12298,16 +12310,16 @@
         <v>83.0</v>
       </c>
       <c r="K90" s="4">
-        <v>91.60017368131598</v>
+        <v>140.1205598713433</v>
       </c>
       <c r="L90" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M90" s="6">
-        <v>1.3400066069263623</v>
+        <v>0.9539147545666875</v>
       </c>
       <c r="N90" s="4">
-        <v>111.22054837488807</v>
+        <v>79.17492462903506</v>
       </c>
     </row>
     <row r="91">
@@ -12356,16 +12368,16 @@
         <v>92.0</v>
       </c>
       <c r="K91" s="4">
-        <v>92.66534141137483</v>
+        <v>144.1490568315369</v>
       </c>
       <c r="L91" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M91" s="6">
-        <v>1.3246035255366637</v>
+        <v>0.9272559419908497</v>
       </c>
       <c r="N91" s="4">
-        <v>121.86352434937307</v>
+        <v>85.30754666315818</v>
       </c>
     </row>
     <row r="92">
@@ -12414,16 +12426,16 @@
         <v>92.0</v>
       </c>
       <c r="K92" s="4">
-        <v>92.66534141137483</v>
+        <v>144.1490568315369</v>
       </c>
       <c r="L92" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M92" s="6">
-        <v>1.3246035255366637</v>
+        <v>0.9272559419908497</v>
       </c>
       <c r="N92" s="4">
-        <v>121.86352434937307</v>
+        <v>85.30754666315818</v>
       </c>
     </row>
     <row r="93">
@@ -12472,16 +12484,16 @@
         <v>92.0</v>
       </c>
       <c r="K93" s="4">
-        <v>97.58237466892555</v>
+        <v>156.52756401825053</v>
       </c>
       <c r="L93" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M93" s="6">
-        <v>1.2592839750399847</v>
+        <v>0.874287099958829</v>
       </c>
       <c r="N93" s="4">
-        <v>115.85412570367859</v>
+        <v>80.43441319621228</v>
       </c>
     </row>
     <row r="94">
@@ -12530,16 +12542,16 @@
         <v>104.5</v>
       </c>
       <c r="K94" s="4">
-        <v>102.0776915134187</v>
+        <v>155.1174166681702</v>
       </c>
       <c r="L94" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M94" s="6">
-        <v>1.203827387209005</v>
+        <v>0.882235102599008</v>
       </c>
       <c r="N94" s="4">
-        <v>125.79996196334103</v>
+        <v>92.19356822159634</v>
       </c>
     </row>
     <row r="95">
@@ -12588,16 +12600,16 @@
         <v>92.0</v>
       </c>
       <c r="K95" s="4">
-        <v>97.19577630049312</v>
+        <v>156.52756401825053</v>
       </c>
       <c r="L95" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M95" s="6">
-        <v>1.2642928051422149</v>
+        <v>0.874287099958829</v>
       </c>
       <c r="N95" s="4">
-        <v>116.31493807308377</v>
+        <v>80.43441319621228</v>
       </c>
     </row>
     <row r="96">
@@ -12646,16 +12658,16 @@
         <v>107.71</v>
       </c>
       <c r="K96" s="4">
-        <v>101.67328375918721</v>
+        <v>155.1174166681702</v>
       </c>
       <c r="L96" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M96" s="6">
-        <v>1.2086156374960384</v>
+        <v>0.882235102599008</v>
       </c>
       <c r="N96" s="4">
-        <v>130.1799903146983</v>
+        <v>95.02554290093914</v>
       </c>
     </row>
     <row r="97">
@@ -12704,16 +12716,16 @@
         <v>112.0</v>
       </c>
       <c r="K97" s="4">
-        <v>106.23382292548273</v>
+        <v>128.66089802326437</v>
       </c>
       <c r="L97" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M97" s="6">
-        <v>1.1554214519293404</v>
+        <v>1.0388787233184895</v>
       </c>
       <c r="N97" s="4">
-        <v>129.40720261608612</v>
+        <v>116.35441701167082</v>
       </c>
     </row>
     <row r="98">
@@ -12762,16 +12774,16 @@
         <v>134.0</v>
       </c>
       <c r="K98" s="4">
-        <v>133.31119012106313</v>
+        <v>141.23577148513135</v>
       </c>
       <c r="L98" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M98" s="6">
-        <v>0.9207391953901104</v>
+        <v>0.9463825493634996</v>
       </c>
       <c r="N98" s="4">
-        <v>123.37905218227479</v>
+        <v>126.81526161470894</v>
       </c>
     </row>
     <row r="99">
@@ -12820,16 +12832,16 @@
         <v>114.43</v>
       </c>
       <c r="K99" s="4">
-        <v>106.23382292548273</v>
+        <v>128.66089802326437</v>
       </c>
       <c r="L99" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M99" s="6">
-        <v>1.1554214519293404</v>
+        <v>1.0388787233184895</v>
       </c>
       <c r="N99" s="4">
-        <v>132.21487674427442</v>
+        <v>118.87889230933476</v>
       </c>
     </row>
     <row r="100">
@@ -12878,16 +12890,16 @@
         <v>134.0</v>
       </c>
       <c r="K100" s="4">
-        <v>133.31119012106313</v>
+        <v>141.23577148513135</v>
       </c>
       <c r="L100" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
       <c r="M100" s="6">
-        <v>0.9207391953901104</v>
+        <v>0.9463825493634996</v>
       </c>
       <c r="N100" s="4">
-        <v>123.37905218227479</v>
+        <v>126.81526161470894</v>
       </c>
     </row>
     <row r="101">
@@ -12936,16 +12948,16 @@
         <v>119.0</v>
       </c>
       <c r="K101" s="4">
-        <v>111.47285229808246</v>
+        <v>145.38258184831957</v>
       </c>
       <c r="L101" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M101" s="6">
-        <v>1.1023663442138323</v>
+        <v>0.9413096690765503</v>
       </c>
       <c r="N101" s="4">
-        <v>131.18159496144605</v>
+        <v>112.01585062010949</v>
       </c>
     </row>
     <row r="102">
@@ -12994,16 +13006,16 @@
         <v>107.25</v>
       </c>
       <c r="K102" s="4">
-        <v>105.90433306375704</v>
+        <v>132.3222914049477</v>
       </c>
       <c r="L102" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M102" s="6">
-        <v>1.1603294890016114</v>
+        <v>1.0342175045195687</v>
       </c>
       <c r="N102" s="4">
-        <v>124.44533769542282</v>
+        <v>110.91982735972374</v>
       </c>
     </row>
     <row r="103">
@@ -13052,16 +13064,16 @@
         <v>136.75</v>
       </c>
       <c r="K103" s="4">
-        <v>140.80796531259895</v>
+        <v>162.08574359104642</v>
       </c>
       <c r="L103" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M103" s="6">
-        <v>0.8727057478184473</v>
+        <v>0.8443063959679162</v>
       </c>
       <c r="N103" s="4">
-        <v>119.34251101417267</v>
+        <v>115.45889964861254</v>
       </c>
     </row>
     <row r="104">
@@ -13110,16 +13122,16 @@
         <v>123.25</v>
       </c>
       <c r="K104" s="4">
-        <v>133.39983923298843</v>
+        <v>147.5249422824168</v>
       </c>
       <c r="L104" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M104" s="6">
-        <v>0.9211699307395995</v>
+        <v>0.9276399495019295</v>
       </c>
       <c r="N104" s="4">
-        <v>113.53419396365564</v>
+        <v>114.3316237761128</v>
       </c>
     </row>
     <row r="105">
@@ -13168,16 +13180,16 @@
         <v>119.0</v>
       </c>
       <c r="K105" s="4">
-        <v>117.69733946950019</v>
+        <v>157.21513426867773</v>
       </c>
       <c r="L105" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M105" s="6">
-        <v>1.0440671065361635</v>
+        <v>0.8704634617126747</v>
       </c>
       <c r="N105" s="4">
-        <v>124.24398567780347</v>
+        <v>103.5851519438083</v>
       </c>
     </row>
     <row r="106">
@@ -13226,16 +13238,16 @@
         <v>107.25</v>
       </c>
       <c r="K106" s="4">
-        <v>111.81788195896411</v>
+        <v>143.09187899601477</v>
       </c>
       <c r="L106" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M106" s="6">
-        <v>1.0989648392018612</v>
+        <v>0.9563787335055374</v>
       </c>
       <c r="N106" s="4">
-        <v>117.86397900439961</v>
+        <v>102.57161916846889</v>
       </c>
     </row>
     <row r="107">
@@ -13284,16 +13296,16 @@
         <v>120.71</v>
       </c>
       <c r="K107" s="4">
-        <v>111.03122313124614</v>
+        <v>145.38258184831957</v>
       </c>
       <c r="L107" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M107" s="6">
-        <v>1.1067510309390076</v>
+        <v>0.9413096690765503</v>
       </c>
       <c r="N107" s="4">
-        <v>133.5959169446476</v>
+        <v>113.62549015423039</v>
       </c>
     </row>
     <row r="108">
@@ -13342,16 +13354,16 @@
         <v>108.71</v>
       </c>
       <c r="K108" s="4">
-        <v>105.90433306375704</v>
+        <v>132.3222914049477</v>
       </c>
       <c r="L108" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M108" s="6">
-        <v>1.1603294890016114</v>
+        <v>1.0342175045195687</v>
       </c>
       <c r="N108" s="4">
-        <v>126.13941874936516</v>
+        <v>112.4297849163223</v>
       </c>
     </row>
     <row r="109">
@@ -13400,16 +13412,16 @@
         <v>140.29</v>
       </c>
       <c r="K109" s="4">
-        <v>140.25011734223722</v>
+        <v>162.08574359104642</v>
       </c>
       <c r="L109" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M109" s="6">
-        <v>0.8761769543983005</v>
+        <v>0.8443063959679162</v>
       </c>
       <c r="N109" s="4">
-        <v>122.91886493253756</v>
+        <v>118.44774429033896</v>
       </c>
     </row>
     <row r="110">
@@ -13458,16 +13470,16 @@
         <v>126.43</v>
       </c>
       <c r="K110" s="4">
-        <v>133.39983923298843</v>
+        <v>147.5249422824168</v>
       </c>
       <c r="L110" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M110" s="6">
-        <v>0.9211699307395995</v>
+        <v>0.9276399495019295</v>
       </c>
       <c r="N110" s="4">
-        <v>116.46351434340757</v>
+        <v>117.28151881552895</v>
       </c>
     </row>
     <row r="111">
@@ -13516,16 +13528,16 @@
         <v>120.71</v>
       </c>
       <c r="K111" s="4">
-        <v>117.23105035159215</v>
+        <v>157.21513426867773</v>
       </c>
       <c r="L111" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M111" s="6">
-        <v>1.0482199067429643</v>
+        <v>0.8704634617126747</v>
       </c>
       <c r="N111" s="4">
-        <v>126.5306249429432</v>
+        <v>105.07364446333696</v>
       </c>
     </row>
     <row r="112">
@@ -13574,16 +13586,16 @@
         <v>108.71</v>
       </c>
       <c r="K112" s="4">
-        <v>111.81788195896411</v>
+        <v>143.09187899601477</v>
       </c>
       <c r="L112" s="4">
-        <v>122.88392066692566</v>
+        <v>136.8500300091362</v>
       </c>
       <c r="M112" s="6">
-        <v>1.0989648392018612</v>
+        <v>0.9563787335055374</v>
       </c>
       <c r="N112" s="4">
-        <v>119.46846766963432</v>
+        <v>103.96793211938696</v>
       </c>
     </row>
   </sheetData>
@@ -13659,7 +13671,7 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <v>59.97577158285408</v>
+        <v>35.79981320938094</v>
       </c>
     </row>
     <row r="8">
@@ -13669,7 +13681,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <v>0.8842284171459198</v>
+        <v>25.060186790619056</v>
       </c>
     </row>
     <row r="9">
@@ -13679,7 +13691,7 @@
         </is>
       </c>
       <c r="B9" s="4">
-        <v>122.7448379285657</v>
+        <v>133.66306947941928</v>
       </c>
     </row>
     <row r="10">
@@ -13689,7 +13701,7 @@
         </is>
       </c>
       <c r="B10" s="4">
-        <v>62.76906634571162</v>
+        <v>97.86325627003833</v>
       </c>
     </row>
     <row r="11">
@@ -13711,81 +13723,81 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>subscore_location</t>
+          <t>star_rating</t>
         </is>
       </c>
       <c r="B13" s="4">
-        <v>0.08929645949405834</v>
+        <v>0.23636669603545163</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>room_size_sqm</t>
+          <t>facility__sun_loungers_or_beach_chairs</t>
         </is>
       </c>
       <c r="B14" s="4">
-        <v>0.07269365381880571</v>
+        <v>-0.07794140951721594</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>subscore_comfort</t>
+          <t>room_size_sqm</t>
         </is>
       </c>
       <c r="B15" s="4">
-        <v>0.07055837185899178</v>
+        <v>0.07772012185133068</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>facility__free_toiletries</t>
+          <t>amenity__private_apartment_in_building</t>
         </is>
       </c>
       <c r="B16" s="4">
-        <v>0.054870486755297807</v>
+        <v>0.055805792600977386</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>facility__laundry_additional_charge</t>
+          <t>amenity__free_toiletries</t>
         </is>
       </c>
       <c r="B17" s="4">
-        <v>0.04794153024297472</v>
+        <v>0.03584584984733296</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>amenity__dining_area</t>
+          <t>facility__beachfront</t>
         </is>
       </c>
       <c r="B18" s="4">
-        <v>0.03874755113585365</v>
+        <v>0.027933792382918324</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>review_score</t>
+          <t>subscore_location</t>
         </is>
       </c>
       <c r="B19" s="4">
-        <v>0.03589691121488158</v>
+        <v>0.020546126585844718</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>review_count</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="B20" s="4">
-        <v>-0.03270767532155847</v>
+        <v>-0.020280208138876044</v>
       </c>
     </row>
     <row r="21">
@@ -13795,17 +13807,17 @@
         </is>
       </c>
       <c r="B21" s="4">
-        <v>0.032535023956222875</v>
+        <v>-0.019134197254294598</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>facility__car_hire</t>
+          <t>review_count</t>
         </is>
       </c>
       <c r="B22" s="4">
-        <v>0.03209535247965844</v>
+        <v>-0.017830935829421003</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/competitive_pricing_workbook.xlsx
+++ b/data/modelling/competitive_pricing_workbook.xlsx
@@ -99,7 +99,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B56"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -133,7 +133,7 @@
       </c>
       <c r="B3" t="inlineStr" s="6">
         <is>
-          <t>data\modelling\hedonic_training_table.parquet</t>
+          <t>C:\Users\gabri\Documents\Projects\tourism_pricing_analytics\data\modelling\hedonic_training_table.parquet</t>
         </is>
       </c>
     </row>
@@ -350,7 +350,7 @@
         </is>
       </c>
       <c r="B26" s="4">
-        <v>99.18554836537695</v>
+        <v>95.42249828422335</v>
       </c>
     </row>
     <row r="27">
@@ -360,7 +360,7 @@
         </is>
       </c>
       <c r="B27" s="4">
-        <v>113.62549015423039</v>
+        <v>108.86281067827358</v>
       </c>
     </row>
     <row r="28">
@@ -370,7 +370,7 @@
         </is>
       </c>
       <c r="B28" s="4">
-        <v>130.79983170794557</v>
+        <v>129.08809164518496</v>
       </c>
     </row>
     <row r="29">
@@ -422,7 +422,7 @@
         </is>
       </c>
       <c r="B34" s="6">
-        <v>0.3108050369803198</v>
+        <v>0.2591675394311855</v>
       </c>
     </row>
     <row r="35">
@@ -432,7 +432,7 @@
         </is>
       </c>
       <c r="B35" s="6">
-        <v>0.2851139151161721</v>
+        <v>0.2958767926228879</v>
       </c>
     </row>
     <row r="36">
@@ -442,7 +442,7 @@
         </is>
       </c>
       <c r="B36" s="4">
-        <v>53.32149472419017</v>
+        <v>54.619712119834205</v>
       </c>
     </row>
     <row r="37">
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B37" s="6">
-        <v>0.6246570229449309</v>
+        <v>0.72813823401472</v>
       </c>
     </row>
     <row r="38">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B38" s="6">
-        <v>9.448097188104942e+16</v>
+        <v>8.898396873876027e+16</v>
       </c>
     </row>
     <row r="39">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B44" s="4">
-        <v>35.79981320938094</v>
+        <v>35.015549797110054</v>
       </c>
     </row>
     <row r="45">
@@ -524,7 +524,105 @@
         </is>
       </c>
       <c r="B45" s="4">
-        <v>25.060186790619056</v>
+        <v>25.844450202889945</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46"/>
+      <c r="B46" s="6"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr" s="2">
+        <is>
+          <t>Prediction Band</t>
+        </is>
+      </c>
+      <c r="B47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr" s="6">
+        <is>
+          <t>80% conformal band</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Adjusted peer median</t>
+        </is>
+      </c>
+      <c r="B49" s="4">
+        <v>108.86281067827358</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="B50" s="4">
+        <v>70.86945006526639</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="B51" s="4">
+        <v>190.24123868409902</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52"/>
+      <c r="B52" s="6"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr" s="2">
+        <is>
+          <t>Selected Model</t>
+        </is>
+      </c>
+      <c r="B53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr" s="6">
+        <is>
+          <t>hist_gradient_boosting</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Min token frequency</t>
+        </is>
+      </c>
+      <c r="B55" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Out-of-fold residuals</t>
+        </is>
+      </c>
+      <c r="B56" s="6">
+        <v>1583</v>
       </c>
     </row>
   </sheetData>
@@ -7322,16 +7420,16 @@
         <v>108.0</v>
       </c>
       <c r="K4" s="4">
-        <v>159.76552449754183</v>
+        <v>130.09830850774077</v>
       </c>
       <c r="L4" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M4" s="6">
-        <v>0.8366202276729348</v>
+        <v>0.9486474997826311</v>
       </c>
       <c r="N4" s="4">
-        <v>90.35498458867696</v>
+        <v>102.45392997652415</v>
       </c>
     </row>
     <row r="5">
@@ -7380,16 +7478,16 @@
         <v>108.0</v>
       </c>
       <c r="K5" s="4">
-        <v>159.76552449754183</v>
+        <v>130.6929654143414</v>
       </c>
       <c r="L5" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M5" s="6">
-        <v>0.8366202276729348</v>
+        <v>0.9443311252487249</v>
       </c>
       <c r="N5" s="4">
-        <v>90.35498458867696</v>
+        <v>101.98776152686229</v>
       </c>
     </row>
     <row r="6">
@@ -7438,16 +7536,16 @@
         <v>109.25</v>
       </c>
       <c r="K6" s="4">
-        <v>169.36024625036478</v>
+        <v>153.33977732097074</v>
       </c>
       <c r="L6" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M6" s="6">
-        <v>0.8080410429188393</v>
+        <v>0.8318077188080952</v>
       </c>
       <c r="N6" s="4">
-        <v>88.27848393888318</v>
+        <v>90.8749932797844</v>
       </c>
     </row>
     <row r="7">
@@ -7496,16 +7594,16 @@
         <v>98.0</v>
       </c>
       <c r="K7" s="4">
-        <v>161.09504804553345</v>
+        <v>157.19854052612567</v>
       </c>
       <c r="L7" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M7" s="6">
-        <v>0.8297155691690751</v>
+        <v>0.7851054766714344</v>
       </c>
       <c r="N7" s="4">
-        <v>81.31212577856935</v>
+        <v>76.94033671380056</v>
       </c>
     </row>
     <row r="8">
@@ -7554,16 +7652,16 @@
         <v>67.0</v>
       </c>
       <c r="K8" s="4">
-        <v>80.91214979625612</v>
+        <v>76.77303287645469</v>
       </c>
       <c r="L8" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M8" s="6">
-        <v>1.651953010963058</v>
+        <v>1.6075623232238911</v>
       </c>
       <c r="N8" s="4">
-        <v>110.6808517345249</v>
+        <v>107.70667565600071</v>
       </c>
     </row>
     <row r="9">
@@ -7612,16 +7710,16 @@
         <v>67.0</v>
       </c>
       <c r="K9" s="4">
-        <v>80.91214979625612</v>
+        <v>73.50815322358532</v>
       </c>
       <c r="L9" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
       <c r="M9" s="6">
-        <v>1.651953010963058</v>
+        <v>1.6784802222752324</v>
       </c>
       <c r="N9" s="4">
-        <v>110.6808517345249</v>
+        <v>112.45817489244057</v>
       </c>
     </row>
     <row r="10">
@@ -7670,16 +7768,16 @@
         <v>397.0</v>
       </c>
       <c r="K10" s="4">
-        <v>264.0379161331309</v>
+        <v>299.7951014711909</v>
       </c>
       <c r="L10" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M10" s="6">
-        <v>0.5182968871036494</v>
+        <v>0.4254546180040068</v>
       </c>
       <c r="N10" s="4">
-        <v>205.7638641801488</v>
+        <v>168.9054833475907</v>
       </c>
     </row>
     <row r="11">
@@ -7728,16 +7826,16 @@
         <v>312.0</v>
       </c>
       <c r="K11" s="4">
-        <v>264.0379161331309</v>
+        <v>299.7951014711909</v>
       </c>
       <c r="L11" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M11" s="6">
-        <v>0.5182968871036494</v>
+        <v>0.4254546180040068</v>
       </c>
       <c r="N11" s="4">
-        <v>161.70862877633863</v>
+        <v>132.74184081725014</v>
       </c>
     </row>
     <row r="12">
@@ -7786,16 +7884,16 @@
         <v>359.0</v>
       </c>
       <c r="K12" s="4">
-        <v>247.28879874441662</v>
+        <v>284.71963481923063</v>
       </c>
       <c r="L12" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M12" s="6">
-        <v>0.5534016530630507</v>
+        <v>0.44798178550938134</v>
       </c>
       <c r="N12" s="4">
-        <v>198.67119344963518</v>
+        <v>160.8254609978679</v>
       </c>
     </row>
     <row r="13">
@@ -7844,16 +7942,16 @@
         <v>265.5</v>
       </c>
       <c r="K13" s="4">
-        <v>247.28879874441662</v>
+        <v>284.71963481923063</v>
       </c>
       <c r="L13" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M13" s="6">
-        <v>0.5534016530630507</v>
+        <v>0.44798178550938134</v>
       </c>
       <c r="N13" s="4">
-        <v>146.92813888823994</v>
+        <v>118.93916405274075</v>
       </c>
     </row>
     <row r="14">
@@ -7902,16 +8000,16 @@
         <v>94.0</v>
       </c>
       <c r="K14" s="4">
-        <v>112.22666603798459</v>
+        <v>108.74012960776881</v>
       </c>
       <c r="L14" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M14" s="6">
-        <v>1.191009892730657</v>
+        <v>1.1349759793094847</v>
       </c>
       <c r="N14" s="4">
-        <v>111.95492991668175</v>
+        <v>106.68774205509156</v>
       </c>
     </row>
     <row r="15">
@@ -7960,16 +8058,16 @@
         <v>84.75</v>
       </c>
       <c r="K15" s="4">
-        <v>112.22666603798459</v>
+        <v>108.70521518288092</v>
       </c>
       <c r="L15" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M15" s="6">
-        <v>1.191009892730657</v>
+        <v>1.1353405159465952</v>
       </c>
       <c r="N15" s="4">
-        <v>100.93808840892318</v>
+        <v>96.22010872647395</v>
       </c>
     </row>
     <row r="16">
@@ -8018,16 +8116,16 @@
         <v>105.5</v>
       </c>
       <c r="K16" s="4">
-        <v>110.00185161043224</v>
+        <v>106.50055630186178</v>
       </c>
       <c r="L16" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M16" s="6">
-        <v>1.215098359914726</v>
+        <v>1.158843102584434</v>
       </c>
       <c r="N16" s="4">
-        <v>128.19287697100359</v>
+        <v>122.25794732265777</v>
       </c>
     </row>
     <row r="17">
@@ -8076,16 +8174,16 @@
         <v>95.25</v>
       </c>
       <c r="K17" s="4">
-        <v>110.00185161043224</v>
+        <v>104.61696798320885</v>
       </c>
       <c r="L17" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M17" s="6">
-        <v>1.215098359914726</v>
+        <v>1.1797076274627492</v>
       </c>
       <c r="N17" s="4">
-        <v>115.73811878187766</v>
+        <v>112.36715151582686</v>
       </c>
     </row>
     <row r="18">
@@ -8134,16 +8232,16 @@
         <v>94.0</v>
       </c>
       <c r="K18" s="4">
-        <v>113.57728926038003</v>
+        <v>117.57847235546159</v>
       </c>
       <c r="L18" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M18" s="6">
-        <v>1.1768468005341444</v>
+        <v>1.0496601343713996</v>
       </c>
       <c r="N18" s="4">
-        <v>110.62359925020957</v>
+        <v>98.66805263091156</v>
       </c>
     </row>
     <row r="19">
@@ -8192,16 +8290,16 @@
         <v>84.75</v>
       </c>
       <c r="K19" s="4">
-        <v>113.57728926038003</v>
+        <v>115.49895798723539</v>
       </c>
       <c r="L19" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M19" s="6">
-        <v>1.1768468005341444</v>
+        <v>1.0685588618510085</v>
       </c>
       <c r="N19" s="4">
-        <v>99.73776634526874</v>
+        <v>90.56036354187297</v>
       </c>
     </row>
     <row r="20">
@@ -8250,16 +8348,16 @@
         <v>94.0</v>
       </c>
       <c r="K20" s="4">
-        <v>112.22666603798459</v>
+        <v>107.82238791794677</v>
       </c>
       <c r="L20" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
       <c r="M20" s="6">
-        <v>1.191009892730657</v>
+        <v>1.1443076316920329</v>
       </c>
       <c r="N20" s="4">
-        <v>111.95492991668175</v>
+        <v>107.5649173790511</v>
       </c>
     </row>
     <row r="21">
@@ -8308,16 +8406,16 @@
         <v>84.86</v>
       </c>
       <c r="K21" s="4">
-        <v>112.22666603798459</v>
+        <v>108.46619032679506</v>
       </c>
       <c r="L21" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
       <c r="M21" s="6">
-        <v>1.191009892730657</v>
+        <v>1.1375155796477303</v>
       </c>
       <c r="N21" s="4">
-        <v>101.06909949712355</v>
+        <v>96.52957208890639</v>
       </c>
     </row>
     <row r="22">
@@ -8366,16 +8464,16 @@
         <v>105.57</v>
       </c>
       <c r="K22" s="4">
-        <v>110.00185161043224</v>
+        <v>105.69702853257664</v>
       </c>
       <c r="L22" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
       <c r="M22" s="6">
-        <v>1.215098359914726</v>
+        <v>1.1673174078279605</v>
       </c>
       <c r="N22" s="4">
-        <v>128.27793385619762</v>
+        <v>123.23369874439777</v>
       </c>
     </row>
     <row r="23">
@@ -8424,16 +8522,16 @@
         <v>95.14</v>
       </c>
       <c r="K23" s="4">
-        <v>110.00185161043224</v>
+        <v>104.30832951033237</v>
       </c>
       <c r="L23" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
       <c r="M23" s="6">
-        <v>1.215098359914726</v>
+        <v>1.1828583770919618</v>
       </c>
       <c r="N23" s="4">
-        <v>115.60445796228703</v>
+        <v>112.53714599652925</v>
       </c>
     </row>
     <row r="24">
@@ -8482,16 +8580,16 @@
         <v>94.0</v>
       </c>
       <c r="K24" s="4">
-        <v>113.57728926038003</v>
+        <v>116.88987874501692</v>
       </c>
       <c r="L24" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
       <c r="M24" s="6">
-        <v>1.1768468005341444</v>
+        <v>1.0555403315192948</v>
       </c>
       <c r="N24" s="4">
-        <v>110.62359925020957</v>
+        <v>99.22079116281371</v>
       </c>
     </row>
     <row r="25">
@@ -8540,16 +8638,16 @@
         <v>84.86</v>
       </c>
       <c r="K25" s="4">
-        <v>113.57728926038003</v>
+        <v>115.35412260714756</v>
       </c>
       <c r="L25" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
       <c r="M25" s="6">
-        <v>1.1768468005341444</v>
+        <v>1.0695931673110428</v>
       </c>
       <c r="N25" s="4">
-        <v>99.8672194933275</v>
+        <v>90.7656761780151</v>
       </c>
     </row>
     <row r="26">
@@ -8598,16 +8696,16 @@
         <v>94.0</v>
       </c>
       <c r="K26" s="4">
-        <v>115.58397887994236</v>
+        <v>111.73090163699598</v>
       </c>
       <c r="L26" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M26" s="6">
-        <v>1.1839878790752045</v>
+        <v>1.1415750567402947</v>
       </c>
       <c r="N26" s="4">
-        <v>111.29486063306922</v>
+        <v>107.3080553335877</v>
       </c>
     </row>
     <row r="27">
@@ -8656,16 +8754,16 @@
         <v>84.75</v>
       </c>
       <c r="K27" s="4">
-        <v>115.58397887994236</v>
+        <v>112.73651105904109</v>
       </c>
       <c r="L27" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M27" s="6">
-        <v>1.1839878790752045</v>
+        <v>1.1313922098325302</v>
       </c>
       <c r="N27" s="4">
-        <v>100.34297275162358</v>
+        <v>95.88548978330694</v>
       </c>
     </row>
     <row r="28">
@@ -8714,16 +8812,16 @@
         <v>105.5</v>
       </c>
       <c r="K28" s="4">
-        <v>114.53332534144914</v>
+        <v>107.63451526372504</v>
       </c>
       <c r="L28" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M28" s="6">
-        <v>1.1948490066201782</v>
+        <v>1.1850214595511315</v>
       </c>
       <c r="N28" s="4">
-        <v>126.0565701984288</v>
+        <v>125.01976398264436</v>
       </c>
     </row>
     <row r="29">
@@ -8772,16 +8870,16 @@
         <v>95.25</v>
       </c>
       <c r="K29" s="4">
-        <v>114.53332534144914</v>
+        <v>106.91208320790143</v>
       </c>
       <c r="L29" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M29" s="6">
-        <v>1.1948490066201782</v>
+        <v>1.1930289500380005</v>
       </c>
       <c r="N29" s="4">
-        <v>113.80936788057198</v>
+        <v>113.63600749111954</v>
       </c>
     </row>
     <row r="30">
@@ -8830,16 +8928,16 @@
         <v>94.0</v>
       </c>
       <c r="K30" s="4">
-        <v>115.58397887994236</v>
+        <v>110.78791851895537</v>
       </c>
       <c r="L30" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M30" s="6">
-        <v>1.1839878790752045</v>
+        <v>1.1509609660390705</v>
       </c>
       <c r="N30" s="4">
-        <v>111.29486063306922</v>
+        <v>108.19033080767262</v>
       </c>
     </row>
     <row r="31">
@@ -8888,16 +8986,16 @@
         <v>84.86</v>
       </c>
       <c r="K31" s="4">
-        <v>115.58397887994236</v>
+        <v>112.48862204758773</v>
       </c>
       <c r="L31" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M31" s="6">
-        <v>1.1839878790752045</v>
+        <v>1.1335597094441352</v>
       </c>
       <c r="N31" s="4">
-        <v>100.47321141832185</v>
+        <v>96.19387694342932</v>
       </c>
     </row>
     <row r="32">
@@ -8946,16 +9044,16 @@
         <v>105.57</v>
       </c>
       <c r="K32" s="4">
-        <v>114.53332534144914</v>
+        <v>106.82243197560764</v>
       </c>
       <c r="L32" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M32" s="6">
-        <v>1.1948490066201782</v>
+        <v>1.19368720001761</v>
       </c>
       <c r="N32" s="4">
-        <v>126.14020962889221</v>
+        <v>126.01755770585908</v>
       </c>
     </row>
     <row r="33">
@@ -9004,16 +9102,16 @@
         <v>95.14</v>
       </c>
       <c r="K33" s="4">
-        <v>114.53332534144914</v>
+        <v>106.59667374106785</v>
       </c>
       <c r="L33" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M33" s="6">
-        <v>1.1948490066201782</v>
+        <v>1.1962152781030795</v>
       </c>
       <c r="N33" s="4">
-        <v>113.67793448984376</v>
+        <v>113.80792155872699</v>
       </c>
     </row>
     <row r="34">
@@ -9062,16 +9160,16 @@
         <v>78.25</v>
       </c>
       <c r="K34" s="4">
-        <v>137.07818020641773</v>
+        <v>129.6684348743938</v>
       </c>
       <c r="L34" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M34" s="6">
-        <v>0.9750864016296696</v>
+        <v>0.9517924328412596</v>
       </c>
       <c r="N34" s="4">
-        <v>76.30051092752164</v>
+        <v>74.47775786982857</v>
       </c>
     </row>
     <row r="35">
@@ -9120,16 +9218,16 @@
         <v>162.0</v>
       </c>
       <c r="K35" s="4">
-        <v>169.49337450969628</v>
+        <v>161.99076495565504</v>
       </c>
       <c r="L35" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M35" s="6">
-        <v>0.8074063685675652</v>
+        <v>0.787385690849812</v>
       </c>
       <c r="N35" s="4">
-        <v>130.79983170794557</v>
+        <v>127.55648191766954</v>
       </c>
     </row>
     <row r="36">
@@ -9178,16 +9276,16 @@
         <v>162.0</v>
       </c>
       <c r="K36" s="4">
-        <v>169.49337450969628</v>
+        <v>160.02278778798677</v>
       </c>
       <c r="L36" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M36" s="6">
-        <v>0.8074063685675652</v>
+        <v>0.7968400718838577</v>
       </c>
       <c r="N36" s="4">
-        <v>130.79983170794557</v>
+        <v>129.08809164518496</v>
       </c>
     </row>
     <row r="37">
@@ -9236,16 +9334,16 @@
         <v>57.0</v>
       </c>
       <c r="K37" s="4">
-        <v>97.86325627003833</v>
+        <v>88.36643156465529</v>
       </c>
       <c r="L37" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M37" s="6">
-        <v>1.365814653771554</v>
+        <v>1.3966551880225757</v>
       </c>
       <c r="N37" s="4">
-        <v>77.85143526497858</v>
+        <v>79.60934571728681</v>
       </c>
     </row>
     <row r="38">
@@ -9294,16 +9392,16 @@
         <v>57.0</v>
       </c>
       <c r="K38" s="4">
-        <v>97.86325627003833</v>
+        <v>88.01847265721676</v>
       </c>
       <c r="L38" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
       <c r="M38" s="6">
-        <v>1.365814653771554</v>
+        <v>1.4017737145050206</v>
       </c>
       <c r="N38" s="4">
-        <v>77.85143526497858</v>
+        <v>79.90110172678618</v>
       </c>
     </row>
     <row r="39">
@@ -9352,16 +9450,16 @@
         <v>104.5</v>
       </c>
       <c r="K39" s="4">
-        <v>138.65658333877644</v>
+        <v>139.68291256198503</v>
       </c>
       <c r="L39" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M39" s="6">
-        <v>0.9869710237614442</v>
+        <v>0.9131339548729508</v>
       </c>
       <c r="N39" s="4">
-        <v>103.13847198307091</v>
+        <v>95.42249828422335</v>
       </c>
     </row>
     <row r="40">
@@ -9410,16 +9508,16 @@
         <v>292.0</v>
       </c>
       <c r="K40" s="4">
-        <v>193.5507743994551</v>
+        <v>157.57377532659262</v>
       </c>
       <c r="L40" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M40" s="6">
-        <v>0.6905840077062259</v>
+        <v>0.7832358832300529</v>
       </c>
       <c r="N40" s="4">
-        <v>201.65053025021794</v>
+        <v>228.70487790317543</v>
       </c>
     </row>
     <row r="41">
@@ -9468,16 +9566,16 @@
         <v>237.0</v>
       </c>
       <c r="K41" s="4">
-        <v>193.5507743994551</v>
+        <v>157.57377532659262</v>
       </c>
       <c r="L41" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M41" s="6">
-        <v>0.6905840077062259</v>
+        <v>0.7832358832300529</v>
       </c>
       <c r="N41" s="4">
-        <v>163.66840982637552</v>
+        <v>185.62690432552253</v>
       </c>
     </row>
     <row r="42">
@@ -9526,16 +9624,16 @@
         <v>148.25</v>
       </c>
       <c r="K42" s="4">
-        <v>144.5534797662274</v>
+        <v>139.33614990017682</v>
       </c>
       <c r="L42" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M42" s="6">
-        <v>0.946708652261092</v>
+        <v>0.9154064502806828</v>
       </c>
       <c r="N42" s="4">
-        <v>140.3495576977069</v>
+        <v>135.70900625411122</v>
       </c>
     </row>
     <row r="43">
@@ -9584,16 +9682,16 @@
         <v>155.5</v>
       </c>
       <c r="K43" s="4">
-        <v>144.5534797662274</v>
+        <v>139.33614990017682</v>
       </c>
       <c r="L43" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M43" s="6">
-        <v>0.946708652261092</v>
+        <v>0.9154064502806828</v>
       </c>
       <c r="N43" s="4">
-        <v>147.2131954265998</v>
+        <v>142.34570301864616</v>
       </c>
     </row>
     <row r="44">
@@ -9642,16 +9740,16 @@
         <v>126.25</v>
       </c>
       <c r="K44" s="4">
-        <v>135.96498312721945</v>
+        <v>121.89294114866142</v>
       </c>
       <c r="L44" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M44" s="6">
-        <v>1.0065093736751958</v>
+        <v>1.0464035831274112</v>
       </c>
       <c r="N44" s="4">
-        <v>127.07180842649346</v>
+        <v>132.10845236983567</v>
       </c>
     </row>
     <row r="45">
@@ -9700,16 +9798,16 @@
         <v>148.14</v>
       </c>
       <c r="K45" s="4">
-        <v>144.5534797662274</v>
+        <v>136.00191766075258</v>
       </c>
       <c r="L45" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M45" s="6">
-        <v>0.946708652261092</v>
+        <v>0.9375792041558267</v>
       </c>
       <c r="N45" s="4">
-        <v>140.24541974595815</v>
+        <v>138.89298330364417</v>
       </c>
     </row>
     <row r="46">
@@ -9758,16 +9856,16 @@
         <v>155.57</v>
       </c>
       <c r="K46" s="4">
-        <v>144.5534797662274</v>
+        <v>136.00191766075258</v>
       </c>
       <c r="L46" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M46" s="6">
-        <v>0.946708652261092</v>
+        <v>0.9375792041558267</v>
       </c>
       <c r="N46" s="4">
-        <v>147.2794650322581</v>
+        <v>145.85919679052196</v>
       </c>
     </row>
     <row r="47">
@@ -9816,16 +9914,16 @@
         <v>126.29</v>
       </c>
       <c r="K47" s="4">
-        <v>135.96498312721945</v>
+        <v>121.58040542260484</v>
       </c>
       <c r="L47" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M47" s="6">
-        <v>1.0065093736751958</v>
+        <v>1.0487921082415383</v>
       </c>
       <c r="N47" s="4">
-        <v>127.11206880144049</v>
+        <v>132.4519553498239</v>
       </c>
     </row>
     <row r="48">
@@ -9874,16 +9972,16 @@
         <v>96.5</v>
       </c>
       <c r="K48" s="4">
-        <v>141.03401096560432</v>
+        <v>133.77948881217355</v>
       </c>
       <c r="L48" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M48" s="6">
-        <v>0.9703335321187984</v>
+        <v>0.9534287468759662</v>
       </c>
       <c r="N48" s="4">
-        <v>93.63718584946405</v>
+        <v>92.00587407353075</v>
       </c>
     </row>
     <row r="49">
@@ -9932,16 +10030,16 @@
         <v>99.5</v>
       </c>
       <c r="K49" s="4">
-        <v>141.03401096560432</v>
+        <v>138.34593588707583</v>
       </c>
       <c r="L49" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M49" s="6">
-        <v>0.9703335321187984</v>
+        <v>0.921958491646689</v>
       </c>
       <c r="N49" s="4">
-        <v>96.54818644582043</v>
+        <v>91.73486991884555</v>
       </c>
     </row>
     <row r="50">
@@ -9990,16 +10088,16 @@
         <v>100.43</v>
       </c>
       <c r="K50" s="4">
-        <v>141.03401096560432</v>
+        <v>130.17752483443084</v>
       </c>
       <c r="L50" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M50" s="6">
-        <v>0.9703335321187984</v>
+        <v>0.9795283009583595</v>
       </c>
       <c r="N50" s="4">
-        <v>97.45059663069092</v>
+        <v>98.37402726524806</v>
       </c>
     </row>
     <row r="51">
@@ -10048,16 +10146,16 @@
         <v>103.43</v>
       </c>
       <c r="K51" s="4">
-        <v>141.03401096560432</v>
+        <v>133.8765107520553</v>
       </c>
       <c r="L51" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M51" s="6">
-        <v>0.9703335321187984</v>
+        <v>0.95246409551406</v>
       </c>
       <c r="N51" s="4">
-        <v>100.36159722704733</v>
+        <v>98.51336139901923</v>
       </c>
     </row>
     <row r="52">
@@ -10106,16 +10204,16 @@
         <v>127.5</v>
       </c>
       <c r="K52" s="4">
-        <v>199.10000053971513</v>
+        <v>252.61342722474882</v>
       </c>
       <c r="L52" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M52" s="6">
-        <v>0.6713363592018528</v>
+        <v>0.48856245072837656</v>
       </c>
       <c r="N52" s="4">
-        <v>85.59538579823622</v>
+        <v>62.29171246786801</v>
       </c>
     </row>
     <row r="53">
@@ -10164,16 +10262,16 @@
         <v>114.0</v>
       </c>
       <c r="K53" s="4">
-        <v>197.9361580715072</v>
+        <v>239.82412313766739</v>
       </c>
       <c r="L53" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M53" s="6">
-        <v>0.6752837418978882</v>
+        <v>0.5146164342315631</v>
       </c>
       <c r="N53" s="4">
-        <v>76.98234657635925</v>
+        <v>58.6662735023982</v>
       </c>
     </row>
     <row r="54">
@@ -10222,16 +10320,16 @@
         <v>141.0</v>
       </c>
       <c r="K54" s="4">
-        <v>199.10000053971513</v>
+        <v>252.61342722474882</v>
       </c>
       <c r="L54" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M54" s="6">
-        <v>0.6713363592018528</v>
+        <v>0.48856245072837656</v>
       </c>
       <c r="N54" s="4">
-        <v>94.65842664746124</v>
+        <v>68.8873055527011</v>
       </c>
     </row>
     <row r="55">
@@ -10280,16 +10378,16 @@
         <v>161.0</v>
       </c>
       <c r="K55" s="4">
-        <v>221.41082210362913</v>
+        <v>282.2546031214548</v>
       </c>
       <c r="L55" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M55" s="6">
-        <v>0.6180819379510045</v>
+        <v>0.45189417272678895</v>
       </c>
       <c r="N55" s="4">
-        <v>99.51119201011173</v>
+        <v>72.75496180901303</v>
       </c>
     </row>
     <row r="56">
@@ -10338,16 +10436,16 @@
         <v>147.5</v>
       </c>
       <c r="K56" s="4">
-        <v>220.11656134528408</v>
+        <v>267.22999210573886</v>
       </c>
       <c r="L56" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M56" s="6">
-        <v>0.6217161906071551</v>
+        <v>0.4773012541400244</v>
       </c>
       <c r="N56" s="4">
-        <v>91.70313811455537</v>
+        <v>70.4019349856536</v>
       </c>
     </row>
     <row r="57">
@@ -10396,16 +10494,16 @@
         <v>174.5</v>
       </c>
       <c r="K57" s="4">
-        <v>221.41082210362913</v>
+        <v>282.2546031214548</v>
       </c>
       <c r="L57" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M57" s="6">
-        <v>0.6180819379510045</v>
+        <v>0.45189417272678895</v>
       </c>
       <c r="N57" s="4">
-        <v>107.85529817245029</v>
+        <v>78.85553314082468</v>
       </c>
     </row>
     <row r="58">
@@ -10454,16 +10552,16 @@
         <v>174.25</v>
       </c>
       <c r="K58" s="4">
-        <v>165.15338178273944</v>
+        <v>155.8675087074236</v>
       </c>
       <c r="L58" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M58" s="6">
-        <v>0.8093268695839003</v>
+        <v>0.7918098910753913</v>
       </c>
       <c r="N58" s="4">
-        <v>141.02520702499464</v>
+        <v>137.97287351988695</v>
       </c>
     </row>
     <row r="59">
@@ -10512,16 +10610,16 @@
         <v>193.25</v>
       </c>
       <c r="K59" s="4">
-        <v>165.15338178273944</v>
+        <v>155.8675087074236</v>
       </c>
       <c r="L59" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M59" s="6">
-        <v>0.8093268695839003</v>
+        <v>0.7918098910753913</v>
       </c>
       <c r="N59" s="4">
-        <v>156.40241754708873</v>
+        <v>153.01726145031938</v>
       </c>
     </row>
     <row r="60">
@@ -10570,16 +10668,16 @@
         <v>93.75</v>
       </c>
       <c r="K60" s="4">
-        <v>146.02245920024416</v>
+        <v>144.05638622143118</v>
       </c>
       <c r="L60" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M60" s="6">
-        <v>0.9371848053967535</v>
+        <v>0.8854117038576841</v>
       </c>
       <c r="N60" s="4">
-        <v>87.86107550594565</v>
+        <v>83.00734723665788</v>
       </c>
     </row>
     <row r="61">
@@ -10628,16 +10726,16 @@
         <v>105.0</v>
       </c>
       <c r="K61" s="4">
-        <v>146.02245920024416</v>
+        <v>136.20699345339207</v>
       </c>
       <c r="L61" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M61" s="6">
-        <v>0.9371848053967535</v>
+        <v>0.9361675673993018</v>
       </c>
       <c r="N61" s="4">
-        <v>98.40440456665912</v>
+        <v>98.2975945769267</v>
       </c>
     </row>
     <row r="62">
@@ -10686,16 +10784,16 @@
         <v>98.5</v>
       </c>
       <c r="K62" s="4">
-        <v>128.95914476387685</v>
+        <v>117.13995481609304</v>
       </c>
       <c r="L62" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M62" s="6">
-        <v>1.036476084919416</v>
+        <v>1.0535895739893373</v>
       </c>
       <c r="N62" s="4">
-        <v>102.09289436456247</v>
+        <v>103.77857303794973</v>
       </c>
     </row>
     <row r="63">
@@ -10744,16 +10842,16 @@
         <v>103.75</v>
       </c>
       <c r="K63" s="4">
-        <v>143.14777553222757</v>
+        <v>134.2977493303026</v>
       </c>
       <c r="L63" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M63" s="6">
-        <v>0.9560052854494163</v>
+        <v>0.9497494262706762</v>
       </c>
       <c r="N63" s="4">
-        <v>99.18554836537695</v>
+        <v>98.53650297558265</v>
       </c>
     </row>
     <row r="64">
@@ -10802,16 +10900,16 @@
         <v>268.5</v>
       </c>
       <c r="K64" s="4">
-        <v>177.3028997780227</v>
+        <v>175.82580751264337</v>
       </c>
       <c r="L64" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M64" s="6">
-        <v>0.7718431575595653</v>
+        <v>0.725429401862557</v>
       </c>
       <c r="N64" s="4">
-        <v>207.2398878047433</v>
+        <v>194.77779440009655</v>
       </c>
     </row>
     <row r="65">
@@ -10860,16 +10958,16 @@
         <v>269.5</v>
       </c>
       <c r="K65" s="4">
-        <v>177.3028997780227</v>
+        <v>175.82580751264337</v>
       </c>
       <c r="L65" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M65" s="6">
-        <v>0.7718431575595653</v>
+        <v>0.725429401862557</v>
       </c>
       <c r="N65" s="4">
-        <v>208.01173096230286</v>
+        <v>195.5032238019591</v>
       </c>
     </row>
     <row r="66">
@@ -10918,16 +11016,16 @@
         <v>213.25</v>
       </c>
       <c r="K66" s="4">
-        <v>166.4658778765534</v>
+        <v>163.5718872066862</v>
       </c>
       <c r="L66" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M66" s="6">
-        <v>0.822090579491735</v>
+        <v>0.7797746455949934</v>
       </c>
       <c r="N66" s="4">
-        <v>175.3108160766125</v>
+        <v>166.28694317313236</v>
       </c>
     </row>
     <row r="67">
@@ -10976,16 +11074,16 @@
         <v>214.0</v>
       </c>
       <c r="K67" s="4">
-        <v>166.4658778765534</v>
+        <v>163.5718872066862</v>
       </c>
       <c r="L67" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M67" s="6">
-        <v>0.822090579491735</v>
+        <v>0.7797746455949934</v>
       </c>
       <c r="N67" s="4">
-        <v>175.92738401123128</v>
+        <v>166.8717741573286</v>
       </c>
     </row>
     <row r="68">
@@ -11034,16 +11132,16 @@
         <v>271.14</v>
       </c>
       <c r="K68" s="4">
-        <v>177.3028997780227</v>
+        <v>172.43796909657183</v>
       </c>
       <c r="L68" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M68" s="6">
-        <v>0.7718431575595653</v>
+        <v>0.7394692154639261</v>
       </c>
       <c r="N68" s="4">
-        <v>209.27755374070054</v>
+        <v>200.4996830808889</v>
       </c>
     </row>
     <row r="69">
@@ -11092,16 +11190,16 @@
         <v>272.29</v>
       </c>
       <c r="K69" s="4">
-        <v>177.3028997780227</v>
+        <v>172.43796909657183</v>
       </c>
       <c r="L69" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M69" s="6">
-        <v>0.7718431575595653</v>
+        <v>0.7394692154639261</v>
       </c>
       <c r="N69" s="4">
-        <v>210.16517337189407</v>
+        <v>201.35007267867243</v>
       </c>
     </row>
     <row r="70">
@@ -11150,16 +11248,16 @@
         <v>253.57</v>
       </c>
       <c r="K70" s="4">
-        <v>166.4658778765534</v>
+        <v>168.18191103661843</v>
       </c>
       <c r="L70" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M70" s="6">
-        <v>0.822090579491735</v>
+        <v>0.758182428407959</v>
       </c>
       <c r="N70" s="4">
-        <v>208.45750824171924</v>
+        <v>192.25231837140618</v>
       </c>
     </row>
     <row r="71">
@@ -11208,16 +11306,16 @@
         <v>254.57</v>
       </c>
       <c r="K71" s="4">
-        <v>166.4658778765534</v>
+        <v>168.18191103661843</v>
       </c>
       <c r="L71" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M71" s="6">
-        <v>0.822090579491735</v>
+        <v>0.758182428407959</v>
       </c>
       <c r="N71" s="4">
-        <v>209.27959882121098</v>
+        <v>193.0105007998141</v>
       </c>
     </row>
     <row r="72">
@@ -11266,16 +11364,16 @@
         <v>215.43</v>
       </c>
       <c r="K72" s="4">
-        <v>166.4658778765534</v>
+        <v>163.82462092943103</v>
       </c>
       <c r="L72" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M72" s="6">
-        <v>0.822090579491735</v>
+        <v>0.7783480224194257</v>
       </c>
       <c r="N72" s="4">
-        <v>177.1029735399045</v>
+        <v>167.6795144698169</v>
       </c>
     </row>
     <row r="73">
@@ -11324,16 +11422,16 @@
         <v>216.29</v>
       </c>
       <c r="K73" s="4">
-        <v>166.4658778765534</v>
+        <v>163.82462092943103</v>
       </c>
       <c r="L73" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M73" s="6">
-        <v>0.822090579491735</v>
+        <v>0.7783480224194257</v>
       </c>
       <c r="N73" s="4">
-        <v>177.80997143826735</v>
+        <v>168.34889376909757</v>
       </c>
     </row>
     <row r="74">
@@ -11382,16 +11480,16 @@
         <v>145.25</v>
       </c>
       <c r="K74" s="4">
-        <v>170.06009663053555</v>
+        <v>157.888908514683</v>
       </c>
       <c r="L74" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M74" s="6">
-        <v>0.7859755000010924</v>
+        <v>0.7816726092595693</v>
       </c>
       <c r="N74" s="4">
-        <v>114.16294137515867</v>
+        <v>113.53794649495244</v>
       </c>
     </row>
     <row r="75">
@@ -11440,16 +11538,16 @@
         <v>184.75</v>
       </c>
       <c r="K75" s="4">
-        <v>185.3932137216464</v>
+        <v>195.59037224566885</v>
       </c>
       <c r="L75" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M75" s="6">
-        <v>0.720970669833169</v>
+        <v>0.6309995409017412</v>
       </c>
       <c r="N75" s="4">
-        <v>133.199331251678</v>
+        <v>116.57716518159668</v>
       </c>
     </row>
     <row r="76">
@@ -11498,16 +11596,16 @@
         <v>161.0</v>
       </c>
       <c r="K76" s="4">
-        <v>170.06009663053555</v>
+        <v>157.888908514683</v>
       </c>
       <c r="L76" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M76" s="6">
-        <v>0.7859755000010924</v>
+        <v>0.7816726092595693</v>
       </c>
       <c r="N76" s="4">
-        <v>126.54205550017588</v>
+        <v>125.84929009079065</v>
       </c>
     </row>
     <row r="77">
@@ -11556,16 +11654,16 @@
         <v>145.14</v>
       </c>
       <c r="K77" s="4">
-        <v>170.06009663053555</v>
+        <v>157.18907099502985</v>
       </c>
       <c r="L77" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
       <c r="M77" s="6">
-        <v>0.7859755000010924</v>
+        <v>0.7849272254154779</v>
       </c>
       <c r="N77" s="4">
-        <v>114.07648407015854</v>
+        <v>113.92433749680245</v>
       </c>
     </row>
     <row r="78">
@@ -11614,16 +11712,16 @@
         <v>184.71</v>
       </c>
       <c r="K78" s="4">
-        <v>185.3932137216464</v>
+        <v>189.0452341925609</v>
       </c>
       <c r="L78" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
       <c r="M78" s="6">
-        <v>0.720970669833169</v>
+        <v>0.6526585125975132</v>
       </c>
       <c r="N78" s="4">
-        <v>133.17049242488466</v>
+        <v>120.55255386188666</v>
       </c>
     </row>
     <row r="79">
@@ -11672,16 +11770,16 @@
         <v>161.0</v>
       </c>
       <c r="K79" s="4">
-        <v>170.06009663053555</v>
+        <v>157.18907099502985</v>
       </c>
       <c r="L79" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
       <c r="M79" s="6">
-        <v>0.7859755000010924</v>
+        <v>0.7849272254154779</v>
       </c>
       <c r="N79" s="4">
-        <v>126.54205550017588</v>
+        <v>126.37328329189194</v>
       </c>
     </row>
     <row r="80">
@@ -11730,16 +11828,16 @@
         <v>169.0</v>
       </c>
       <c r="K80" s="4">
-        <v>186.31710450169973</v>
+        <v>166.54737537670866</v>
       </c>
       <c r="L80" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M80" s="6">
-        <v>0.7345006266340283</v>
+        <v>0.7658434129472057</v>
       </c>
       <c r="N80" s="4">
-        <v>124.13060590115077</v>
+        <v>129.42753678807776</v>
       </c>
     </row>
     <row r="81">
@@ -11788,16 +11886,16 @@
         <v>215.25</v>
       </c>
       <c r="K81" s="4">
-        <v>203.11600110357506</v>
+        <v>205.5299632994456</v>
       </c>
       <c r="L81" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M81" s="6">
-        <v>0.673753073443742</v>
+        <v>0.6205869369521851</v>
       </c>
       <c r="N81" s="4">
-        <v>145.02534905876547</v>
+        <v>133.58133817895785</v>
       </c>
     </row>
     <row r="82">
@@ -11846,16 +11944,16 @@
         <v>187.5</v>
       </c>
       <c r="K82" s="4">
-        <v>203.11600110357506</v>
+        <v>205.5299632994456</v>
       </c>
       <c r="L82" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M82" s="6">
-        <v>0.673753073443742</v>
+        <v>0.6205869369521851</v>
       </c>
       <c r="N82" s="4">
-        <v>126.32870127070163</v>
+        <v>116.36005067853472</v>
       </c>
     </row>
     <row r="83">
@@ -11904,16 +12002,16 @@
         <v>127.5</v>
       </c>
       <c r="K83" s="4">
-        <v>207.3118842825195</v>
+        <v>185.6297116894301</v>
       </c>
       <c r="L83" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M83" s="6">
-        <v>0.6601166666482099</v>
+        <v>0.6871163523073053</v>
       </c>
       <c r="N83" s="4">
-        <v>84.16487499764676</v>
+        <v>87.60733491918143</v>
       </c>
     </row>
     <row r="84">
@@ -11962,16 +12060,16 @@
         <v>162.25</v>
       </c>
       <c r="K84" s="4">
-        <v>225.19267012523204</v>
+        <v>220.80331631844356</v>
       </c>
       <c r="L84" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M84" s="6">
-        <v>0.6077019733059359</v>
+        <v>0.5776598490574567</v>
       </c>
       <c r="N84" s="4">
-        <v>98.5996451688881</v>
+        <v>93.72531050957235</v>
       </c>
     </row>
     <row r="85">
@@ -12020,16 +12118,16 @@
         <v>141.25</v>
       </c>
       <c r="K85" s="4">
-        <v>225.19267012523204</v>
+        <v>220.80331631844356</v>
       </c>
       <c r="L85" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M85" s="6">
-        <v>0.6077019733059359</v>
+        <v>0.5776598490574567</v>
       </c>
       <c r="N85" s="4">
-        <v>85.83790372946345</v>
+        <v>81.59445367936576</v>
       </c>
     </row>
     <row r="86">
@@ -12078,16 +12176,16 @@
         <v>169.14</v>
       </c>
       <c r="K86" s="4">
-        <v>186.31710450169973</v>
+        <v>165.80915948057722</v>
       </c>
       <c r="L86" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M86" s="6">
-        <v>0.7345006266340283</v>
+        <v>0.7690321217687098</v>
       </c>
       <c r="N86" s="4">
-        <v>124.23343598887953</v>
+        <v>130.07409307595958</v>
       </c>
     </row>
     <row r="87">
@@ -12136,16 +12234,16 @@
         <v>215.29</v>
       </c>
       <c r="K87" s="4">
-        <v>203.11600110357506</v>
+        <v>198.8892548993821</v>
       </c>
       <c r="L87" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M87" s="6">
-        <v>0.673753073443742</v>
+        <v>0.6411234723994677</v>
       </c>
       <c r="N87" s="4">
-        <v>145.0522991817032</v>
+        <v>138.0274723728814</v>
       </c>
     </row>
     <row r="88">
@@ -12194,16 +12292,16 @@
         <v>187.57</v>
       </c>
       <c r="K88" s="4">
-        <v>203.11600110357506</v>
+        <v>198.8892548993821</v>
       </c>
       <c r="L88" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M88" s="6">
-        <v>0.673753073443742</v>
+        <v>0.6411234723994677</v>
       </c>
       <c r="N88" s="4">
-        <v>126.37586398584268</v>
+        <v>120.25552971796814</v>
       </c>
     </row>
     <row r="89">
@@ -12252,16 +12350,16 @@
         <v>83.0</v>
       </c>
       <c r="K89" s="4">
-        <v>140.1205598713433</v>
+        <v>114.36053224428096</v>
       </c>
       <c r="L89" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M89" s="6">
-        <v>0.9539147545666875</v>
+        <v>1.0791960536541632</v>
       </c>
       <c r="N89" s="4">
-        <v>79.17492462903506</v>
+        <v>89.57327245329554</v>
       </c>
     </row>
     <row r="90">
@@ -12310,16 +12408,16 @@
         <v>83.0</v>
       </c>
       <c r="K90" s="4">
-        <v>140.1205598713433</v>
+        <v>114.10907227784233</v>
       </c>
       <c r="L90" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
       <c r="M90" s="6">
-        <v>0.9539147545666875</v>
+        <v>1.0812635568655273</v>
       </c>
       <c r="N90" s="4">
-        <v>79.17492462903506</v>
+        <v>89.74487521983878</v>
       </c>
     </row>
     <row r="91">
@@ -12368,16 +12466,16 @@
         <v>92.0</v>
       </c>
       <c r="K91" s="4">
-        <v>144.1490568315369</v>
+        <v>122.08587528340719</v>
       </c>
       <c r="L91" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M91" s="6">
-        <v>0.9272559419908497</v>
+        <v>1.0109067474457587</v>
       </c>
       <c r="N91" s="4">
-        <v>85.30754666315818</v>
+        <v>93.0034207650098</v>
       </c>
     </row>
     <row r="92">
@@ -12426,16 +12524,16 @@
         <v>92.0</v>
       </c>
       <c r="K92" s="4">
-        <v>144.1490568315369</v>
+        <v>122.16024393175476</v>
       </c>
       <c r="L92" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
       <c r="M92" s="6">
-        <v>0.9272559419908497</v>
+        <v>1.0100011050296616</v>
       </c>
       <c r="N92" s="4">
-        <v>85.30754666315818</v>
+        <v>92.92010166272887</v>
       </c>
     </row>
     <row r="93">
@@ -12484,16 +12582,16 @@
         <v>92.0</v>
       </c>
       <c r="K93" s="4">
-        <v>156.52756401825053</v>
+        <v>136.09447058683335</v>
       </c>
       <c r="L93" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M93" s="6">
-        <v>0.874287099958829</v>
+        <v>0.9372108199981337</v>
       </c>
       <c r="N93" s="4">
-        <v>80.43441319621228</v>
+        <v>86.2233954398283</v>
       </c>
     </row>
     <row r="94">
@@ -12542,16 +12640,16 @@
         <v>104.5</v>
       </c>
       <c r="K94" s="4">
-        <v>155.1174166681702</v>
+        <v>140.08938323480157</v>
       </c>
       <c r="L94" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M94" s="6">
-        <v>0.882235102599008</v>
+        <v>0.9104844880508525</v>
       </c>
       <c r="N94" s="4">
-        <v>92.19356822159634</v>
+        <v>95.14562900131408</v>
       </c>
     </row>
     <row r="95">
@@ -12600,16 +12698,16 @@
         <v>92.0</v>
       </c>
       <c r="K95" s="4">
-        <v>156.52756401825053</v>
+        <v>132.0943747287276</v>
       </c>
       <c r="L95" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M95" s="6">
-        <v>0.874287099958829</v>
+        <v>0.9653141550190747</v>
       </c>
       <c r="N95" s="4">
-        <v>80.43441319621228</v>
+        <v>88.80890226175487</v>
       </c>
     </row>
     <row r="96">
@@ -12658,16 +12756,16 @@
         <v>107.71</v>
       </c>
       <c r="K96" s="4">
-        <v>155.1174166681702</v>
+        <v>135.97186869342585</v>
       </c>
       <c r="L96" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M96" s="6">
-        <v>0.882235102599008</v>
+        <v>0.9377864035356885</v>
       </c>
       <c r="N96" s="4">
-        <v>95.02554290093914</v>
+        <v>101.008973524829</v>
       </c>
     </row>
     <row r="97">
@@ -12716,16 +12814,16 @@
         <v>112.0</v>
       </c>
       <c r="K97" s="4">
-        <v>128.66089802326437</v>
+        <v>126.9740570187416</v>
       </c>
       <c r="L97" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M97" s="6">
-        <v>1.0388787233184895</v>
+        <v>0.9719893810560141</v>
       </c>
       <c r="N97" s="4">
-        <v>116.35441701167082</v>
+        <v>108.86281067827358</v>
       </c>
     </row>
     <row r="98">
@@ -12774,16 +12872,16 @@
         <v>134.0</v>
       </c>
       <c r="K98" s="4">
-        <v>141.23577148513135</v>
+        <v>135.2071574362543</v>
       </c>
       <c r="L98" s="4">
-        <v>133.66306947941928</v>
+        <v>123.4174350918177</v>
       </c>
       <c r="M98" s="6">
-        <v>0.9463825493634996</v>
+        <v>0.9128025278543772</v>
       </c>
       <c r="N98" s="4">
-        <v>126.81526161470894</v>
+        <v>122.31553873248654</v>
       </c>
     </row>
     <row r="99">
@@ -12832,16 +12930,16 @@
         <v>114.43</v>
       </c>
       <c r="K99" s="4">
-        <v>128.66089802326437</v>
+        <v>126.66788738814606</v>
       </c>
       <c r="L99" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
       <c r="M99" s="6">
-        <v>1.0388787233184895</v>
+        <v>0.9740588866354755</v>
       </c>
       <c r="N99" s="4">
-        <v>118.87889230933476</v>
+        <v>111.46155839769746</v>
       </c>
     </row>
     <row r="100">
@@ -12890,16 +12988,16 @@
         <v>134.0</v>
       </c>
       <c r="K100" s="4">
-        <v>141.23577148513135</v>
+        <v>134.88113551950937</v>
       </c>
       <c r="L100" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
       <c r="M100" s="6">
-        <v>0.9463825493634996</v>
+        <v>0.9147460160870251</v>
       </c>
       <c r="N100" s="4">
-        <v>126.81526161470894</v>
+        <v>122.57596615566136</v>
       </c>
     </row>
     <row r="101">
@@ -12948,16 +13046,16 @@
         <v>119.0</v>
       </c>
       <c r="K101" s="4">
-        <v>145.38258184831957</v>
+        <v>145.5682540958385</v>
       </c>
       <c r="L101" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M101" s="6">
-        <v>0.9413096690765503</v>
+        <v>0.8762158423080539</v>
       </c>
       <c r="N101" s="4">
-        <v>112.01585062010949</v>
+        <v>104.26968523465843</v>
       </c>
     </row>
     <row r="102">
@@ -13006,16 +13104,16 @@
         <v>107.25</v>
       </c>
       <c r="K102" s="4">
-        <v>132.3222914049477</v>
+        <v>131.90472525357382</v>
       </c>
       <c r="L102" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M102" s="6">
-        <v>1.0342175045195687</v>
+        <v>0.9669798419328587</v>
       </c>
       <c r="N102" s="4">
-        <v>110.91982735972374</v>
+        <v>103.70858804729909</v>
       </c>
     </row>
     <row r="103">
@@ -13064,16 +13162,16 @@
         <v>136.75</v>
       </c>
       <c r="K103" s="4">
-        <v>162.08574359104642</v>
+        <v>159.48131975719488</v>
       </c>
       <c r="L103" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M103" s="6">
-        <v>0.8443063959679162</v>
+        <v>0.7997752374390147</v>
       </c>
       <c r="N103" s="4">
-        <v>115.45889964861254</v>
+        <v>109.36926371978525</v>
       </c>
     </row>
     <row r="104">
@@ -13122,16 +13220,16 @@
         <v>123.25</v>
       </c>
       <c r="K104" s="4">
-        <v>147.5249422824168</v>
+        <v>144.3143104692759</v>
       </c>
       <c r="L104" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M104" s="6">
-        <v>0.9276399495019295</v>
+        <v>0.8838292610146435</v>
       </c>
       <c r="N104" s="4">
-        <v>114.3316237761128</v>
+        <v>108.93195642005482</v>
       </c>
     </row>
     <row r="105">
@@ -13180,16 +13278,16 @@
         <v>119.0</v>
       </c>
       <c r="K105" s="4">
-        <v>157.21513426867773</v>
+        <v>158.00487428078586</v>
       </c>
       <c r="L105" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M105" s="6">
-        <v>0.8704634617126747</v>
+        <v>0.8072485798712387</v>
       </c>
       <c r="N105" s="4">
-        <v>103.5851519438083</v>
+        <v>96.0625810046774</v>
       </c>
     </row>
     <row r="106">
@@ -13238,16 +13336,16 @@
         <v>107.25</v>
       </c>
       <c r="K106" s="4">
-        <v>143.09187899601477</v>
+        <v>143.60514195844735</v>
       </c>
       <c r="L106" s="4">
-        <v>136.8500300091362</v>
+        <v>127.54921037589797</v>
       </c>
       <c r="M106" s="6">
-        <v>0.9563787335055374</v>
+        <v>0.8881938949846571</v>
       </c>
       <c r="N106" s="4">
-        <v>102.57161916846889</v>
+        <v>95.25879523710447</v>
       </c>
     </row>
     <row r="107">
@@ -13296,16 +13394,16 @@
         <v>120.71</v>
       </c>
       <c r="K107" s="4">
-        <v>145.38258184831957</v>
+        <v>142.62090725792496</v>
       </c>
       <c r="L107" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M107" s="6">
-        <v>0.9413096690765503</v>
+        <v>0.8940664603502531</v>
       </c>
       <c r="N107" s="4">
-        <v>113.62549015423039</v>
+        <v>107.92276242887904</v>
       </c>
     </row>
     <row r="108">
@@ -13354,16 +13452,16 @@
         <v>108.71</v>
       </c>
       <c r="K108" s="4">
-        <v>132.3222914049477</v>
+        <v>131.58666641578515</v>
       </c>
       <c r="L108" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M108" s="6">
-        <v>1.0342175045195687</v>
+        <v>0.9690386814810157</v>
       </c>
       <c r="N108" s="4">
-        <v>112.4297849163223</v>
+        <v>105.34419506380121</v>
       </c>
     </row>
     <row r="109">
@@ -13412,16 +13510,16 @@
         <v>140.29</v>
       </c>
       <c r="K109" s="4">
-        <v>162.08574359104642</v>
+        <v>156.25227255585125</v>
       </c>
       <c r="L109" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M109" s="6">
-        <v>0.8443063959679162</v>
+        <v>0.8160685770407355</v>
       </c>
       <c r="N109" s="4">
-        <v>118.44774429033896</v>
+        <v>114.48626067304478</v>
       </c>
     </row>
     <row r="110">
@@ -13470,16 +13568,16 @@
         <v>126.43</v>
       </c>
       <c r="K110" s="4">
-        <v>147.5249422824168</v>
+        <v>143.9663286833627</v>
       </c>
       <c r="L110" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M110" s="6">
-        <v>0.9276399495019295</v>
+        <v>0.88571106098346</v>
       </c>
       <c r="N110" s="4">
-        <v>117.28151881552895</v>
+        <v>111.98044944013886</v>
       </c>
     </row>
     <row r="111">
@@ -13528,16 +13626,16 @@
         <v>120.71</v>
       </c>
       <c r="K111" s="4">
-        <v>157.21513426867773</v>
+        <v>154.80572093874054</v>
       </c>
       <c r="L111" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M111" s="6">
-        <v>0.8704634617126747</v>
+        <v>0.8236941693808186</v>
       </c>
       <c r="N111" s="4">
-        <v>105.07364446333696</v>
+        <v>99.42812318595861</v>
       </c>
     </row>
     <row r="112">
@@ -13586,16 +13684,16 @@
         <v>108.71</v>
       </c>
       <c r="K112" s="4">
-        <v>143.09187899601477</v>
+        <v>143.25887017429426</v>
       </c>
       <c r="L112" s="4">
-        <v>136.8500300091362</v>
+        <v>127.51256972403469</v>
       </c>
       <c r="M112" s="6">
-        <v>0.9563787335055374</v>
+        <v>0.8900849878886941</v>
       </c>
       <c r="N112" s="4">
-        <v>103.96793211938696</v>
+        <v>96.76113903337992</v>
       </c>
     </row>
   </sheetData>
@@ -13671,7 +13769,7 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <v>35.79981320938094</v>
+        <v>35.015549797110054</v>
       </c>
     </row>
     <row r="8">
@@ -13681,7 +13779,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <v>25.060186790619056</v>
+        <v>25.844450202889945</v>
       </c>
     </row>
     <row r="9">
@@ -13691,7 +13789,7 @@
         </is>
       </c>
       <c r="B9" s="4">
-        <v>133.66306947941928</v>
+        <v>123.38198136176534</v>
       </c>
     </row>
     <row r="10">
@@ -13701,7 +13799,7 @@
         </is>
       </c>
       <c r="B10" s="4">
-        <v>97.86325627003833</v>
+        <v>88.36643156465529</v>
       </c>
     </row>
     <row r="11">
@@ -13727,7 +13825,7 @@
         </is>
       </c>
       <c r="B13" s="4">
-        <v>0.23636669603545163</v>
+        <v>0.273802798844977</v>
       </c>
     </row>
     <row r="14">
@@ -13737,7 +13835,7 @@
         </is>
       </c>
       <c r="B14" s="4">
-        <v>-0.07794140951721594</v>
+        <v>-0.06449136362196928</v>
       </c>
     </row>
     <row r="15">
@@ -13747,47 +13845,47 @@
         </is>
       </c>
       <c r="B15" s="4">
-        <v>0.07772012185133068</v>
+        <v>0.05413050755737717</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>amenity__private_apartment_in_building</t>
+          <t>top_attraction_km</t>
         </is>
       </c>
       <c r="B16" s="4">
-        <v>0.055805792600977386</v>
+        <v>-0.02602353227274371</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>amenity__free_toiletries</t>
+          <t>facility__beachfront</t>
         </is>
       </c>
       <c r="B17" s="4">
-        <v>0.03584584984733296</v>
+        <v>0.02451800017533952</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>facility__beachfront</t>
+          <t>amenity__free_toiletries</t>
         </is>
       </c>
       <c r="B18" s="4">
-        <v>0.027933792382918324</v>
+        <v>0.024086754446320226</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>subscore_location</t>
+          <t>facility__sun_terrace</t>
         </is>
       </c>
       <c r="B19" s="4">
-        <v>0.020546126585844718</v>
+        <v>0.02045352178935876</v>
       </c>
     </row>
     <row r="20">
@@ -13797,27 +13895,27 @@
         </is>
       </c>
       <c r="B20" s="4">
-        <v>-0.020280208138876044</v>
+        <v>-0.019709009359610265</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>subscore_cleanliness</t>
+          <t>amenity__free_wifi</t>
         </is>
       </c>
       <c r="B21" s="4">
-        <v>-0.019134197254294598</v>
+        <v>0.017905256015963367</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>review_count</t>
+          <t>facility__safety_deposit_box</t>
         </is>
       </c>
       <c r="B22" s="4">
-        <v>-0.017830935829421003</v>
+        <v>-0.01769648056388714</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/competitive_pricing_workbook.xlsx
+++ b/data/modelling/competitive_pricing_workbook.xlsx
@@ -121,7 +121,7 @@
       </c>
       <c r="B2" t="inlineStr" s="6">
         <is>
-          <t>C:\Users\gabri\Documents\Projects\tourism_pricing_analytics\data\modelling\modelling_table.parquet</t>
+          <t>data\modelling\modelling_table.parquet</t>
         </is>
       </c>
     </row>
@@ -350,7 +350,7 @@
         </is>
       </c>
       <c r="B26" s="4">
-        <v>170.7671971549345</v>
+        <v>99.42803960297633</v>
       </c>
     </row>
     <row r="27">
@@ -360,7 +360,7 @@
         </is>
       </c>
       <c r="B27" s="4">
-        <v>185.20879816687994</v>
+        <v>110.37743649567014</v>
       </c>
     </row>
     <row r="28">
@@ -370,7 +370,7 @@
         </is>
       </c>
       <c r="B28" s="4">
-        <v>196.7377095872978</v>
+        <v>126.94352955488208</v>
       </c>
     </row>
     <row r="29">
@@ -422,7 +422,7 @@
         </is>
       </c>
       <c r="B34" s="6">
-        <v>0.5402789567551329</v>
+        <v>0.532632481097383</v>
       </c>
     </row>
     <row r="35">
@@ -432,7 +432,7 @@
         </is>
       </c>
       <c r="B35" s="6">
-        <v>0.26213843860491537</v>
+        <v>0.2645846013071335</v>
       </c>
     </row>
     <row r="36">
@@ -442,7 +442,7 @@
         </is>
       </c>
       <c r="B36" s="4">
-        <v>52.34962535851578</v>
+        <v>53.358999841823035</v>
       </c>
     </row>
     <row r="37">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B44" s="4">
-        <v>53.35093460216628</v>
+        <v>52.353746007247224</v>
       </c>
     </row>
     <row r="45">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B45" s="4">
-        <v>-9.350934602166276</v>
+        <v>-8.353746007247224</v>
       </c>
     </row>
     <row r="46">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B49" s="4">
-        <v>185.20879816687994</v>
+        <v>110.37743649567014</v>
       </c>
     </row>
     <row r="50">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B50" s="4">
-        <v>129.59308739123878</v>
+        <v>77.4300859791136</v>
       </c>
     </row>
     <row r="51">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B51" s="4">
-        <v>306.93256049453555</v>
+        <v>185.5713282331026</v>
       </c>
     </row>
     <row r="52">
@@ -11126,16 +11126,16 @@
         <v>108.0</v>
       </c>
       <c r="K4" s="4">
-        <v>114.76963547224267</v>
+        <v>116.16571733601175</v>
       </c>
       <c r="L4" s="4">
-        <v>170.42453395837398</v>
+        <v>109.31203876392127</v>
       </c>
       <c r="M4" s="6">
-        <v>1.4849270301951214</v>
+        <v>0.9410008500850032</v>
       </c>
       <c r="N4" s="4">
-        <v>160.37211926107312</v>
+        <v>101.62809180918035</v>
       </c>
     </row>
     <row r="5">
@@ -11184,16 +11184,16 @@
         <v>98.0</v>
       </c>
       <c r="K5" s="4">
-        <v>101.50488469720801</v>
+        <v>103.29316752049105</v>
       </c>
       <c r="L5" s="4">
-        <v>188.13852602407508</v>
+        <v>99.94299351365942</v>
       </c>
       <c r="M5" s="6">
-        <v>1.8534923376869765</v>
+        <v>0.9675663542202145</v>
       </c>
       <c r="N5" s="4">
-        <v>181.6422490933237</v>
+        <v>94.82150271358103</v>
       </c>
     </row>
     <row r="6">
@@ -11242,16 +11242,16 @@
         <v>85.5</v>
       </c>
       <c r="K6" s="4">
-        <v>90.68310874941803</v>
+        <v>91.89205210319383</v>
       </c>
       <c r="L6" s="4">
-        <v>170.42453395837398</v>
+        <v>101.26147189184518</v>
       </c>
       <c r="M6" s="6">
-        <v>1.8793415478212496</v>
+        <v>1.1019611552273267</v>
       </c>
       <c r="N6" s="4">
-        <v>160.68370233871684</v>
+        <v>94.21767877193643</v>
       </c>
     </row>
     <row r="7">
@@ -11300,16 +11300,16 @@
         <v>90.0</v>
       </c>
       <c r="K7" s="4">
-        <v>91.24617929795522</v>
+        <v>90.1974544580118</v>
       </c>
       <c r="L7" s="4">
-        <v>188.13852602407508</v>
+        <v>101.55822242218522</v>
       </c>
       <c r="M7" s="6">
-        <v>2.061878398324248</v>
+        <v>1.1259544189183524</v>
       </c>
       <c r="N7" s="4">
-        <v>185.56905584918232</v>
+        <v>101.3358977026517</v>
       </c>
     </row>
     <row r="8">
@@ -11358,16 +11358,16 @@
         <v>98.0</v>
       </c>
       <c r="K8" s="4">
-        <v>93.68938056478484</v>
+        <v>94.6698037032188</v>
       </c>
       <c r="L8" s="4">
-        <v>188.13852602407508</v>
+        <v>101.55822242218522</v>
       </c>
       <c r="M8" s="6">
-        <v>2.008109402473635</v>
+        <v>1.0727625752828325</v>
       </c>
       <c r="N8" s="4">
-        <v>196.79472144241623</v>
+        <v>105.13073237771758</v>
       </c>
     </row>
     <row r="9">
@@ -11416,16 +11416,16 @@
         <v>98.0</v>
       </c>
       <c r="K9" s="4">
-        <v>91.55126436756814</v>
+        <v>92.44626540260073</v>
       </c>
       <c r="L9" s="4">
-        <v>188.13852602407508</v>
+        <v>101.55822242218522</v>
       </c>
       <c r="M9" s="6">
-        <v>2.055007402942245</v>
+        <v>1.0985649012418424</v>
       </c>
       <c r="N9" s="4">
-        <v>201.39072548834002</v>
+        <v>107.65936032170055</v>
       </c>
     </row>
     <row r="10">
@@ -11474,16 +11474,16 @@
         <v>85.86</v>
       </c>
       <c r="K10" s="4">
-        <v>91.97297404114583</v>
+        <v>90.17597563369989</v>
       </c>
       <c r="L10" s="4">
-        <v>188.5294537264215</v>
+        <v>101.21999283506118</v>
       </c>
       <c r="M10" s="6">
-        <v>2.049835353177547</v>
+        <v>1.1224718349177916</v>
       </c>
       <c r="N10" s="4">
-        <v>175.9988634238242</v>
+        <v>96.37543174604158</v>
       </c>
     </row>
     <row r="11">
@@ -11532,16 +11532,16 @@
         <v>93.57</v>
       </c>
       <c r="K11" s="4">
-        <v>95.14932963929367</v>
+        <v>95.25637604236904</v>
       </c>
       <c r="L11" s="4">
-        <v>188.5294537264215</v>
+        <v>101.21999283506118</v>
       </c>
       <c r="M11" s="6">
-        <v>1.9814060113836558</v>
+        <v>1.0626059592067578</v>
       </c>
       <c r="N11" s="4">
-        <v>185.40016048516867</v>
+        <v>99.42803960297633</v>
       </c>
     </row>
     <row r="12">
@@ -11590,16 +11590,16 @@
         <v>93.57</v>
       </c>
       <c r="K12" s="4">
-        <v>92.36452835256866</v>
+        <v>92.72907602508718</v>
       </c>
       <c r="L12" s="4">
-        <v>188.5294537264215</v>
+        <v>101.21999283506118</v>
       </c>
       <c r="M12" s="6">
-        <v>2.0411456333840365</v>
+        <v>1.0915669299635513</v>
       </c>
       <c r="N12" s="4">
-        <v>190.98999691574429</v>
+        <v>102.1379176366895</v>
       </c>
     </row>
     <row r="13">
@@ -11648,16 +11648,16 @@
         <v>59.0</v>
       </c>
       <c r="K13" s="4">
-        <v>66.05218225716344</v>
+        <v>65.28455048701424</v>
       </c>
       <c r="L13" s="4">
-        <v>188.13852602407508</v>
+        <v>90.5030183485564</v>
       </c>
       <c r="M13" s="6">
-        <v>2.8483317219041804</v>
+        <v>1.3862853871768381</v>
       </c>
       <c r="N13" s="4">
-        <v>168.05157159234665</v>
+        <v>81.79083784343345</v>
       </c>
     </row>
     <row r="14">
@@ -11706,16 +11706,16 @@
         <v>59.0</v>
       </c>
       <c r="K14" s="4">
-        <v>66.47569727676341</v>
+        <v>65.74031427387384</v>
       </c>
       <c r="L14" s="4">
-        <v>188.5294537264215</v>
+        <v>91.7051167567904</v>
       </c>
       <c r="M14" s="6">
-        <v>2.8360658323221832</v>
+        <v>1.3949601210415168</v>
       </c>
       <c r="N14" s="4">
-        <v>167.3278841070088</v>
+        <v>82.30264714144948</v>
       </c>
     </row>
     <row r="15">
@@ -11764,16 +11764,16 @@
         <v>142.5</v>
       </c>
       <c r="K15" s="4">
-        <v>120.68804136196667</v>
+        <v>121.13573736508206</v>
       </c>
       <c r="L15" s="4">
-        <v>170.42453395837398</v>
+        <v>125.02241954541809</v>
       </c>
       <c r="M15" s="6">
-        <v>1.412107877757648</v>
+        <v>1.032085347106298</v>
       </c>
       <c r="N15" s="4">
-        <v>201.22537258046484</v>
+        <v>147.07216196264747</v>
       </c>
     </row>
     <row r="16">
@@ -11822,16 +11822,16 @@
         <v>104.25</v>
       </c>
       <c r="K16" s="4">
-        <v>120.68804136196667</v>
+        <v>121.13573736508206</v>
       </c>
       <c r="L16" s="4">
-        <v>170.42453395837398</v>
+        <v>125.02241954541809</v>
       </c>
       <c r="M16" s="6">
-        <v>1.412107877757648</v>
+        <v>1.032085347106298</v>
       </c>
       <c r="N16" s="4">
-        <v>147.2122462562348</v>
+        <v>107.59489743583157</v>
       </c>
     </row>
     <row r="17">
@@ -11880,16 +11880,16 @@
         <v>120.0</v>
       </c>
       <c r="K17" s="4">
-        <v>112.95801893461748</v>
+        <v>113.96539227303907</v>
       </c>
       <c r="L17" s="4">
-        <v>170.42453395837398</v>
+        <v>125.02241954541809</v>
       </c>
       <c r="M17" s="6">
-        <v>1.5087422350866417</v>
+        <v>1.0970209205781394</v>
       </c>
       <c r="N17" s="4">
-        <v>181.049068210397</v>
+        <v>131.64251046937673</v>
       </c>
     </row>
     <row r="18">
@@ -11938,16 +11938,16 @@
         <v>132.25</v>
       </c>
       <c r="K18" s="4">
-        <v>112.95801893461748</v>
+        <v>113.96539227303907</v>
       </c>
       <c r="L18" s="4">
-        <v>170.42453395837398</v>
+        <v>125.02241954541809</v>
       </c>
       <c r="M18" s="6">
-        <v>1.5087422350866417</v>
+        <v>1.0970209205781394</v>
       </c>
       <c r="N18" s="4">
-        <v>199.53116059020837</v>
+        <v>145.08101674645894</v>
       </c>
     </row>
     <row r="19">
@@ -11996,16 +11996,16 @@
         <v>89.0</v>
       </c>
       <c r="K19" s="4">
-        <v>112.95801893461748</v>
+        <v>113.96539227303907</v>
       </c>
       <c r="L19" s="4">
-        <v>170.42453395837398</v>
+        <v>125.02241954541809</v>
       </c>
       <c r="M19" s="6">
-        <v>1.5087422350866417</v>
+        <v>1.0970209205781394</v>
       </c>
       <c r="N19" s="4">
-        <v>134.27805892271112</v>
+        <v>97.63486193145441</v>
       </c>
     </row>
     <row r="20">
@@ -12054,16 +12054,16 @@
         <v>406.75</v>
       </c>
       <c r="K20" s="4">
-        <v>339.05329104002243</v>
+        <v>338.1841324119249</v>
       </c>
       <c r="L20" s="4">
-        <v>188.13852602407508</v>
+        <v>114.97925917726775</v>
       </c>
       <c r="M20" s="6">
-        <v>0.5548936730476004</v>
+        <v>0.5</v>
       </c>
       <c r="N20" s="4">
-        <v>225.70300151211146</v>
+        <v>203.375</v>
       </c>
     </row>
     <row r="21">
@@ -12112,16 +12112,16 @@
         <v>296.5</v>
       </c>
       <c r="K21" s="4">
-        <v>339.05329104002243</v>
+        <v>338.1841324119249</v>
       </c>
       <c r="L21" s="4">
-        <v>188.13852602407508</v>
+        <v>114.97925917726775</v>
       </c>
       <c r="M21" s="6">
-        <v>0.5548936730476004</v>
+        <v>0.5</v>
       </c>
       <c r="N21" s="4">
-        <v>164.5259740586135</v>
+        <v>148.25</v>
       </c>
     </row>
     <row r="22">
@@ -12170,16 +12170,16 @@
         <v>368.25</v>
       </c>
       <c r="K22" s="4">
-        <v>299.44653233092754</v>
+        <v>306.25810204093113</v>
       </c>
       <c r="L22" s="4">
-        <v>188.13852602407508</v>
+        <v>114.97925917726775</v>
       </c>
       <c r="M22" s="6">
-        <v>0.6282875428864791</v>
+        <v>0.5</v>
       </c>
       <c r="N22" s="4">
-        <v>231.36688766794595</v>
+        <v>184.125</v>
       </c>
     </row>
     <row r="23">
@@ -12228,16 +12228,16 @@
         <v>252.25</v>
       </c>
       <c r="K23" s="4">
-        <v>299.44653233092754</v>
+        <v>306.25810204093113</v>
       </c>
       <c r="L23" s="4">
-        <v>188.13852602407508</v>
+        <v>114.97925917726775</v>
       </c>
       <c r="M23" s="6">
-        <v>0.6282875428864791</v>
+        <v>0.5</v>
       </c>
       <c r="N23" s="4">
-        <v>158.48553269311435</v>
+        <v>126.125</v>
       </c>
     </row>
     <row r="24">
@@ -12286,16 +12286,16 @@
         <v>132.5</v>
       </c>
       <c r="K24" s="4">
-        <v>113.98989903023869</v>
+        <v>114.60327262943316</v>
       </c>
       <c r="L24" s="4">
-        <v>188.13852602407508</v>
+        <v>114.26031309781452</v>
       </c>
       <c r="M24" s="6">
-        <v>1.6504841887276926</v>
+        <v>0.9970074193890814</v>
       </c>
       <c r="N24" s="4">
-        <v>218.68915500641927</v>
+        <v>132.10348306905328</v>
       </c>
     </row>
     <row r="25">
@@ -12344,16 +12344,16 @@
         <v>95.0</v>
       </c>
       <c r="K25" s="4">
-        <v>113.98989903023869</v>
+        <v>114.60327262943316</v>
       </c>
       <c r="L25" s="4">
-        <v>188.13852602407508</v>
+        <v>114.26031309781452</v>
       </c>
       <c r="M25" s="6">
-        <v>1.6504841887276926</v>
+        <v>0.9970074193890814</v>
       </c>
       <c r="N25" s="4">
-        <v>156.7959979291308</v>
+        <v>94.71570484196273</v>
       </c>
     </row>
     <row r="26">
@@ -12402,16 +12402,16 @@
         <v>122.75</v>
       </c>
       <c r="K26" s="4">
-        <v>103.84867417755734</v>
+        <v>103.2905860153903</v>
       </c>
       <c r="L26" s="4">
-        <v>188.13852602407508</v>
+        <v>114.26031309781452</v>
       </c>
       <c r="M26" s="6">
-        <v>1.811660355936769</v>
+        <v>1.106202583464767</v>
       </c>
       <c r="N26" s="4">
-        <v>222.3813086912384</v>
+        <v>135.78636712030016</v>
       </c>
     </row>
     <row r="27">
@@ -12460,16 +12460,16 @@
         <v>81.0</v>
       </c>
       <c r="K27" s="4">
-        <v>103.84867417755734</v>
+        <v>103.2905860153903</v>
       </c>
       <c r="L27" s="4">
-        <v>188.13852602407508</v>
+        <v>114.26031309781452</v>
       </c>
       <c r="M27" s="6">
-        <v>1.811660355936769</v>
+        <v>1.106202583464767</v>
       </c>
       <c r="N27" s="4">
-        <v>146.74448883087828</v>
+        <v>89.60240926064613</v>
       </c>
     </row>
     <row r="28">
@@ -12518,16 +12518,16 @@
         <v>127.5</v>
       </c>
       <c r="K28" s="4">
-        <v>111.58800882408535</v>
+        <v>112.93072995341235</v>
       </c>
       <c r="L28" s="4">
-        <v>188.13852602407508</v>
+        <v>114.74840800823874</v>
       </c>
       <c r="M28" s="6">
-        <v>1.686010244350439</v>
+        <v>1.016095513201555</v>
       </c>
       <c r="N28" s="4">
-        <v>214.96630615468098</v>
+        <v>129.55217793319827</v>
       </c>
     </row>
     <row r="29">
@@ -12576,16 +12576,16 @@
         <v>90.25</v>
       </c>
       <c r="K29" s="4">
-        <v>111.58800882408535</v>
+        <v>112.93072995341235</v>
       </c>
       <c r="L29" s="4">
-        <v>188.13852602407508</v>
+        <v>114.74840800823874</v>
       </c>
       <c r="M29" s="6">
-        <v>1.686010244350439</v>
+        <v>1.016095513201555</v>
       </c>
       <c r="N29" s="4">
-        <v>152.16242455262713</v>
+        <v>91.70262006644033</v>
       </c>
     </row>
     <row r="30">
@@ -12634,16 +12634,16 @@
         <v>106.0</v>
       </c>
       <c r="K30" s="4">
-        <v>100.96170111397849</v>
+        <v>100.5537473987474</v>
       </c>
       <c r="L30" s="4">
-        <v>188.13852602407508</v>
+        <v>114.74840800823874</v>
       </c>
       <c r="M30" s="6">
-        <v>1.863464303277539</v>
+        <v>1.1411649090829226</v>
       </c>
       <c r="N30" s="4">
-        <v>197.52721614741915</v>
+        <v>120.9634803627898</v>
       </c>
     </row>
     <row r="31">
@@ -12692,16 +12692,16 @@
         <v>118.25</v>
       </c>
       <c r="K31" s="4">
-        <v>100.96170111397849</v>
+        <v>100.5537473987474</v>
       </c>
       <c r="L31" s="4">
-        <v>188.13852602407508</v>
+        <v>114.74840800823874</v>
       </c>
       <c r="M31" s="6">
-        <v>1.863464303277539</v>
+        <v>1.1411649090829226</v>
       </c>
       <c r="N31" s="4">
-        <v>220.354653862569</v>
+        <v>134.9427504990556</v>
       </c>
     </row>
     <row r="32">
@@ -12750,16 +12750,16 @@
         <v>77.0</v>
       </c>
       <c r="K32" s="4">
-        <v>100.96170111397849</v>
+        <v>100.5537473987474</v>
       </c>
       <c r="L32" s="4">
-        <v>188.13852602407508</v>
+        <v>114.74840800823874</v>
       </c>
       <c r="M32" s="6">
-        <v>1.863464303277539</v>
+        <v>1.1411649090829226</v>
       </c>
       <c r="N32" s="4">
-        <v>143.4867513523705</v>
+        <v>87.86969799938504</v>
       </c>
     </row>
     <row r="33">
@@ -12808,16 +12808,16 @@
         <v>127.75</v>
       </c>
       <c r="K33" s="4">
-        <v>108.52186867031656</v>
+        <v>109.35362445112685</v>
       </c>
       <c r="L33" s="4">
-        <v>188.13852602407508</v>
+        <v>112.21293474902966</v>
       </c>
       <c r="M33" s="6">
-        <v>1.7336462072509047</v>
+        <v>1.0261473756563113</v>
       </c>
       <c r="N33" s="4">
-        <v>221.47330297630307</v>
+        <v>131.09032724009376</v>
       </c>
     </row>
     <row r="34">
@@ -12866,16 +12866,16 @@
         <v>90.25</v>
       </c>
       <c r="K34" s="4">
-        <v>108.52186867031656</v>
+        <v>109.35362445112685</v>
       </c>
       <c r="L34" s="4">
-        <v>188.13852602407508</v>
+        <v>112.21293474902966</v>
       </c>
       <c r="M34" s="6">
-        <v>1.7336462072509047</v>
+        <v>1.0261473756563113</v>
       </c>
       <c r="N34" s="4">
-        <v>156.46157020439415</v>
+        <v>92.6098006529821</v>
       </c>
     </row>
     <row r="35">
@@ -12924,16 +12924,16 @@
         <v>132.5</v>
       </c>
       <c r="K35" s="4">
-        <v>108.52186867031656</v>
+        <v>109.35362445112685</v>
       </c>
       <c r="L35" s="4">
-        <v>188.13852602407508</v>
+        <v>112.21293474902966</v>
       </c>
       <c r="M35" s="6">
-        <v>1.7336462072509047</v>
+        <v>1.0261473756563113</v>
       </c>
       <c r="N35" s="4">
-        <v>229.70812246074487</v>
+        <v>135.96452727446126</v>
       </c>
     </row>
     <row r="36">
@@ -12982,16 +12982,16 @@
         <v>95.0</v>
       </c>
       <c r="K36" s="4">
-        <v>108.52186867031656</v>
+        <v>109.35362445112685</v>
       </c>
       <c r="L36" s="4">
-        <v>188.13852602407508</v>
+        <v>112.21293474902966</v>
       </c>
       <c r="M36" s="6">
-        <v>1.7336462072509047</v>
+        <v>1.0261473756563113</v>
       </c>
       <c r="N36" s="4">
-        <v>164.69638968883595</v>
+        <v>97.48400068734958</v>
       </c>
     </row>
     <row r="37">
@@ -13040,16 +13040,16 @@
         <v>76.75</v>
       </c>
       <c r="K37" s="4">
-        <v>97.97290771465813</v>
+        <v>97.14309708122002</v>
       </c>
       <c r="L37" s="4">
-        <v>188.13852602407508</v>
+        <v>112.21293474902966</v>
       </c>
       <c r="M37" s="6">
-        <v>1.9203117516121948</v>
+        <v>1.1551302987098502</v>
       </c>
       <c r="N37" s="4">
-        <v>147.38392693623595</v>
+        <v>88.656250425981</v>
       </c>
     </row>
     <row r="38">
@@ -13098,16 +13098,16 @@
         <v>122.75</v>
       </c>
       <c r="K38" s="4">
-        <v>97.97290771465813</v>
+        <v>97.14309708122002</v>
       </c>
       <c r="L38" s="4">
-        <v>188.13852602407508</v>
+        <v>112.21293474902966</v>
       </c>
       <c r="M38" s="6">
-        <v>1.9203117516121948</v>
+        <v>1.1551302987098502</v>
       </c>
       <c r="N38" s="4">
-        <v>235.7182675103969</v>
+        <v>141.7922441666341</v>
       </c>
     </row>
     <row r="39">
@@ -13156,16 +13156,16 @@
         <v>81.0</v>
       </c>
       <c r="K39" s="4">
-        <v>97.97290771465813</v>
+        <v>97.14309708122002</v>
       </c>
       <c r="L39" s="4">
-        <v>188.13852602407508</v>
+        <v>112.21293474902966</v>
       </c>
       <c r="M39" s="6">
-        <v>1.9203117516121948</v>
+        <v>1.1551302987098502</v>
       </c>
       <c r="N39" s="4">
-        <v>155.54525188058778</v>
+        <v>93.56555419549787</v>
       </c>
     </row>
     <row r="40">
@@ -13214,16 +13214,16 @@
         <v>132.5</v>
       </c>
       <c r="K40" s="4">
-        <v>115.87353790312686</v>
+        <v>114.02053530271539</v>
       </c>
       <c r="L40" s="4">
-        <v>188.13852602407508</v>
+        <v>114.26031309781452</v>
       </c>
       <c r="M40" s="6">
-        <v>1.6236539371168899</v>
+        <v>1.0021029351814787</v>
       </c>
       <c r="N40" s="4">
-        <v>215.13414666798792</v>
+        <v>132.77863891154593</v>
       </c>
     </row>
     <row r="41">
@@ -13272,16 +13272,16 @@
         <v>95.0</v>
       </c>
       <c r="K41" s="4">
-        <v>115.87353790312686</v>
+        <v>114.02053530271539</v>
       </c>
       <c r="L41" s="4">
-        <v>188.13852602407508</v>
+        <v>114.26031309781452</v>
       </c>
       <c r="M41" s="6">
-        <v>1.6236539371168899</v>
+        <v>1.0021029351814787</v>
       </c>
       <c r="N41" s="4">
-        <v>154.24712402610453</v>
+        <v>95.19977884224048</v>
       </c>
     </row>
     <row r="42">
@@ -13330,16 +13330,16 @@
         <v>110.75</v>
       </c>
       <c r="K42" s="4">
-        <v>104.89101710702565</v>
+        <v>101.52411225738976</v>
       </c>
       <c r="L42" s="4">
-        <v>188.13852602407508</v>
+        <v>114.26031309781452</v>
       </c>
       <c r="M42" s="6">
-        <v>1.7936571806917248</v>
+        <v>1.1254500094335738</v>
       </c>
       <c r="N42" s="4">
-        <v>198.64753276160852</v>
+        <v>124.64358854476829</v>
       </c>
     </row>
     <row r="43">
@@ -13388,16 +13388,16 @@
         <v>122.75</v>
       </c>
       <c r="K43" s="4">
-        <v>104.89101710702565</v>
+        <v>101.52411225738976</v>
       </c>
       <c r="L43" s="4">
-        <v>188.13852602407508</v>
+        <v>114.26031309781452</v>
       </c>
       <c r="M43" s="6">
-        <v>1.7936571806917248</v>
+        <v>1.1254500094335738</v>
       </c>
       <c r="N43" s="4">
-        <v>220.1714189299092</v>
+        <v>138.1489886579712</v>
       </c>
     </row>
     <row r="44">
@@ -13446,16 +13446,16 @@
         <v>81.0</v>
       </c>
       <c r="K44" s="4">
-        <v>104.89101710702565</v>
+        <v>101.52411225738976</v>
       </c>
       <c r="L44" s="4">
-        <v>188.13852602407508</v>
+        <v>114.26031309781452</v>
       </c>
       <c r="M44" s="6">
-        <v>1.7936571806917248</v>
+        <v>1.1254500094335738</v>
       </c>
       <c r="N44" s="4">
-        <v>145.2862316360297</v>
+        <v>91.16145076411948</v>
       </c>
     </row>
     <row r="45">
@@ -13504,16 +13504,16 @@
         <v>406.71</v>
       </c>
       <c r="K45" s="4">
-        <v>338.11924969541514</v>
+        <v>337.7434999001935</v>
       </c>
       <c r="L45" s="4">
-        <v>188.5294537264215</v>
+        <v>114.56350448475818</v>
       </c>
       <c r="M45" s="6">
-        <v>0.5575827282719124</v>
+        <v>0.5</v>
       </c>
       <c r="N45" s="4">
-        <v>226.77447141546946</v>
+        <v>203.355</v>
       </c>
     </row>
     <row r="46">
@@ -13562,16 +13562,16 @@
         <v>296.43</v>
       </c>
       <c r="K46" s="4">
-        <v>338.11924969541514</v>
+        <v>337.7434999001935</v>
       </c>
       <c r="L46" s="4">
-        <v>188.5294537264215</v>
+        <v>114.56350448475818</v>
       </c>
       <c r="M46" s="6">
-        <v>0.5575827282719124</v>
+        <v>0.5</v>
       </c>
       <c r="N46" s="4">
-        <v>165.284248141643</v>
+        <v>148.215</v>
       </c>
     </row>
     <row r="47">
@@ -13620,16 +13620,16 @@
         <v>368.29</v>
       </c>
       <c r="K47" s="4">
-        <v>298.8574391651052</v>
+        <v>306.31838223924734</v>
       </c>
       <c r="L47" s="4">
-        <v>188.5294537264215</v>
+        <v>114.56350448475818</v>
       </c>
       <c r="M47" s="6">
-        <v>0.6308340667480175</v>
+        <v>0.5</v>
       </c>
       <c r="N47" s="4">
-        <v>232.32987844262735</v>
+        <v>184.145</v>
       </c>
     </row>
     <row r="48">
@@ -13678,16 +13678,16 @@
         <v>252.29</v>
       </c>
       <c r="K48" s="4">
-        <v>298.8574391651052</v>
+        <v>306.31838223924734</v>
       </c>
       <c r="L48" s="4">
-        <v>188.5294537264215</v>
+        <v>114.56350448475818</v>
       </c>
       <c r="M48" s="6">
-        <v>0.6308340667480175</v>
+        <v>0.5</v>
       </c>
       <c r="N48" s="4">
-        <v>159.15312669985732</v>
+        <v>126.145</v>
       </c>
     </row>
     <row r="49">
@@ -13736,16 +13736,16 @@
         <v>127.43</v>
       </c>
       <c r="K49" s="4">
-        <v>111.24306222409378</v>
+        <v>112.3536586625937</v>
       </c>
       <c r="L49" s="4">
-        <v>188.5294537264215</v>
+        <v>114.333488052859</v>
       </c>
       <c r="M49" s="6">
-        <v>1.6947524632739617</v>
+        <v>1.0176214056029174</v>
       </c>
       <c r="N49" s="4">
-        <v>215.96230639500095</v>
+        <v>129.67549571597976</v>
       </c>
     </row>
     <row r="50">
@@ -13794,16 +13794,16 @@
         <v>90.29</v>
       </c>
       <c r="K50" s="4">
-        <v>111.24306222409378</v>
+        <v>112.3536586625937</v>
       </c>
       <c r="L50" s="4">
-        <v>188.5294537264215</v>
+        <v>114.333488052859</v>
       </c>
       <c r="M50" s="6">
-        <v>1.6947524632739617</v>
+        <v>1.0176214056029174</v>
       </c>
       <c r="N50" s="4">
-        <v>153.019199909006</v>
+        <v>91.88103671188742</v>
       </c>
     </row>
     <row r="51">
@@ -13852,16 +13852,16 @@
         <v>106.14</v>
       </c>
       <c r="K51" s="4">
-        <v>100.72909147977684</v>
+        <v>100.19015406348338</v>
       </c>
       <c r="L51" s="4">
-        <v>188.5294537264215</v>
+        <v>114.333488052859</v>
       </c>
       <c r="M51" s="6">
-        <v>1.871648507464918</v>
+        <v>1.1411649090829226</v>
       </c>
       <c r="N51" s="4">
-        <v>198.6567725823264</v>
+        <v>121.1232434500614</v>
       </c>
     </row>
     <row r="52">
@@ -13910,16 +13910,16 @@
         <v>118.14</v>
       </c>
       <c r="K52" s="4">
-        <v>100.72909147977684</v>
+        <v>100.19015406348338</v>
       </c>
       <c r="L52" s="4">
-        <v>188.5294537264215</v>
+        <v>114.333488052859</v>
       </c>
       <c r="M52" s="6">
-        <v>1.871648507464918</v>
+        <v>1.1411649090829226</v>
       </c>
       <c r="N52" s="4">
-        <v>221.11655467190542</v>
+        <v>134.81722235905647</v>
       </c>
     </row>
     <row r="53">
@@ -13968,16 +13968,16 @@
         <v>77.0</v>
       </c>
       <c r="K53" s="4">
-        <v>100.72909147977684</v>
+        <v>100.19015406348338</v>
       </c>
       <c r="L53" s="4">
-        <v>188.5294537264215</v>
+        <v>114.333488052859</v>
       </c>
       <c r="M53" s="6">
-        <v>1.871648507464918</v>
+        <v>1.1411649090829226</v>
       </c>
       <c r="N53" s="4">
-        <v>144.1169350747987</v>
+        <v>87.86969799938504</v>
       </c>
     </row>
     <row r="54">
@@ -14026,16 +14026,16 @@
         <v>127.86</v>
       </c>
       <c r="K54" s="4">
-        <v>108.08254017498025</v>
+        <v>108.7948320193083</v>
       </c>
       <c r="L54" s="4">
-        <v>188.5294537264215</v>
+        <v>111.80718283763274</v>
       </c>
       <c r="M54" s="6">
-        <v>1.744309982178451</v>
+        <v>1.0276883631548768</v>
       </c>
       <c r="N54" s="4">
-        <v>223.02747432133674</v>
+        <v>131.40023411298253</v>
       </c>
     </row>
     <row r="55">
@@ -14084,16 +14084,16 @@
         <v>90.29</v>
       </c>
       <c r="K55" s="4">
-        <v>108.08254017498025</v>
+        <v>108.7948320193083</v>
       </c>
       <c r="L55" s="4">
-        <v>188.5294537264215</v>
+        <v>111.80718283763274</v>
       </c>
       <c r="M55" s="6">
-        <v>1.744309982178451</v>
+        <v>1.0276883631548768</v>
       </c>
       <c r="N55" s="4">
-        <v>157.49374829089234</v>
+        <v>92.78998230925383</v>
       </c>
     </row>
     <row r="56">
@@ -14142,16 +14142,16 @@
         <v>132.57</v>
       </c>
       <c r="K56" s="4">
-        <v>108.08254017498025</v>
+        <v>108.7948320193083</v>
       </c>
       <c r="L56" s="4">
-        <v>188.5294537264215</v>
+        <v>111.80718283763274</v>
       </c>
       <c r="M56" s="6">
-        <v>1.744309982178451</v>
+        <v>1.0276883631548768</v>
       </c>
       <c r="N56" s="4">
-        <v>231.24317433739722</v>
+        <v>136.24064630344202</v>
       </c>
     </row>
     <row r="57">
@@ -14200,16 +14200,16 @@
         <v>95.0</v>
       </c>
       <c r="K57" s="4">
-        <v>108.08254017498025</v>
+        <v>108.7948320193083</v>
       </c>
       <c r="L57" s="4">
-        <v>188.5294537264215</v>
+        <v>111.80718283763274</v>
       </c>
       <c r="M57" s="6">
-        <v>1.744309982178451</v>
+        <v>1.0276883631548768</v>
       </c>
       <c r="N57" s="4">
-        <v>165.70944830695282</v>
+        <v>97.63039449971329</v>
       </c>
     </row>
     <row r="58">
@@ -14258,16 +14258,16 @@
         <v>76.86</v>
       </c>
       <c r="K58" s="4">
-        <v>97.65334573304398</v>
+        <v>96.79183635171609</v>
       </c>
       <c r="L58" s="4">
-        <v>188.5294537264215</v>
+        <v>111.80718283763274</v>
       </c>
       <c r="M58" s="6">
-        <v>1.93059902158198</v>
+        <v>1.1551302987098502</v>
       </c>
       <c r="N58" s="4">
-        <v>148.38584079879098</v>
+        <v>88.78331475883908</v>
       </c>
     </row>
     <row r="59">
@@ -14316,16 +14316,16 @@
         <v>122.86</v>
       </c>
       <c r="K59" s="4">
-        <v>97.65334573304398</v>
+        <v>96.79183635171609</v>
       </c>
       <c r="L59" s="4">
-        <v>188.5294537264215</v>
+        <v>111.80718283763274</v>
       </c>
       <c r="M59" s="6">
-        <v>1.93059902158198</v>
+        <v>1.1551302987098502</v>
       </c>
       <c r="N59" s="4">
-        <v>237.19339579156204</v>
+        <v>141.9193084994922</v>
       </c>
     </row>
     <row r="60">
@@ -14374,16 +14374,16 @@
         <v>81.0</v>
       </c>
       <c r="K60" s="4">
-        <v>97.65334573304398</v>
+        <v>96.79183635171609</v>
       </c>
       <c r="L60" s="4">
-        <v>188.5294537264215</v>
+        <v>111.80718283763274</v>
       </c>
       <c r="M60" s="6">
-        <v>1.93059902158198</v>
+        <v>1.1551302987098502</v>
       </c>
       <c r="N60" s="4">
-        <v>156.37852074814037</v>
+        <v>93.56555419549787</v>
       </c>
     </row>
     <row r="61">
@@ -14432,16 +14432,16 @@
         <v>360.43</v>
       </c>
       <c r="K61" s="4">
-        <v>395.1646470103032</v>
+        <v>395.4837769260858</v>
       </c>
       <c r="L61" s="4">
-        <v>188.5294537264215</v>
+        <v>199.4200453387736</v>
       </c>
       <c r="M61" s="6">
-        <v>0.4770908914873297</v>
+        <v>0.5042433014288835</v>
       </c>
       <c r="N61" s="4">
-        <v>171.95787001877824</v>
+        <v>181.7444131340125</v>
       </c>
     </row>
     <row r="62">
@@ -14490,16 +14490,16 @@
         <v>117.0</v>
       </c>
       <c r="K62" s="4">
-        <v>114.08140228647513</v>
+        <v>113.10261038932695</v>
       </c>
       <c r="L62" s="4">
-        <v>170.42453395837398</v>
+        <v>110.34397745200364</v>
       </c>
       <c r="M62" s="6">
-        <v>1.49388533575712</v>
+        <v>0.9756094671216922</v>
       </c>
       <c r="N62" s="4">
-        <v>174.78458428358303</v>
+        <v>114.14630765323798</v>
       </c>
     </row>
     <row r="63">
@@ -14548,16 +14548,16 @@
         <v>105.5</v>
       </c>
       <c r="K63" s="4">
-        <v>107.34093415152904</v>
+        <v>106.57850416075905</v>
       </c>
       <c r="L63" s="4">
-        <v>170.42453395837398</v>
+        <v>110.34397745200364</v>
       </c>
       <c r="M63" s="6">
-        <v>1.5876937843469132</v>
+        <v>1.035330513604928</v>
       </c>
       <c r="N63" s="4">
-        <v>167.50169424859934</v>
+        <v>109.2273691853199</v>
       </c>
     </row>
     <row r="64">
@@ -14606,16 +14606,16 @@
         <v>105.5</v>
       </c>
       <c r="K64" s="4">
-        <v>99.17885055822563</v>
+        <v>99.1153903614236</v>
       </c>
       <c r="L64" s="4">
-        <v>170.42453395837398</v>
+        <v>107.60037157746615</v>
       </c>
       <c r="M64" s="6">
-        <v>1.7183556070588017</v>
+        <v>1.085607100825635</v>
       </c>
       <c r="N64" s="4">
-        <v>181.28651654470357</v>
+        <v>114.53154913710449</v>
       </c>
     </row>
     <row r="65">
@@ -14664,16 +14664,16 @@
         <v>95.25</v>
       </c>
       <c r="K65" s="4">
-        <v>93.24819902830238</v>
+        <v>93.50598611819177</v>
       </c>
       <c r="L65" s="4">
-        <v>170.42453395837398</v>
+        <v>107.60037157746615</v>
       </c>
       <c r="M65" s="6">
-        <v>1.8276442412217238</v>
+        <v>1.1507324401825894</v>
       </c>
       <c r="N65" s="4">
-        <v>174.0831139763692</v>
+        <v>109.60726492739164</v>
       </c>
     </row>
     <row r="66">
@@ -14722,16 +14722,16 @@
         <v>94.0</v>
       </c>
       <c r="K66" s="4">
-        <v>99.17885055822563</v>
+        <v>99.1153903614236</v>
       </c>
       <c r="L66" s="4">
-        <v>170.42453395837398</v>
+        <v>107.60037157746615</v>
       </c>
       <c r="M66" s="6">
-        <v>1.7183556070588017</v>
+        <v>1.085607100825635</v>
       </c>
       <c r="N66" s="4">
-        <v>161.52542706352736</v>
+        <v>102.04706747760969</v>
       </c>
     </row>
     <row r="67">
@@ -14780,16 +14780,16 @@
         <v>84.75</v>
       </c>
       <c r="K67" s="4">
-        <v>93.24819902830238</v>
+        <v>93.50598611819177</v>
       </c>
       <c r="L67" s="4">
-        <v>170.42453395837398</v>
+        <v>107.60037157746615</v>
       </c>
       <c r="M67" s="6">
-        <v>1.8276442412217238</v>
+        <v>1.1507324401825894</v>
       </c>
       <c r="N67" s="4">
-        <v>154.89284944354108</v>
+        <v>97.52457430547445</v>
       </c>
     </row>
     <row r="68">
@@ -14838,16 +14838,16 @@
         <v>117.0</v>
       </c>
       <c r="K68" s="4">
-        <v>109.7947701790648</v>
+        <v>106.37356400611723</v>
       </c>
       <c r="L68" s="4">
-        <v>188.13852602407508</v>
+        <v>104.88203525005937</v>
       </c>
       <c r="M68" s="6">
-        <v>1.713547245622347</v>
+        <v>0.9859783888037061</v>
       </c>
       <c r="N68" s="4">
-        <v>200.48502773781462</v>
+        <v>115.35947149003361</v>
       </c>
     </row>
     <row r="69">
@@ -14896,16 +14896,16 @@
         <v>105.5</v>
       </c>
       <c r="K69" s="4">
-        <v>103.11391160704447</v>
+        <v>99.99699254176039</v>
       </c>
       <c r="L69" s="4">
-        <v>188.13852602407508</v>
+        <v>104.88203525005937</v>
       </c>
       <c r="M69" s="6">
-        <v>1.824569770382195</v>
+        <v>1.0488518962833697</v>
       </c>
       <c r="N69" s="4">
-        <v>192.49211077532158</v>
+        <v>110.6538750578955</v>
       </c>
     </row>
     <row r="70">
@@ -14954,16 +14954,16 @@
         <v>94.0</v>
       </c>
       <c r="K70" s="4">
-        <v>94.81769908780475</v>
+        <v>95.6618215361571</v>
       </c>
       <c r="L70" s="4">
-        <v>188.13852602407508</v>
+        <v>103.78889904865372</v>
       </c>
       <c r="M70" s="6">
-        <v>1.9842131567636094</v>
+        <v>1.0849563324426645</v>
       </c>
       <c r="N70" s="4">
-        <v>186.5160367357793</v>
+        <v>101.98589524961046</v>
       </c>
     </row>
     <row r="71">
@@ -15012,16 +15012,16 @@
         <v>84.75</v>
       </c>
       <c r="K71" s="4">
-        <v>88.87086800312353</v>
+        <v>90.00586913087443</v>
       </c>
       <c r="L71" s="4">
-        <v>188.13852602407508</v>
+        <v>103.78889904865372</v>
       </c>
       <c r="M71" s="6">
-        <v>2.11698760517859</v>
+        <v>1.1531347905516902</v>
       </c>
       <c r="N71" s="4">
-        <v>179.4146995388855</v>
+        <v>97.72817349925575</v>
       </c>
     </row>
     <row r="72">
@@ -15070,16 +15070,16 @@
         <v>105.5</v>
       </c>
       <c r="K72" s="4">
-        <v>95.48694026040924</v>
+        <v>95.24777766021086</v>
       </c>
       <c r="L72" s="4">
-        <v>188.13852602407508</v>
+        <v>102.75642504785716</v>
       </c>
       <c r="M72" s="6">
-        <v>1.9703063634774463</v>
+        <v>1.0788327830013298</v>
       </c>
       <c r="N72" s="4">
-        <v>207.86732134687057</v>
+        <v>113.8168586066403</v>
       </c>
     </row>
     <row r="73">
@@ -15128,16 +15128,16 @@
         <v>95.25</v>
       </c>
       <c r="K73" s="4">
-        <v>89.26603063468418</v>
+        <v>89.48243284521826</v>
       </c>
       <c r="L73" s="4">
-        <v>188.13852602407508</v>
+        <v>102.75642504785716</v>
       </c>
       <c r="M73" s="6">
-        <v>2.1076161299702076</v>
+        <v>1.148341878741714</v>
       </c>
       <c r="N73" s="4">
-        <v>200.7504363796623</v>
+        <v>109.37956395014825</v>
       </c>
     </row>
     <row r="74">
@@ -15186,16 +15186,16 @@
         <v>117.0</v>
       </c>
       <c r="K74" s="4">
-        <v>110.1460947396131</v>
+        <v>106.610387763675</v>
       </c>
       <c r="L74" s="4">
-        <v>188.13852602407508</v>
+        <v>105.98141671019003</v>
       </c>
       <c r="M74" s="6">
-        <v>1.7080816752408443</v>
+        <v>0.9941002835963862</v>
       </c>
       <c r="N74" s="4">
-        <v>199.84555600317879</v>
+        <v>116.30973318077719</v>
       </c>
     </row>
     <row r="75">
@@ -15244,16 +15244,16 @@
         <v>105.5</v>
       </c>
       <c r="K75" s="4">
-        <v>103.44385855827612</v>
+        <v>99.93642210036407</v>
       </c>
       <c r="L75" s="4">
-        <v>188.13852602407508</v>
+        <v>105.98141671019003</v>
       </c>
       <c r="M75" s="6">
-        <v>1.818750079958448</v>
+        <v>1.0604884033546358</v>
       </c>
       <c r="N75" s="4">
-        <v>191.87813343561626</v>
+        <v>111.88152655391407</v>
       </c>
     </row>
     <row r="76">
@@ -15302,16 +15302,16 @@
         <v>94.0</v>
       </c>
       <c r="K76" s="4">
-        <v>95.48694026040924</v>
+        <v>95.24777766021086</v>
       </c>
       <c r="L76" s="4">
-        <v>188.13852602407508</v>
+        <v>102.75642504785716</v>
       </c>
       <c r="M76" s="6">
-        <v>1.9703063634774463</v>
+        <v>1.0788327830013298</v>
       </c>
       <c r="N76" s="4">
-        <v>185.20879816687994</v>
+        <v>101.410281602125</v>
       </c>
     </row>
     <row r="77">
@@ -15360,16 +15360,16 @@
         <v>84.75</v>
       </c>
       <c r="K77" s="4">
-        <v>89.26603063468418</v>
+        <v>89.48243284521826</v>
       </c>
       <c r="L77" s="4">
-        <v>188.13852602407508</v>
+        <v>102.75642504785716</v>
       </c>
       <c r="M77" s="6">
-        <v>2.1076161299702076</v>
+        <v>1.148341878741714</v>
       </c>
       <c r="N77" s="4">
-        <v>178.6204670149751</v>
+        <v>97.32197422336026</v>
       </c>
     </row>
     <row r="78">
@@ -15418,16 +15418,16 @@
         <v>117.0</v>
       </c>
       <c r="K78" s="4">
-        <v>109.71084141291263</v>
+        <v>105.92427082137786</v>
       </c>
       <c r="L78" s="4">
-        <v>188.5294537264215</v>
+        <v>104.87678142859123</v>
       </c>
       <c r="M78" s="6">
-        <v>1.7184213638182178</v>
+        <v>0.9901109596066702</v>
       </c>
       <c r="N78" s="4">
-        <v>201.05529956673146</v>
+        <v>115.84298227398041</v>
       </c>
     </row>
     <row r="79">
@@ -15476,16 +15476,16 @@
         <v>105.57</v>
       </c>
       <c r="K79" s="4">
-        <v>103.11646211177334</v>
+        <v>99.72416563009217</v>
       </c>
       <c r="L79" s="4">
-        <v>188.5294537264215</v>
+        <v>104.87678142859123</v>
       </c>
       <c r="M79" s="6">
-        <v>1.8283157690385514</v>
+        <v>1.0516686779572737</v>
       </c>
       <c r="N79" s="4">
-        <v>193.01529573739987</v>
+        <v>111.02466233194937</v>
       </c>
     </row>
     <row r="80">
@@ -15534,16 +15534,16 @@
         <v>94.0</v>
       </c>
       <c r="K80" s="4">
-        <v>94.56552891115604</v>
+        <v>95.10515449924657</v>
       </c>
       <c r="L80" s="4">
-        <v>188.5294537264215</v>
+        <v>103.78369998529958</v>
       </c>
       <c r="M80" s="6">
-        <v>1.9936382305178482</v>
+        <v>1.091252104386432</v>
       </c>
       <c r="N80" s="4">
-        <v>187.40199366867773</v>
+        <v>102.57769781232462</v>
       </c>
     </row>
     <row r="81">
@@ -15592,16 +15592,16 @@
         <v>84.86</v>
       </c>
       <c r="K81" s="4">
-        <v>88.70451299804475</v>
+        <v>89.6164919340918</v>
       </c>
       <c r="L81" s="4">
-        <v>188.5294537264215</v>
+        <v>103.78369998529958</v>
       </c>
       <c r="M81" s="6">
-        <v>2.125364847339584</v>
+        <v>1.1580870635019613</v>
       </c>
       <c r="N81" s="4">
-        <v>180.3584609452371</v>
+        <v>98.27526820877644</v>
       </c>
     </row>
     <row r="82">
@@ -15650,16 +15650,16 @@
         <v>105.57</v>
       </c>
       <c r="K82" s="4">
-        <v>95.23299021917468</v>
+        <v>94.69351999178059</v>
       </c>
       <c r="L82" s="4">
-        <v>188.5294537264215</v>
+        <v>102.75127770388525</v>
       </c>
       <c r="M82" s="6">
-        <v>1.9796653795342243</v>
+        <v>1.085093021283865</v>
       </c>
       <c r="N82" s="4">
-        <v>208.99327411742803</v>
+        <v>114.55327025693762</v>
       </c>
     </row>
     <row r="83">
@@ -15708,16 +15708,16 @@
         <v>95.14</v>
       </c>
       <c r="K83" s="4">
-        <v>89.09893593522571</v>
+        <v>89.09532010247146</v>
       </c>
       <c r="L83" s="4">
-        <v>188.5294537264215</v>
+        <v>102.75127770388525</v>
       </c>
       <c r="M83" s="6">
-        <v>2.1159562877774554</v>
+        <v>1.1532735679686388</v>
       </c>
       <c r="N83" s="4">
-        <v>201.3120812191471</v>
+        <v>109.7224472565363</v>
       </c>
     </row>
     <row r="84">
@@ -15766,16 +15766,16 @@
         <v>117.0</v>
       </c>
       <c r="K84" s="4">
-        <v>110.06189741570688</v>
+        <v>106.16009429939015</v>
       </c>
       <c r="L84" s="4">
-        <v>188.5294537264215</v>
+        <v>105.97610781776619</v>
       </c>
       <c r="M84" s="6">
-        <v>1.712940246835292</v>
+        <v>0.9982668960230472</v>
       </c>
       <c r="N84" s="4">
-        <v>200.41400887972915</v>
+        <v>116.79722683469652</v>
       </c>
     </row>
     <row r="85">
@@ -15824,16 +15824,16 @@
         <v>105.57</v>
       </c>
       <c r="K85" s="4">
-        <v>103.44641722418562</v>
+        <v>99.66376044613054</v>
       </c>
       <c r="L85" s="4">
-        <v>188.5294537264215</v>
+        <v>105.97610781776619</v>
       </c>
       <c r="M85" s="6">
-        <v>1.822484130289856</v>
+        <v>1.0633364358657482</v>
       </c>
       <c r="N85" s="4">
-        <v>192.3996496347001</v>
+        <v>112.25642753434703</v>
       </c>
     </row>
     <row r="86">
@@ -15882,16 +15882,16 @@
         <v>94.0</v>
       </c>
       <c r="K86" s="4">
-        <v>95.23299021917468</v>
+        <v>94.69351999178059</v>
       </c>
       <c r="L86" s="4">
-        <v>188.5294537264215</v>
+        <v>102.75127770388525</v>
       </c>
       <c r="M86" s="6">
-        <v>1.9796653795342243</v>
+        <v>1.085093021283865</v>
       </c>
       <c r="N86" s="4">
-        <v>186.08854567621708</v>
+        <v>101.9987440006833</v>
       </c>
     </row>
     <row r="87">
@@ -15940,16 +15940,16 @@
         <v>84.86</v>
       </c>
       <c r="K87" s="4">
-        <v>89.09893593522571</v>
+        <v>89.09532010247146</v>
       </c>
       <c r="L87" s="4">
-        <v>188.5294537264215</v>
+        <v>102.75127770388525</v>
       </c>
       <c r="M87" s="6">
-        <v>2.1159562877774554</v>
+        <v>1.1532735679686388</v>
       </c>
       <c r="N87" s="4">
-        <v>179.56005058079487</v>
+        <v>97.86679497781869</v>
       </c>
     </row>
     <row r="88">
@@ -15998,16 +15998,16 @@
         <v>87.0</v>
       </c>
       <c r="K88" s="4">
-        <v>97.47213054228524</v>
+        <v>100.16738948242313</v>
       </c>
       <c r="L88" s="4">
-        <v>188.13852602407508</v>
+        <v>105.49389147251836</v>
       </c>
       <c r="M88" s="6">
-        <v>1.930177631055854</v>
+        <v>1.0531760088549567</v>
       </c>
       <c r="N88" s="4">
-        <v>167.9254539018593</v>
+        <v>91.62631277038123</v>
       </c>
     </row>
     <row r="89">
@@ -16056,16 +16056,16 @@
         <v>162.0</v>
       </c>
       <c r="K89" s="4">
-        <v>136.3044585221214</v>
+        <v>138.68604291486457</v>
       </c>
       <c r="L89" s="4">
-        <v>188.13852602407508</v>
+        <v>111.212473332622</v>
       </c>
       <c r="M89" s="6">
-        <v>1.3802815261068024</v>
+        <v>0.8019009771653243</v>
       </c>
       <c r="N89" s="4">
-        <v>223.605607229302</v>
+        <v>129.90795830078252</v>
       </c>
     </row>
     <row r="90">
@@ -16114,16 +16114,16 @@
         <v>87.0</v>
       </c>
       <c r="K90" s="4">
-        <v>97.32750136209226</v>
+        <v>100.53675968588256</v>
       </c>
       <c r="L90" s="4">
-        <v>188.5294537264215</v>
+        <v>105.48860700153669</v>
       </c>
       <c r="M90" s="6">
-        <v>1.9370625063621656</v>
+        <v>1.049254097020092</v>
       </c>
       <c r="N90" s="4">
-        <v>168.52443805350842</v>
+        <v>91.28510644074801</v>
       </c>
     </row>
     <row r="91">
@@ -16172,16 +16172,16 @@
         <v>162.0</v>
       </c>
       <c r="K91" s="4">
-        <v>136.14813672498443</v>
+        <v>138.5908277994188</v>
       </c>
       <c r="L91" s="4">
-        <v>188.5294537264215</v>
+        <v>111.20690240259069</v>
       </c>
       <c r="M91" s="6">
-        <v>1.3847376707567138</v>
+        <v>0.8024117047885692</v>
       </c>
       <c r="N91" s="4">
-        <v>224.32750266258765</v>
+        <v>129.9906961757482</v>
       </c>
     </row>
     <row r="92">
@@ -16230,16 +16230,16 @@
         <v>57.0</v>
       </c>
       <c r="K92" s="4">
-        <v>55.69439934865881</v>
+        <v>56.7246936262313</v>
       </c>
       <c r="L92" s="4">
-        <v>188.13852602407508</v>
+        <v>100.0741461100599</v>
       </c>
       <c r="M92" s="6">
-        <v>3.378051082772036</v>
+        <v>1.7642077852278153</v>
       </c>
       <c r="N92" s="4">
-        <v>192.54891171800605</v>
+        <v>100.55984375798548</v>
       </c>
     </row>
     <row r="93">
@@ -16288,16 +16288,16 @@
         <v>62.0</v>
       </c>
       <c r="K93" s="4">
-        <v>71.15281687986142</v>
+        <v>71.87373400349027</v>
       </c>
       <c r="L93" s="4">
-        <v>188.13852602407508</v>
+        <v>100.85439783468243</v>
       </c>
       <c r="M93" s="6">
-        <v>2.644147263231183</v>
+        <v>1.4032163381101757</v>
       </c>
       <c r="N93" s="4">
-        <v>163.93713032033332</v>
+        <v>86.99941296283089</v>
       </c>
     </row>
     <row r="94">
@@ -16346,16 +16346,16 @@
         <v>57.0</v>
       </c>
       <c r="K94" s="4">
-        <v>55.54277253379359</v>
+        <v>56.44838223998839</v>
       </c>
       <c r="L94" s="4">
-        <v>188.5294537264215</v>
+        <v>100.06913312860902</v>
       </c>
       <c r="M94" s="6">
-        <v>3.394311179041622</v>
+        <v>1.7727546682058748</v>
       </c>
       <c r="N94" s="4">
-        <v>193.47573720537247</v>
+        <v>101.04701608773486</v>
       </c>
     </row>
     <row r="95">
@@ -16404,16 +16404,16 @@
         <v>116.0</v>
       </c>
       <c r="K95" s="4">
-        <v>95.98887021849617</v>
+        <v>96.61468964926848</v>
       </c>
       <c r="L95" s="4">
-        <v>188.13852602407508</v>
+        <v>98.42781664557464</v>
       </c>
       <c r="M95" s="6">
-        <v>1.9600035462009482</v>
+        <v>1.0187665768309995</v>
       </c>
       <c r="N95" s="4">
-        <v>227.36041135930998</v>
+        <v>118.17692291239594</v>
       </c>
     </row>
     <row r="96">
@@ -16462,16 +16462,16 @@
         <v>104.0</v>
       </c>
       <c r="K96" s="4">
-        <v>99.14091870156075</v>
+        <v>98.96127153952118</v>
       </c>
       <c r="L96" s="4">
-        <v>188.13852602407508</v>
+        <v>98.42781664557464</v>
       </c>
       <c r="M96" s="6">
-        <v>1.8976879424571367</v>
+        <v>0.994609457966256</v>
       </c>
       <c r="N96" s="4">
-        <v>197.3595460155422</v>
+        <v>103.43938362849062</v>
       </c>
     </row>
     <row r="97">
@@ -16520,16 +16520,16 @@
         <v>110.0</v>
       </c>
       <c r="K97" s="4">
-        <v>99.14091870156075</v>
+        <v>98.96127153952118</v>
       </c>
       <c r="L97" s="4">
-        <v>188.13852602407508</v>
+        <v>98.42781664557464</v>
       </c>
       <c r="M97" s="6">
-        <v>1.8976879424571367</v>
+        <v>0.994609457966256</v>
       </c>
       <c r="N97" s="4">
-        <v>208.74567367028504</v>
+        <v>109.40704037628817</v>
       </c>
     </row>
     <row r="98">
@@ -16578,16 +16578,16 @@
         <v>72.75</v>
       </c>
       <c r="K98" s="4">
-        <v>80.9118002250791</v>
+        <v>80.19830646564564</v>
       </c>
       <c r="L98" s="4">
-        <v>188.13852602407508</v>
+        <v>95.00263579120141</v>
       </c>
       <c r="M98" s="6">
-        <v>2.3252297625403764</v>
+        <v>1.1845965329940908</v>
       </c>
       <c r="N98" s="4">
-        <v>169.16046522481238</v>
+        <v>86.17939777532011</v>
       </c>
     </row>
     <row r="99">
@@ -16636,16 +16636,16 @@
         <v>80.0</v>
       </c>
       <c r="K99" s="4">
-        <v>80.9118002250791</v>
+        <v>80.19830646564564</v>
       </c>
       <c r="L99" s="4">
-        <v>188.13852602407508</v>
+        <v>95.00263579120141</v>
       </c>
       <c r="M99" s="6">
-        <v>2.3252297625403764</v>
+        <v>1.1845965329940908</v>
       </c>
       <c r="N99" s="4">
-        <v>186.0183810032301</v>
+        <v>94.76772263952726</v>
       </c>
     </row>
     <row r="100">
@@ -16694,16 +16694,16 @@
         <v>80.0</v>
       </c>
       <c r="K100" s="4">
-        <v>78.54071656000824</v>
+        <v>78.7642420672286</v>
       </c>
       <c r="L100" s="4">
-        <v>188.13852602407508</v>
+        <v>95.00263579120141</v>
       </c>
       <c r="M100" s="6">
-        <v>2.3954266559349477</v>
+        <v>1.2061645398696617</v>
       </c>
       <c r="N100" s="4">
-        <v>191.63413247479582</v>
+        <v>96.49316318957293</v>
       </c>
     </row>
     <row r="101">
@@ -16752,16 +16752,16 @@
         <v>88.0</v>
       </c>
       <c r="K101" s="4">
-        <v>78.54071656000824</v>
+        <v>78.7642420672286</v>
       </c>
       <c r="L101" s="4">
-        <v>188.13852602407508</v>
+        <v>95.00263579120141</v>
       </c>
       <c r="M101" s="6">
-        <v>2.3954266559349477</v>
+        <v>1.2061645398696617</v>
       </c>
       <c r="N101" s="4">
-        <v>210.7975457222754</v>
+        <v>106.14247950853023</v>
       </c>
     </row>
     <row r="102">
@@ -16810,16 +16810,16 @@
         <v>89.57</v>
       </c>
       <c r="K102" s="4">
-        <v>98.88657453898848</v>
+        <v>97.5048880540554</v>
       </c>
       <c r="L102" s="4">
-        <v>188.5294537264215</v>
+        <v>97.79247026317168</v>
       </c>
       <c r="M102" s="6">
-        <v>1.9065222413189074</v>
+        <v>1.0029494132535883</v>
       </c>
       <c r="N102" s="4">
-        <v>170.7671971549345</v>
+        <v>89.8341789451239</v>
       </c>
     </row>
     <row r="103">
@@ -16868,16 +16868,16 @@
         <v>94.71</v>
       </c>
       <c r="K103" s="4">
-        <v>98.88657453898848</v>
+        <v>97.5048880540554</v>
       </c>
       <c r="L103" s="4">
-        <v>188.5294537264215</v>
+        <v>97.79247026317168</v>
       </c>
       <c r="M103" s="6">
-        <v>1.9065222413189074</v>
+        <v>1.0029494132535883</v>
       </c>
       <c r="N103" s="4">
-        <v>180.5667214753137</v>
+        <v>94.98933892924734</v>
       </c>
     </row>
     <row r="104">
@@ -16926,16 +16926,16 @@
         <v>69.14</v>
       </c>
       <c r="K104" s="4">
-        <v>78.52173850148405</v>
+        <v>77.87086788245188</v>
       </c>
       <c r="L104" s="4">
-        <v>188.5294537264215</v>
+        <v>94.38939877116233</v>
       </c>
       <c r="M104" s="6">
-        <v>2.400984202901447</v>
+        <v>1.2121272221294055</v>
       </c>
       <c r="N104" s="4">
-        <v>166.00404778860604</v>
+        <v>83.8064761380271</v>
       </c>
     </row>
     <row r="105">
@@ -16984,16 +16984,16 @@
         <v>76.0</v>
       </c>
       <c r="K105" s="4">
-        <v>78.52173850148405</v>
+        <v>77.87086788245188</v>
       </c>
       <c r="L105" s="4">
-        <v>188.5294537264215</v>
+        <v>94.38939877116233</v>
       </c>
       <c r="M105" s="6">
-        <v>2.400984202901447</v>
+        <v>1.2121272221294055</v>
       </c>
       <c r="N105" s="4">
-        <v>182.47479942050998</v>
+        <v>92.12166888183482</v>
       </c>
     </row>
     <row r="106">
@@ -17042,16 +17042,16 @@
         <v>132.5</v>
       </c>
       <c r="K106" s="4">
-        <v>134.78268415920513</v>
+        <v>133.42289591412538</v>
       </c>
       <c r="L106" s="4">
-        <v>170.42453395837398</v>
+        <v>106.09264256931598</v>
       </c>
       <c r="M106" s="6">
-        <v>1.2644393827108291</v>
+        <v>0.7951606944403314</v>
       </c>
       <c r="N106" s="4">
-        <v>167.53821820918486</v>
+        <v>105.35879201334392</v>
       </c>
     </row>
     <row r="107">
@@ -17100,16 +17100,16 @@
         <v>119.5</v>
       </c>
       <c r="K107" s="4">
-        <v>129.41861993150866</v>
+        <v>131.034459645504</v>
       </c>
       <c r="L107" s="4">
-        <v>170.42453395837398</v>
+        <v>106.09264256931598</v>
       </c>
       <c r="M107" s="6">
-        <v>1.31684709702952</v>
+        <v>0.8096545203172911</v>
       </c>
       <c r="N107" s="4">
-        <v>157.36322809502764</v>
+        <v>96.75371517791629</v>
       </c>
     </row>
     <row r="108">
@@ -17158,16 +17158,16 @@
         <v>99.0</v>
       </c>
       <c r="K108" s="4">
-        <v>97.39483101737237</v>
+        <v>96.90598706164944</v>
       </c>
       <c r="L108" s="4">
-        <v>188.13852602407508</v>
+        <v>105.27810224788202</v>
       </c>
       <c r="M108" s="6">
-        <v>1.9317095584930655</v>
+        <v>1.0863941995751658</v>
       </c>
       <c r="N108" s="4">
-        <v>191.23924629081347</v>
+        <v>107.55302575794141</v>
       </c>
     </row>
     <row r="109">
@@ -17216,16 +17216,16 @@
         <v>102.0</v>
       </c>
       <c r="K109" s="4">
-        <v>103.3240926513572</v>
+        <v>103.60911154659564</v>
       </c>
       <c r="L109" s="4">
-        <v>188.13852602407508</v>
+        <v>105.27810224788202</v>
       </c>
       <c r="M109" s="6">
-        <v>1.820858245122986</v>
+        <v>1.016108532120129</v>
       </c>
       <c r="N109" s="4">
-        <v>185.72754100254457</v>
+        <v>103.64307027625317</v>
       </c>
     </row>
     <row r="110">
@@ -17274,16 +17274,16 @@
         <v>94.25</v>
       </c>
       <c r="K110" s="4">
-        <v>95.10629526319384</v>
+        <v>94.44904967235733</v>
       </c>
       <c r="L110" s="4">
-        <v>188.13852602407508</v>
+        <v>103.46828767397751</v>
       </c>
       <c r="M110" s="6">
-        <v>1.978192142837938</v>
+        <v>1.0954931577703302</v>
       </c>
       <c r="N110" s="4">
-        <v>186.44460946247565</v>
+        <v>103.25023011985363</v>
       </c>
     </row>
     <row r="111">
@@ -17332,16 +17332,16 @@
         <v>97.0</v>
       </c>
       <c r="K111" s="4">
-        <v>100.47243758947117</v>
+        <v>100.75092837241593</v>
       </c>
       <c r="L111" s="4">
-        <v>188.13852602407508</v>
+        <v>103.46828767397751</v>
       </c>
       <c r="M111" s="6">
-        <v>1.8725386836219322</v>
+        <v>1.0269710596761663</v>
       </c>
       <c r="N111" s="4">
-        <v>181.6362523113274</v>
+        <v>99.61619278858814</v>
       </c>
     </row>
     <row r="112">
@@ -17390,16 +17390,16 @@
         <v>99.0</v>
       </c>
       <c r="K112" s="4">
-        <v>97.44139468028142</v>
+        <v>96.67864680654975</v>
       </c>
       <c r="L112" s="4">
-        <v>188.5294537264215</v>
+        <v>105.31319119231442</v>
       </c>
       <c r="M112" s="6">
-        <v>1.9347983918437592</v>
+        <v>1.0893118043226448</v>
       </c>
       <c r="N112" s="4">
-        <v>191.54504079253218</v>
+        <v>107.84186862794184</v>
       </c>
     </row>
     <row r="113">
@@ -17448,16 +17448,16 @@
         <v>102.0</v>
       </c>
       <c r="K113" s="4">
-        <v>103.29191589331941</v>
+        <v>103.2110515963939</v>
       </c>
       <c r="L113" s="4">
-        <v>188.5294537264215</v>
+        <v>105.31319119231442</v>
       </c>
       <c r="M113" s="6">
-        <v>1.825210154114442</v>
+        <v>1.0203673886023459</v>
       </c>
       <c r="N113" s="4">
-        <v>186.1714357196731</v>
+        <v>104.07747363743928</v>
       </c>
     </row>
     <row r="114">
@@ -17506,16 +17506,16 @@
         <v>94.14</v>
       </c>
       <c r="K114" s="4">
-        <v>95.15176479609313</v>
+        <v>94.227473362188</v>
       </c>
       <c r="L114" s="4">
-        <v>188.5294537264215</v>
+        <v>103.50277341145936</v>
       </c>
       <c r="M114" s="6">
-        <v>1.9813553025572723</v>
+        <v>1.0984351985499954</v>
       </c>
       <c r="N114" s="4">
-        <v>186.52478818274162</v>
+        <v>103.40668959149657</v>
       </c>
     </row>
     <row r="115">
@@ -17564,16 +17564,16 @@
         <v>97.0</v>
       </c>
       <c r="K115" s="4">
-        <v>100.4411488819604</v>
+        <v>100.36384938938008</v>
       </c>
       <c r="L115" s="4">
-        <v>188.5294537264215</v>
+        <v>103.50277341145936</v>
       </c>
       <c r="M115" s="6">
-        <v>1.8770141105014988</v>
+        <v>1.0312754447062034</v>
       </c>
       <c r="N115" s="4">
-        <v>182.0703687186454</v>
+        <v>100.03371813650173</v>
       </c>
     </row>
     <row r="116">
@@ -17622,16 +17622,16 @@
         <v>136.29</v>
       </c>
       <c r="K116" s="4">
-        <v>141.63120937766132</v>
+        <v>144.3410933093013</v>
       </c>
       <c r="L116" s="4">
-        <v>188.5294537264215</v>
+        <v>134.76671676236518</v>
       </c>
       <c r="M116" s="6">
-        <v>1.3311293079741024</v>
+        <v>0.9336683938896067</v>
       </c>
       <c r="N116" s="4">
-        <v>181.41961338379042</v>
+        <v>127.24966540321448</v>
       </c>
     </row>
     <row r="117">
@@ -17680,16 +17680,16 @@
         <v>122.86</v>
       </c>
       <c r="K117" s="4">
-        <v>132.1783433565566</v>
+        <v>133.17874473123607</v>
       </c>
       <c r="L117" s="4">
-        <v>188.5294537264215</v>
+        <v>134.76671676236518</v>
       </c>
       <c r="M117" s="6">
-        <v>1.4263263477123136</v>
+        <v>1.011923614645368</v>
       </c>
       <c r="N117" s="4">
-        <v>175.23845507993485</v>
+        <v>124.32493529532992</v>
       </c>
     </row>
     <row r="118">
@@ -17738,16 +17738,16 @@
         <v>149.71</v>
       </c>
       <c r="K118" s="4">
-        <v>141.63120937766132</v>
+        <v>144.3410933093013</v>
       </c>
       <c r="L118" s="4">
-        <v>188.5294537264215</v>
+        <v>134.76671676236518</v>
       </c>
       <c r="M118" s="6">
-        <v>1.3311293079741024</v>
+        <v>0.9336683938896067</v>
       </c>
       <c r="N118" s="4">
-        <v>199.28336869680288</v>
+        <v>139.77949524921303</v>
       </c>
     </row>
     <row r="119">
@@ -17796,16 +17796,16 @@
         <v>166.57</v>
       </c>
       <c r="K119" s="4">
-        <v>181.57893902194706</v>
+        <v>182.78517670514304</v>
       </c>
       <c r="L119" s="4">
-        <v>188.5294537264215</v>
+        <v>140.83000071387832</v>
       </c>
       <c r="M119" s="6">
-        <v>1.0382781986826917</v>
+        <v>0.7704672952832272</v>
       </c>
       <c r="N119" s="4">
-        <v>172.94599955457593</v>
+        <v>128.33673737532715</v>
       </c>
     </row>
     <row r="120">
@@ -17854,16 +17854,16 @@
         <v>180.14</v>
       </c>
       <c r="K120" s="4">
-        <v>181.57893902194706</v>
+        <v>182.78517670514304</v>
       </c>
       <c r="L120" s="4">
-        <v>188.5294537264215</v>
+        <v>140.83000071387832</v>
       </c>
       <c r="M120" s="6">
-        <v>1.0382781986826917</v>
+        <v>0.7704672952832272</v>
       </c>
       <c r="N120" s="4">
-        <v>187.03543471070006</v>
+        <v>138.79197857232055</v>
       </c>
     </row>
     <row r="121">
@@ -17912,16 +17912,16 @@
         <v>153.14</v>
       </c>
       <c r="K121" s="4">
-        <v>172.64506415381217</v>
+        <v>172.43315288816922</v>
       </c>
       <c r="L121" s="4">
-        <v>188.5294537264215</v>
+        <v>140.83000071387832</v>
       </c>
       <c r="M121" s="6">
-        <v>1.0920060451798246</v>
+        <v>0.816722297046978</v>
       </c>
       <c r="N121" s="4">
-        <v>167.22980575883832</v>
+        <v>125.0728525697742</v>
       </c>
     </row>
     <row r="122">
@@ -17970,16 +17970,16 @@
         <v>174.25</v>
       </c>
       <c r="K122" s="4">
-        <v>164.85920243721193</v>
+        <v>166.97236526975954</v>
       </c>
       <c r="L122" s="4">
-        <v>170.42453395837398</v>
+        <v>149.95513104549858</v>
       </c>
       <c r="M122" s="6">
-        <v>1.0337580883498552</v>
+        <v>0.8980835289913512</v>
       </c>
       <c r="N122" s="4">
-        <v>180.13234689496227</v>
+        <v>156.49105492674295</v>
       </c>
     </row>
     <row r="123">
@@ -18028,16 +18028,16 @@
         <v>193.25</v>
       </c>
       <c r="K123" s="4">
-        <v>164.85920243721193</v>
+        <v>166.97236526975954</v>
       </c>
       <c r="L123" s="4">
-        <v>170.42453395837398</v>
+        <v>149.95513104549858</v>
       </c>
       <c r="M123" s="6">
-        <v>1.0337580883498552</v>
+        <v>0.8980835289913512</v>
       </c>
       <c r="N123" s="4">
-        <v>199.7737505736095</v>
+        <v>173.55464197757863</v>
       </c>
     </row>
     <row r="124">
@@ -18086,16 +18086,16 @@
         <v>87.0</v>
       </c>
       <c r="K124" s="4">
-        <v>95.17172184214442</v>
+        <v>96.22318296245375</v>
       </c>
       <c r="L124" s="4">
-        <v>188.13852602407508</v>
+        <v>115.22390048604666</v>
       </c>
       <c r="M124" s="6">
-        <v>1.9768322184622138</v>
+        <v>1.1974650696288751</v>
       </c>
       <c r="N124" s="4">
-        <v>171.9844030062126</v>
+        <v>104.17946105771213</v>
       </c>
     </row>
     <row r="125">
@@ -18144,16 +18144,16 @@
         <v>81.0</v>
       </c>
       <c r="K125" s="4">
-        <v>95.17172184214442</v>
+        <v>96.22318296245375</v>
       </c>
       <c r="L125" s="4">
-        <v>188.13852602407508</v>
+        <v>115.22390048604666</v>
       </c>
       <c r="M125" s="6">
-        <v>1.9768322184622138</v>
+        <v>1.1974650696288751</v>
       </c>
       <c r="N125" s="4">
-        <v>160.1234096954393</v>
+        <v>96.99467063993889</v>
       </c>
     </row>
     <row r="126">
@@ -18202,16 +18202,16 @@
         <v>85.0</v>
       </c>
       <c r="K126" s="4">
-        <v>95.17172184214442</v>
+        <v>96.22318296245375</v>
       </c>
       <c r="L126" s="4">
-        <v>188.13852602407508</v>
+        <v>115.22390048604666</v>
       </c>
       <c r="M126" s="6">
-        <v>1.9768322184622138</v>
+        <v>1.1974650696288751</v>
       </c>
       <c r="N126" s="4">
-        <v>168.03073856928816</v>
+        <v>101.78453091845438</v>
       </c>
     </row>
     <row r="127">
@@ -18260,16 +18260,16 @@
         <v>116.5</v>
       </c>
       <c r="K127" s="4">
-        <v>119.71860386299319</v>
+        <v>119.15044129221842</v>
       </c>
       <c r="L127" s="4">
-        <v>188.13852602407508</v>
+        <v>107.74502734703366</v>
       </c>
       <c r="M127" s="6">
-        <v>1.5715061816071805</v>
+        <v>0.9042771992995579</v>
       </c>
       <c r="N127" s="4">
-        <v>183.08047015723653</v>
+        <v>105.3482937183985</v>
       </c>
     </row>
     <row r="128">
@@ -18318,16 +18318,16 @@
         <v>116.57</v>
       </c>
       <c r="K128" s="4">
-        <v>119.36380100795026</v>
+        <v>119.42686231201215</v>
       </c>
       <c r="L128" s="4">
-        <v>188.5294537264215</v>
+        <v>108.35873773525829</v>
       </c>
       <c r="M128" s="6">
-        <v>1.5794524984493787</v>
+        <v>0.9073229894641499</v>
       </c>
       <c r="N128" s="4">
-        <v>184.11677774424408</v>
+        <v>105.76664088183595</v>
       </c>
     </row>
     <row r="129">
@@ -18376,16 +18376,16 @@
         <v>77.0</v>
       </c>
       <c r="K129" s="4">
-        <v>86.10694909733152</v>
+        <v>86.55238175452442</v>
       </c>
       <c r="L129" s="4">
-        <v>188.13852602407508</v>
+        <v>100.94840098998617</v>
       </c>
       <c r="M129" s="6">
-        <v>2.184940100611526</v>
+        <v>1.166327245347113</v>
       </c>
       <c r="N129" s="4">
-        <v>168.24038774708748</v>
+        <v>89.8071978917277</v>
       </c>
     </row>
     <row r="130">
@@ -18434,16 +18434,16 @@
         <v>71.0</v>
       </c>
       <c r="K130" s="4">
-        <v>71.59545186446859</v>
+        <v>70.49004710271471</v>
       </c>
       <c r="L130" s="4">
-        <v>188.13852602407508</v>
+        <v>88.7118446727196</v>
       </c>
       <c r="M130" s="6">
-        <v>2.6277999666825838</v>
+        <v>1.2585017079567693</v>
       </c>
       <c r="N130" s="4">
-        <v>186.57379763446346</v>
+        <v>89.35362126493062</v>
       </c>
     </row>
     <row r="131">
@@ -18492,16 +18492,16 @@
         <v>77.0</v>
       </c>
       <c r="K131" s="4">
-        <v>85.80444038679816</v>
+        <v>86.32029817382708</v>
       </c>
       <c r="L131" s="4">
-        <v>188.5294537264215</v>
+        <v>101.26168864642264</v>
       </c>
       <c r="M131" s="6">
-        <v>2.197199269368215</v>
+        <v>1.1730924335143909</v>
       </c>
       <c r="N131" s="4">
-        <v>169.18434374135256</v>
+        <v>90.32811738060809</v>
       </c>
     </row>
     <row r="132">
@@ -18550,16 +18550,16 @@
         <v>66.71</v>
       </c>
       <c r="K132" s="4">
-        <v>71.38519117234672</v>
+        <v>70.30103344181373</v>
       </c>
       <c r="L132" s="4">
-        <v>188.5294537264215</v>
+        <v>88.98715686828798</v>
       </c>
       <c r="M132" s="6">
-        <v>2.641016303665154</v>
+        <v>1.2658015467431252</v>
       </c>
       <c r="N132" s="4">
-        <v>176.1821976175024</v>
+        <v>84.44162118323388</v>
       </c>
     </row>
     <row r="133">
@@ -18608,16 +18608,16 @@
         <v>101.0</v>
       </c>
       <c r="K133" s="4">
-        <v>112.20848842340718</v>
+        <v>110.57769435494272</v>
       </c>
       <c r="L133" s="4">
-        <v>170.42453395837398</v>
+        <v>143.147824734762</v>
       </c>
       <c r="M133" s="6">
-        <v>1.5188203348332663</v>
+        <v>1.2945452115801275</v>
       </c>
       <c r="N133" s="4">
-        <v>153.4008538181599</v>
+        <v>130.74906636959287</v>
       </c>
     </row>
     <row r="134">
@@ -18666,16 +18666,16 @@
         <v>112.0</v>
       </c>
       <c r="K134" s="4">
-        <v>117.39610816191889</v>
+        <v>118.53896886232035</v>
       </c>
       <c r="L134" s="4">
-        <v>188.13852602407508</v>
+        <v>133.78521836299396</v>
       </c>
       <c r="M134" s="6">
-        <v>1.6025959375466223</v>
+        <v>1.1286180371484562</v>
       </c>
       <c r="N134" s="4">
-        <v>179.4907450052217</v>
+        <v>126.4052201606271</v>
       </c>
     </row>
     <row r="135">
@@ -18724,16 +18724,16 @@
         <v>101.0</v>
       </c>
       <c r="K135" s="4">
-        <v>106.73105405364012</v>
+        <v>107.2178429401152</v>
       </c>
       <c r="L135" s="4">
-        <v>188.13852602407508</v>
+        <v>133.78521836299396</v>
       </c>
       <c r="M135" s="6">
-        <v>1.7627346388757839</v>
+        <v>1.2477887513342114</v>
       </c>
       <c r="N135" s="4">
-        <v>178.03619852645417</v>
+        <v>126.02666388475535</v>
       </c>
     </row>
     <row r="136">
@@ -18782,16 +18782,16 @@
         <v>177.0</v>
       </c>
       <c r="K136" s="4">
-        <v>173.74137300210734</v>
+        <v>170.44174482640133</v>
       </c>
       <c r="L136" s="4">
-        <v>188.13852602407508</v>
+        <v>132.89945806239035</v>
       </c>
       <c r="M136" s="6">
-        <v>1.0828654267731217</v>
+        <v>0.7797353764346368</v>
       </c>
       <c r="N136" s="4">
-        <v>191.66718053884253</v>
+        <v>138.0131616289307</v>
       </c>
     </row>
     <row r="137">
@@ -18840,16 +18840,16 @@
         <v>159.5</v>
       </c>
       <c r="K137" s="4">
-        <v>153.561782177783</v>
+        <v>152.63411350354528</v>
       </c>
       <c r="L137" s="4">
-        <v>188.13852602407508</v>
+        <v>132.89945806239035</v>
       </c>
       <c r="M137" s="6">
-        <v>1.2251650336166429</v>
+        <v>0.870706128609339</v>
       </c>
       <c r="N137" s="4">
-        <v>195.41382286185453</v>
+        <v>138.87762751318957</v>
       </c>
     </row>
     <row r="138">
@@ -18898,16 +18898,16 @@
         <v>202.0</v>
       </c>
       <c r="K138" s="4">
-        <v>185.42182987589757</v>
+        <v>188.4089980768099</v>
       </c>
       <c r="L138" s="4">
-        <v>188.13852602407508</v>
+        <v>142.53029819967475</v>
       </c>
       <c r="M138" s="6">
-        <v>1.0146514364031236</v>
+        <v>0.7564941146896208</v>
       </c>
       <c r="N138" s="4">
-        <v>204.95959015343098</v>
+        <v>152.8118111673034</v>
       </c>
     </row>
     <row r="139">
@@ -18956,16 +18956,16 @@
         <v>182.0</v>
       </c>
       <c r="K139" s="4">
-        <v>170.017295379085</v>
+        <v>168.85707689703608</v>
       </c>
       <c r="L139" s="4">
-        <v>188.13852602407508</v>
+        <v>142.53029819967475</v>
       </c>
       <c r="M139" s="6">
-        <v>1.106584630725865</v>
+        <v>0.844088390127619</v>
       </c>
       <c r="N139" s="4">
-        <v>201.39840279210745</v>
+        <v>153.62408700322666</v>
       </c>
     </row>
     <row r="140">
@@ -19014,16 +19014,16 @@
         <v>112.0</v>
       </c>
       <c r="K140" s="4">
-        <v>117.23517347289041</v>
+        <v>117.9662878304016</v>
       </c>
       <c r="L140" s="4">
-        <v>188.5294537264215</v>
+        <v>133.7058655864135</v>
       </c>
       <c r="M140" s="6">
-        <v>1.6081304623993011</v>
+        <v>1.1334243710257328</v>
       </c>
       <c r="N140" s="4">
-        <v>180.1106117887217</v>
+        <v>126.94352955488208</v>
       </c>
     </row>
     <row r="141">
@@ -19072,16 +19072,16 @@
         <v>101.0</v>
       </c>
       <c r="K141" s="4">
-        <v>106.58473975700164</v>
+        <v>106.69985610823747</v>
       </c>
       <c r="L141" s="4">
-        <v>188.5294537264215</v>
+        <v>133.7058655864135</v>
       </c>
       <c r="M141" s="6">
-        <v>1.7688221987147728</v>
+        <v>1.2531025857315201</v>
       </c>
       <c r="N141" s="4">
-        <v>178.65104207019203</v>
+        <v>126.56336115888354</v>
       </c>
     </row>
     <row r="142">
@@ -19130,16 +19130,16 @@
         <v>177.0</v>
       </c>
       <c r="K142" s="4">
-        <v>172.85492168873452</v>
+        <v>170.11538344113677</v>
       </c>
       <c r="L142" s="4">
-        <v>188.5294537264215</v>
+        <v>132.63413139904958</v>
       </c>
       <c r="M142" s="6">
-        <v>1.0906802761793073</v>
+        <v>0.7796715894594187</v>
       </c>
       <c r="N142" s="4">
-        <v>193.0504088837374</v>
+        <v>138.00187133431712</v>
       </c>
     </row>
     <row r="143">
@@ -19188,16 +19188,16 @@
         <v>159.43</v>
       </c>
       <c r="K143" s="4">
-        <v>152.77828978824306</v>
+        <v>152.34185012186973</v>
       </c>
       <c r="L143" s="4">
-        <v>188.5294537264215</v>
+        <v>132.63413139904958</v>
       </c>
       <c r="M143" s="6">
-        <v>1.2340068342676898</v>
+        <v>0.870634899687417</v>
       </c>
       <c r="N143" s="4">
-        <v>196.7377095872978</v>
+        <v>138.80532205716491</v>
       </c>
     </row>
     <row r="144">
@@ -19246,16 +19246,16 @@
         <v>202.0</v>
       </c>
       <c r="K144" s="4">
-        <v>184.47578333683006</v>
+        <v>188.31265108251333</v>
       </c>
       <c r="L144" s="4">
-        <v>188.5294537264215</v>
+        <v>142.44575840486502</v>
       </c>
       <c r="M144" s="6">
-        <v>1.0219739974335276</v>
+        <v>0.7564322289873624</v>
       </c>
       <c r="N144" s="4">
-        <v>206.43874748157256</v>
+        <v>152.7993102554472</v>
       </c>
     </row>
     <row r="145">
@@ -19304,16 +19304,16 @@
         <v>182.0</v>
       </c>
       <c r="K145" s="4">
-        <v>169.14984479906076</v>
+        <v>168.77072819824357</v>
       </c>
       <c r="L145" s="4">
-        <v>188.5294537264215</v>
+        <v>142.44575840486502</v>
       </c>
       <c r="M145" s="6">
-        <v>1.1145706574568988</v>
+        <v>0.844019338694466</v>
       </c>
       <c r="N145" s="4">
-        <v>202.8518596571556</v>
+        <v>153.6115196423928</v>
       </c>
     </row>
     <row r="146">
@@ -19362,16 +19362,16 @@
         <v>145.29</v>
       </c>
       <c r="K146" s="4">
-        <v>146.4272385846696</v>
+        <v>150.3389421191882</v>
       </c>
       <c r="L146" s="4">
-        <v>188.5294537264215</v>
+        <v>110.45965644855193</v>
       </c>
       <c r="M146" s="6">
-        <v>1.2875299401170288</v>
+        <v>0.7347374864523118</v>
       </c>
       <c r="N146" s="4">
-        <v>187.06522499960312</v>
+        <v>106.75000940665639</v>
       </c>
     </row>
     <row r="147">
@@ -19420,16 +19420,16 @@
         <v>152.57</v>
       </c>
       <c r="K147" s="4">
-        <v>157.07310833948054</v>
+        <v>161.46531049893548</v>
       </c>
       <c r="L147" s="4">
-        <v>188.5294537264215</v>
+        <v>110.45965644855193</v>
       </c>
       <c r="M147" s="6">
-        <v>1.200265632478315</v>
+        <v>0.684107664409317</v>
       </c>
       <c r="N147" s="4">
-        <v>183.1245275472165</v>
+        <v>104.37430635892949</v>
       </c>
     </row>
     <row r="148">
@@ -19478,16 +19478,16 @@
         <v>129.14</v>
       </c>
       <c r="K148" s="4">
-        <v>139.252000392381</v>
+        <v>137.75188652742887</v>
       </c>
       <c r="L148" s="4">
-        <v>188.5294537264215</v>
+        <v>110.45965644855193</v>
       </c>
       <c r="M148" s="6">
-        <v>1.3538724987446333</v>
+        <v>0.8018740013884124</v>
       </c>
       <c r="N148" s="4">
-        <v>174.83909448788194</v>
+        <v>103.55400853929956</v>
       </c>
     </row>
     <row r="149">
@@ -19536,16 +19536,16 @@
         <v>135.57</v>
       </c>
       <c r="K149" s="4">
-        <v>149.24131919374867</v>
+        <v>147.95432839611206</v>
       </c>
       <c r="L149" s="4">
-        <v>188.5294537264215</v>
+        <v>110.45965644855193</v>
       </c>
       <c r="M149" s="6">
-        <v>1.2632523938070264</v>
+        <v>0.7465794184325775</v>
       </c>
       <c r="N149" s="4">
-        <v>171.25912702841856</v>
+        <v>101.21377175690452</v>
       </c>
     </row>
     <row r="150">
@@ -19594,16 +19594,16 @@
         <v>243.0</v>
       </c>
       <c r="K150" s="4">
-        <v>238.5064154388266</v>
+        <v>240.99467637995386</v>
       </c>
       <c r="L150" s="4">
-        <v>188.13852602407508</v>
+        <v>124.85513486152388</v>
       </c>
       <c r="M150" s="6">
-        <v>0.7888195614273942</v>
+        <v>0.5180825433034728</v>
       </c>
       <c r="N150" s="4">
-        <v>191.6831534268568</v>
+        <v>125.89405802274389</v>
       </c>
     </row>
     <row r="151">
@@ -19652,16 +19652,16 @@
         <v>269.75</v>
       </c>
       <c r="K151" s="4">
-        <v>251.20624879087623</v>
+        <v>248.37897940384062</v>
       </c>
       <c r="L151" s="4">
-        <v>188.13852602407508</v>
+        <v>124.85513486152388</v>
       </c>
       <c r="M151" s="6">
-        <v>0.7489404699510335</v>
+        <v>0.5026799577049605</v>
       </c>
       <c r="N151" s="4">
-        <v>202.0266917692913</v>
+        <v>135.5979185909131</v>
       </c>
     </row>
     <row r="152">
@@ -19710,16 +19710,16 @@
         <v>243.0</v>
       </c>
       <c r="K152" s="4">
-        <v>238.49470452507188</v>
+        <v>240.46582637390281</v>
       </c>
       <c r="L152" s="4">
-        <v>188.5294537264215</v>
+        <v>124.68294136967333</v>
       </c>
       <c r="M152" s="6">
-        <v>0.7904974414499096</v>
+        <v>0.5185058652608813</v>
       </c>
       <c r="N152" s="4">
-        <v>192.09087827232804</v>
+        <v>125.99692525839414</v>
       </c>
     </row>
     <row r="153">
@@ -19768,16 +19768,16 @@
         <v>243.0</v>
       </c>
       <c r="K153" s="4">
-        <v>250.99568957826452</v>
+        <v>247.56529738542056</v>
       </c>
       <c r="L153" s="4">
-        <v>188.5294537264215</v>
+        <v>124.68294136967333</v>
       </c>
       <c r="M153" s="6">
-        <v>0.751126260547335</v>
+        <v>0.5036365867367971</v>
       </c>
       <c r="N153" s="4">
-        <v>182.5236813130024</v>
+        <v>122.3836905770417</v>
       </c>
     </row>
     <row r="154">
@@ -19826,16 +19826,16 @@
         <v>144.5</v>
       </c>
       <c r="K154" s="4">
-        <v>142.26232151491416</v>
+        <v>141.97913695193654</v>
       </c>
       <c r="L154" s="4">
-        <v>188.13852602407508</v>
+        <v>123.01531226884612</v>
       </c>
       <c r="M154" s="6">
-        <v>1.3224761414029886</v>
+        <v>0.8664323147033205</v>
       </c>
       <c r="N154" s="4">
-        <v>191.09780243273187</v>
+        <v>125.19946947462981</v>
       </c>
     </row>
     <row r="155">
@@ -19884,16 +19884,16 @@
         <v>134.75</v>
       </c>
       <c r="K155" s="4">
-        <v>142.26232151491416</v>
+        <v>141.97913695193654</v>
       </c>
       <c r="L155" s="4">
-        <v>188.13852602407508</v>
+        <v>123.01531226884612</v>
       </c>
       <c r="M155" s="6">
-        <v>1.3224761414029886</v>
+        <v>0.8664323147033205</v>
       </c>
       <c r="N155" s="4">
-        <v>178.2036600540527</v>
+        <v>116.75175440627244</v>
       </c>
     </row>
     <row r="156">
@@ -19942,16 +19942,16 @@
         <v>134.75</v>
       </c>
       <c r="K156" s="4">
-        <v>142.07219461878455</v>
+        <v>141.99683830778275</v>
       </c>
       <c r="L156" s="4">
-        <v>188.13852602407508</v>
+        <v>122.19686672017004</v>
       </c>
       <c r="M156" s="6">
-        <v>1.324245933758524</v>
+        <v>0.8605604756868203</v>
       </c>
       <c r="N156" s="4">
-        <v>178.4421395739611</v>
+        <v>115.96052409879903</v>
       </c>
     </row>
     <row r="157">
@@ -20000,16 +20000,16 @@
         <v>144.43</v>
       </c>
       <c r="K157" s="4">
-        <v>140.79966947174077</v>
+        <v>141.33668462324817</v>
       </c>
       <c r="L157" s="4">
-        <v>188.5294537264215</v>
+        <v>122.33595827664529</v>
       </c>
       <c r="M157" s="6">
-        <v>1.3389907407720183</v>
+        <v>0.8655640862296164</v>
       </c>
       <c r="N157" s="4">
-        <v>193.3904326897026</v>
+        <v>125.01342097414351</v>
       </c>
     </row>
     <row r="158">
@@ -20058,16 +20058,16 @@
         <v>134.86</v>
       </c>
       <c r="K158" s="4">
-        <v>140.79966947174077</v>
+        <v>141.33668462324817</v>
       </c>
       <c r="L158" s="4">
-        <v>188.5294537264215</v>
+        <v>122.33595827664529</v>
       </c>
       <c r="M158" s="6">
-        <v>1.3389907407720183</v>
+        <v>0.8655640862296164</v>
       </c>
       <c r="N158" s="4">
-        <v>180.5762913005144</v>
+        <v>116.72997266892608</v>
       </c>
     </row>
     <row r="159">
@@ -20116,16 +20116,16 @@
         <v>134.86</v>
       </c>
       <c r="K159" s="4">
-        <v>140.61149734121688</v>
+        <v>141.3543058808664</v>
       </c>
       <c r="L159" s="4">
-        <v>188.5294537264215</v>
+        <v>121.52203260635376</v>
       </c>
       <c r="M159" s="6">
-        <v>1.3407826336485407</v>
+        <v>0.8596981312247587</v>
       </c>
       <c r="N159" s="4">
-        <v>180.8179459738422</v>
+        <v>115.93888997697097</v>
       </c>
     </row>
     <row r="160">
@@ -20174,16 +20174,16 @@
         <v>68.0</v>
       </c>
       <c r="K160" s="4">
-        <v>81.35281043406955</v>
+        <v>82.70584038096618</v>
       </c>
       <c r="L160" s="4">
-        <v>188.13852602407508</v>
+        <v>103.93540234822568</v>
       </c>
       <c r="M160" s="6">
-        <v>2.312624788501283</v>
+        <v>1.256687579371302</v>
       </c>
       <c r="N160" s="4">
-        <v>157.25848561808724</v>
+        <v>85.45475539724853</v>
       </c>
     </row>
     <row r="161">
@@ -20232,16 +20232,16 @@
         <v>92.0</v>
       </c>
       <c r="K161" s="4">
-        <v>89.06624088293144</v>
+        <v>88.83705711217803</v>
       </c>
       <c r="L161" s="4">
-        <v>170.42453395837398</v>
+        <v>105.72974455115354</v>
       </c>
       <c r="M161" s="6">
-        <v>1.9134582561127709</v>
+        <v>1.1901536136844837</v>
       </c>
       <c r="N161" s="4">
-        <v>176.03815956237491</v>
+        <v>109.4941324589725</v>
       </c>
     </row>
     <row r="162">
@@ -20290,16 +20290,16 @@
         <v>72.0</v>
       </c>
       <c r="K162" s="4">
-        <v>81.33896845241831</v>
+        <v>81.19081429817096</v>
       </c>
       <c r="L162" s="4">
-        <v>188.13852602407508</v>
+        <v>102.46727593549505</v>
       </c>
       <c r="M162" s="6">
-        <v>2.3130183429131193</v>
+        <v>1.2620550344425279</v>
       </c>
       <c r="N162" s="4">
-        <v>166.53732068974458</v>
+        <v>90.867962479862</v>
       </c>
     </row>
     <row r="163">
@@ -20348,16 +20348,16 @@
         <v>87.0</v>
       </c>
       <c r="K163" s="4">
-        <v>84.91164606929368</v>
+        <v>84.46323270291123</v>
       </c>
       <c r="L163" s="4">
-        <v>188.13852602407508</v>
+        <v>102.46727593549505</v>
       </c>
       <c r="M163" s="6">
-        <v>2.2156975483732966</v>
+        <v>1.2131583489813937</v>
       </c>
       <c r="N163" s="4">
-        <v>192.7656867084768</v>
+        <v>105.54477636138125</v>
       </c>
     </row>
     <row r="164">
@@ -20406,16 +20406,16 @@
         <v>122.0</v>
       </c>
       <c r="K164" s="4">
-        <v>119.308244849754</v>
+        <v>117.47229752929437</v>
       </c>
       <c r="L164" s="4">
-        <v>188.13852602407508</v>
+        <v>104.41362477459518</v>
       </c>
       <c r="M164" s="6">
-        <v>1.5769113547936247</v>
+        <v>0.8888361509108758</v>
       </c>
       <c r="N164" s="4">
-        <v>192.38318528482222</v>
+        <v>108.43801041112684</v>
       </c>
     </row>
     <row r="165">
@@ -20464,16 +20464,16 @@
         <v>72.0</v>
       </c>
       <c r="K165" s="4">
-        <v>81.04419722370366</v>
+        <v>80.69403432621084</v>
       </c>
       <c r="L165" s="4">
-        <v>188.5294537264215</v>
+        <v>102.46399435849126</v>
       </c>
       <c r="M165" s="6">
-        <v>2.326254811384334</v>
+        <v>1.2697840083725886</v>
       </c>
       <c r="N165" s="4">
-        <v>167.49034641967205</v>
+        <v>91.42444860282639</v>
       </c>
     </row>
     <row r="166">
@@ -20522,16 +20522,16 @@
         <v>87.0</v>
       </c>
       <c r="K166" s="4">
-        <v>84.6039275092941</v>
+        <v>83.94642987568844</v>
       </c>
       <c r="L166" s="4">
-        <v>188.5294537264215</v>
+        <v>102.46399435849126</v>
       </c>
       <c r="M166" s="6">
-        <v>2.228377089298966</v>
+        <v>1.2205878738407867</v>
       </c>
       <c r="N166" s="4">
-        <v>193.86880676901004</v>
+        <v>106.19114502414844</v>
       </c>
     </row>
     <row r="167">
@@ -20580,16 +20580,16 @@
         <v>122.0</v>
       </c>
       <c r="K167" s="4">
-        <v>118.3165217429436</v>
+        <v>116.94088003331456</v>
       </c>
       <c r="L167" s="4">
-        <v>188.5294537264215</v>
+        <v>104.4102808645828</v>
       </c>
       <c r="M167" s="6">
-        <v>1.5934330298859163</v>
+        <v>0.8928467173740954</v>
       </c>
       <c r="N167" s="4">
-        <v>194.3988296460818</v>
+        <v>108.92729951963963</v>
       </c>
     </row>
     <row r="168">
@@ -20638,16 +20638,16 @@
         <v>134.0</v>
       </c>
       <c r="K168" s="4">
-        <v>141.647619804783</v>
+        <v>144.11662054145202</v>
       </c>
       <c r="L168" s="4">
-        <v>170.42453395837398</v>
+        <v>126.24976770346038</v>
       </c>
       <c r="M168" s="6">
-        <v>1.2031584730703626</v>
+        <v>0.876025036037723</v>
       </c>
       <c r="N168" s="4">
-        <v>161.2232353914286</v>
+        <v>117.38735482905487</v>
       </c>
     </row>
     <row r="169">
@@ -20696,16 +20696,16 @@
         <v>106.5</v>
       </c>
       <c r="K169" s="4">
-        <v>103.58014605416015</v>
+        <v>103.72607249506027</v>
       </c>
       <c r="L169" s="4">
-        <v>188.13852602407508</v>
+        <v>115.19023625660618</v>
       </c>
       <c r="M169" s="6">
-        <v>1.8163570258503101</v>
+        <v>1.1105234536099096</v>
       </c>
       <c r="N169" s="4">
-        <v>193.44202325305804</v>
+        <v>118.27074780945537</v>
       </c>
     </row>
     <row r="170">
@@ -20754,16 +20754,16 @@
         <v>96.0</v>
       </c>
       <c r="K170" s="4">
-        <v>97.66389806543422</v>
+        <v>97.62678905808623</v>
       </c>
       <c r="L170" s="4">
-        <v>188.13852602407508</v>
+        <v>115.19023625660618</v>
       </c>
       <c r="M170" s="6">
-        <v>1.9263876391460781</v>
+        <v>1.179903972751475</v>
       </c>
       <c r="N170" s="4">
-        <v>184.9332133580235</v>
+        <v>113.2707813841416</v>
       </c>
     </row>
     <row r="171">
@@ -20812,16 +20812,16 @@
         <v>139.5</v>
       </c>
       <c r="K171" s="4">
-        <v>134.46794990950798</v>
+        <v>134.78190353499588</v>
       </c>
       <c r="L171" s="4">
-        <v>188.13852602407508</v>
+        <v>117.38754432203532</v>
       </c>
       <c r="M171" s="6">
-        <v>1.3991328502493379</v>
+        <v>0.8709444016091956</v>
       </c>
       <c r="N171" s="4">
-        <v>195.17903260978264</v>
+        <v>121.4967440244828</v>
       </c>
     </row>
     <row r="172">
@@ -20870,16 +20870,16 @@
         <v>125.75</v>
       </c>
       <c r="K172" s="4">
-        <v>125.66309315142709</v>
+        <v>125.57439542724543</v>
       </c>
       <c r="L172" s="4">
-        <v>188.13852602407508</v>
+        <v>117.38754432203532</v>
       </c>
       <c r="M172" s="6">
-        <v>1.4971661233689637</v>
+        <v>0.934804773876428</v>
       </c>
       <c r="N172" s="4">
-        <v>188.2686400136472</v>
+        <v>117.55170031496083</v>
       </c>
     </row>
     <row r="173">
@@ -20928,16 +20928,16 @@
         <v>128.5</v>
       </c>
       <c r="K173" s="4">
-        <v>131.4370425253535</v>
+        <v>133.13615962016138</v>
       </c>
       <c r="L173" s="4">
-        <v>188.13852602407508</v>
+        <v>117.95017749080775</v>
       </c>
       <c r="M173" s="6">
-        <v>1.4313965257380483</v>
+        <v>0.8859364565368315</v>
       </c>
       <c r="N173" s="4">
-        <v>183.9344535573392</v>
+        <v>113.84283466498285</v>
       </c>
     </row>
     <row r="174">
@@ -20986,16 +20986,16 @@
         <v>115.75</v>
       </c>
       <c r="K174" s="4">
-        <v>123.00204556393547</v>
+        <v>123.91027321430981</v>
       </c>
       <c r="L174" s="4">
-        <v>188.13852602407508</v>
+        <v>117.95017749080775</v>
       </c>
       <c r="M174" s="6">
-        <v>1.5295560749539097</v>
+        <v>0.9518999065299958</v>
       </c>
       <c r="N174" s="4">
-        <v>177.04611567591505</v>
+        <v>110.18241418084702</v>
       </c>
     </row>
     <row r="175">
@@ -21044,16 +21044,16 @@
         <v>106.5</v>
       </c>
       <c r="K175" s="4">
-        <v>105.96832722080534</v>
+        <v>106.37313980081802</v>
       </c>
       <c r="L175" s="4">
-        <v>188.13852602407508</v>
+        <v>115.19023625660618</v>
       </c>
       <c r="M175" s="6">
-        <v>1.7754222507641588</v>
+        <v>1.082888372687861</v>
       </c>
       <c r="N175" s="4">
-        <v>189.0824697063829</v>
+        <v>115.3276116912572</v>
       </c>
     </row>
     <row r="176">
@@ -21102,16 +21102,16 @@
         <v>96.0</v>
       </c>
       <c r="K176" s="4">
-        <v>99.91567208686753</v>
+        <v>100.1858987825649</v>
       </c>
       <c r="L176" s="4">
-        <v>188.13852602407508</v>
+        <v>115.19023625660618</v>
       </c>
       <c r="M176" s="6">
-        <v>1.8829731321879701</v>
+        <v>1.1497649634965639</v>
       </c>
       <c r="N176" s="4">
-        <v>180.76542069004512</v>
+        <v>110.37743649567014</v>
       </c>
     </row>
     <row r="177">
@@ -21160,16 +21160,16 @@
         <v>106.57</v>
       </c>
       <c r="K177" s="4">
-        <v>103.45147556348381</v>
+        <v>103.31258221201317</v>
       </c>
       <c r="L177" s="4">
-        <v>188.5294537264215</v>
+        <v>114.60107575636002</v>
       </c>
       <c r="M177" s="6">
-        <v>1.8223950185295223</v>
+        <v>1.1092654283016674</v>
       </c>
       <c r="N177" s="4">
-        <v>194.21263712469118</v>
+        <v>118.21441669410869</v>
       </c>
     </row>
     <row r="178">
@@ -21218,16 +21218,16 @@
         <v>96.0</v>
       </c>
       <c r="K178" s="4">
-        <v>97.61961151400037</v>
+        <v>97.38363656892255</v>
       </c>
       <c r="L178" s="4">
-        <v>188.5294537264215</v>
+        <v>114.60107575636002</v>
       </c>
       <c r="M178" s="6">
-        <v>1.931266174926163</v>
+        <v>1.176800125709538</v>
       </c>
       <c r="N178" s="4">
-        <v>185.40155279291164</v>
+        <v>112.97281206811564</v>
       </c>
     </row>
     <row r="179">
@@ -21276,16 +21276,16 @@
         <v>139.57</v>
       </c>
       <c r="K179" s="4">
-        <v>134.30090962472164</v>
+        <v>134.68949761913544</v>
       </c>
       <c r="L179" s="4">
-        <v>188.5294537264215</v>
+        <v>116.35976511078636</v>
       </c>
       <c r="M179" s="6">
-        <v>1.403783892850996</v>
+        <v>0.8639111969948802</v>
       </c>
       <c r="N179" s="4">
-        <v>195.9261179252135</v>
+        <v>120.57608576457542</v>
       </c>
     </row>
     <row r="180">
@@ -21334,16 +21334,16 @@
         <v>125.71</v>
       </c>
       <c r="K180" s="4">
-        <v>125.60611011933001</v>
+        <v>125.67675061270928</v>
       </c>
       <c r="L180" s="4">
-        <v>188.5294537264215</v>
+        <v>116.35976511078636</v>
       </c>
       <c r="M180" s="6">
-        <v>1.5009576647769143</v>
+        <v>0.9258654806358374</v>
       </c>
       <c r="N180" s="4">
-        <v>188.68538803910587</v>
+        <v>116.39054957073111</v>
       </c>
     </row>
     <row r="181">
@@ -21392,16 +21392,16 @@
         <v>128.57</v>
       </c>
       <c r="K181" s="4">
-        <v>131.2737673283293</v>
+        <v>132.6493160505498</v>
       </c>
       <c r="L181" s="4">
-        <v>188.5294537264215</v>
+        <v>117.34690079103778</v>
       </c>
       <c r="M181" s="6">
-        <v>1.436154820291626</v>
+        <v>0.8846400741811545</v>
       </c>
       <c r="N181" s="4">
-        <v>184.64642524489435</v>
+        <v>113.73817433747104</v>
       </c>
     </row>
     <row r="182">
@@ -21450,16 +21450,16 @@
         <v>115.86</v>
       </c>
       <c r="K182" s="4">
-        <v>122.94626920721369</v>
+        <v>123.64256453209495</v>
       </c>
       <c r="L182" s="4">
-        <v>188.5294537264215</v>
+        <v>117.34690079103778</v>
       </c>
       <c r="M182" s="6">
-        <v>1.5334296432262935</v>
+        <v>0.9490817440993554</v>
       </c>
       <c r="N182" s="4">
-        <v>177.66315846419837</v>
+        <v>109.96061087135132</v>
       </c>
     </row>
     <row r="183">
@@ -21508,16 +21508,16 @@
         <v>106.57</v>
       </c>
       <c r="K183" s="4">
-        <v>105.83669005693686</v>
+        <v>105.9841614853914</v>
       </c>
       <c r="L183" s="4">
-        <v>188.5294537264215</v>
+        <v>114.60107575636002</v>
       </c>
       <c r="M183" s="6">
-        <v>1.781324166742162</v>
+        <v>1.0813037924742779</v>
       </c>
       <c r="N183" s="4">
-        <v>189.83571644971218</v>
+        <v>115.23454516398378</v>
       </c>
     </row>
     <row r="184">
@@ -21566,16 +21566,16 @@
         <v>96.0</v>
       </c>
       <c r="K184" s="4">
-        <v>99.87036444874767</v>
+        <v>99.9694467141137</v>
       </c>
       <c r="L184" s="4">
-        <v>188.5294537264215</v>
+        <v>114.60107575636002</v>
       </c>
       <c r="M184" s="6">
-        <v>1.8877417216512982</v>
+        <v>1.1463610085198224</v>
       </c>
       <c r="N184" s="4">
-        <v>181.22320527852463</v>
+        <v>110.05065681790295</v>
       </c>
     </row>
     <row r="185">
@@ -21624,16 +21624,16 @@
         <v>84.5</v>
       </c>
       <c r="K185" s="4">
-        <v>88.88535034881471</v>
+        <v>90.35993448685181</v>
       </c>
       <c r="L185" s="4">
-        <v>188.13852602407508</v>
+        <v>136.20497478260836</v>
       </c>
       <c r="M185" s="6">
-        <v>2.1166426783014187</v>
+        <v>1.5073602648796454</v>
       </c>
       <c r="N185" s="4">
-        <v>178.85630631646987</v>
+        <v>127.37194238233003</v>
       </c>
     </row>
     <row r="186">
@@ -21682,16 +21682,16 @@
         <v>89.0</v>
       </c>
       <c r="K186" s="4">
-        <v>88.88535034881471</v>
+        <v>90.35993448685181</v>
       </c>
       <c r="L186" s="4">
-        <v>188.13852602407508</v>
+        <v>136.20497478260836</v>
       </c>
       <c r="M186" s="6">
-        <v>2.1166426783014187</v>
+        <v>1.5073602648796454</v>
       </c>
       <c r="N186" s="4">
-        <v>188.38119836882626</v>
+        <v>134.15506357428845</v>
       </c>
     </row>
     <row r="187">
@@ -21740,16 +21740,16 @@
         <v>84.57</v>
       </c>
       <c r="K187" s="4">
-        <v>88.5400534197052</v>
+        <v>89.80016131814115</v>
       </c>
       <c r="L187" s="4">
-        <v>188.5294537264215</v>
+        <v>136.1354203471176</v>
       </c>
       <c r="M187" s="6">
-        <v>2.1293126268259397</v>
+        <v>1.5159819130482557</v>
       </c>
       <c r="N187" s="4">
-        <v>180.0759688506697</v>
+        <v>128.20659038649097</v>
       </c>
     </row>
     <row r="188">
@@ -21798,16 +21798,16 @@
         <v>89.0</v>
       </c>
       <c r="K188" s="4">
-        <v>88.5400534197052</v>
+        <v>89.80016131814115</v>
       </c>
       <c r="L188" s="4">
-        <v>188.5294537264215</v>
+        <v>136.1354203471176</v>
       </c>
       <c r="M188" s="6">
-        <v>2.1293126268259397</v>
+        <v>1.5159819130482557</v>
       </c>
       <c r="N188" s="4">
-        <v>189.50882378750865</v>
+        <v>134.92239026129477</v>
       </c>
     </row>
   </sheetData>
@@ -21883,7 +21883,7 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <v>53.35093460216628</v>
+        <v>52.353746007247224</v>
       </c>
     </row>
     <row r="8">
@@ -21893,7 +21893,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <v>-9.350934602166276</v>
+        <v>-8.353746007247224</v>
       </c>
     </row>
     <row r="9">
@@ -21903,7 +21903,7 @@
         </is>
       </c>
       <c r="B9" s="4">
-        <v>146.59913363046866</v>
+        <v>145.859732125439</v>
       </c>
     </row>
     <row r="10">
@@ -21913,7 +21913,7 @@
         </is>
       </c>
       <c r="B10" s="4">
-        <v>93.24819902830238</v>
+        <v>93.50598611819177</v>
       </c>
     </row>
     <row r="11">
@@ -21939,97 +21939,97 @@
         </is>
       </c>
       <c r="B13" s="4">
-        <v>0.15751946589394117</v>
+        <v>0.16374860170351876</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>facility__snorkelling_off_site</t>
+          <t>facility__free_toiletries</t>
         </is>
       </c>
       <c r="B14" s="4">
-        <v>0.04977230962165958</v>
+        <v>0.04755205832501258</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>facility__free_toiletries</t>
+          <t>facility__car_hire</t>
         </is>
       </c>
       <c r="B15" s="4">
-        <v>0.04926909149243423</v>
+        <v>0.037961778470629925</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>facility__bicycle_rental_additional_charge</t>
+          <t>facility__snorkelling_off_site</t>
         </is>
       </c>
       <c r="B16" s="4">
-        <v>0.02503129327209793</v>
+        <v>0.024429188032028433</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>lead_time_days</t>
+          <t>facility__children_s_high_chair</t>
         </is>
       </c>
       <c r="B17" s="4">
-        <v>-0.023492429522285377</v>
+        <v>0.021590710769434262</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>facility__car_hire</t>
+          <t>facility__kids_meals_additional_charge</t>
         </is>
       </c>
       <c r="B18" s="4">
-        <v>0.022632213424765776</v>
+        <v>0.020444482305196292</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bed_count_missing</t>
+          <t>lead_time_days</t>
         </is>
       </c>
       <c r="B19" s="4">
-        <v>0.018673862475134844</v>
+        <v>-0.019587934926983578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>subscore_comfort</t>
+          <t>bed_count_missing</t>
         </is>
       </c>
       <c r="B20" s="4">
-        <v>0.015862240538877567</v>
+        <v>0.019262729144516377</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>facility__kitchenette</t>
+          <t>facility__public_transport_tickets_additional_charge</t>
         </is>
       </c>
       <c r="B21" s="4">
-        <v>0.014672844022467199</v>
+        <v>0.019171340136259946</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>facility__public_transport_tickets_additional_charge</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="B22" s="4">
-        <v>0.013783852315357403</v>
+        <v>0.015254698462623296</v>
       </c>
     </row>
   </sheetData>
